--- a/templates/importar_productos_template.xlsx
+++ b/templates/importar_productos_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duqueroso/Desktop/opencode-projects/control-plus/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9E36E1B-3090-544A-9161-F2D47BD534E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBA4327-82D1-F54B-BBFC-25D6B5CEB968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{C1719250-87E2-DB49-8C6B-072748A47088}"/>
   </bookViews>
@@ -1238,6 +1238,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0"/>
+  </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1715,8 +1718,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Énfasis1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2094,15 +2098,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CC4BADA-14F4-D54D-A860-0AAF5E159701}">
   <dimension ref="A1:H397"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="3" width="10.83203125" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -2125,10 +2132,10 @@
       <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>5370</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>7000</v>
       </c>
       <c r="D2">
@@ -2148,10 +2155,10 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>6220</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>8000</v>
       </c>
       <c r="D3">
@@ -2171,10 +2178,10 @@
       <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>610</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>1000</v>
       </c>
       <c r="D4">
@@ -2194,10 +2201,10 @@
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>440</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>800</v>
       </c>
       <c r="D5">
@@ -2217,10 +2224,10 @@
       <c r="A6" t="s">
         <v>13</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>975</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>1500</v>
       </c>
       <c r="D6">
@@ -2240,10 +2247,10 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>500</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>1000</v>
       </c>
       <c r="D7">
@@ -2263,10 +2270,10 @@
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>11900</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>15000</v>
       </c>
       <c r="D8">
@@ -2286,10 +2293,10 @@
       <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>12300</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>16000</v>
       </c>
       <c r="D9">
@@ -2309,10 +2316,10 @@
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>5550</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>7500</v>
       </c>
       <c r="D10">
@@ -2332,10 +2339,10 @@
       <c r="A11" t="s">
         <v>18</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>12350</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>15500</v>
       </c>
       <c r="D11">
@@ -2355,10 +2362,10 @@
       <c r="A12" t="s">
         <v>19</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>530</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>1000</v>
       </c>
       <c r="D12">
@@ -2378,10 +2385,10 @@
       <c r="A13" t="s">
         <v>20</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>530</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>1000</v>
       </c>
       <c r="D13">
@@ -2401,10 +2408,10 @@
       <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>530</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1000</v>
       </c>
       <c r="D14">
@@ -2424,10 +2431,10 @@
       <c r="A15" t="s">
         <v>22</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>550</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>1000</v>
       </c>
       <c r="D15">
@@ -2447,10 +2454,10 @@
       <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>485</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>800</v>
       </c>
       <c r="D16">
@@ -2470,10 +2477,10 @@
       <c r="A17" t="s">
         <v>24</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>498</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>800</v>
       </c>
       <c r="D17">
@@ -2493,10 +2500,10 @@
       <c r="A18" t="s">
         <v>25</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>485</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>800</v>
       </c>
       <c r="D18">
@@ -2516,10 +2523,10 @@
       <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>485</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>800</v>
       </c>
       <c r="D19">
@@ -2539,10 +2546,10 @@
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>590</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>800</v>
       </c>
       <c r="D20">
@@ -2562,10 +2569,10 @@
       <c r="A21" t="s">
         <v>28</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>485</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>800</v>
       </c>
       <c r="D21">
@@ -2585,10 +2592,10 @@
       <c r="A22" t="s">
         <v>29</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>750</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>1100</v>
       </c>
       <c r="D22">
@@ -2608,10 +2615,10 @@
       <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>750</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>1100</v>
       </c>
       <c r="D23">
@@ -2631,10 +2638,10 @@
       <c r="A24" t="s">
         <v>31</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>750</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>1100</v>
       </c>
       <c r="D24">
@@ -2654,10 +2661,10 @@
       <c r="A25" t="s">
         <v>32</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>260</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>600</v>
       </c>
       <c r="D25">
@@ -2677,10 +2684,10 @@
       <c r="A26" t="s">
         <v>33</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>150</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>400</v>
       </c>
       <c r="D26">
@@ -2700,10 +2707,10 @@
       <c r="A27" t="s">
         <v>34</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>280</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>600</v>
       </c>
       <c r="D27">
@@ -2723,10 +2730,10 @@
       <c r="A28" t="s">
         <v>35</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>710</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>1000</v>
       </c>
       <c r="D28">
@@ -2746,10 +2753,10 @@
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>1300</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>1800</v>
       </c>
       <c r="D29">
@@ -2769,10 +2776,10 @@
       <c r="A30" t="s">
         <v>37</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>1300</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>1800</v>
       </c>
       <c r="D30">
@@ -2792,10 +2799,10 @@
       <c r="A31" t="s">
         <v>38</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="1">
         <v>1300</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>1800</v>
       </c>
       <c r="D31">
@@ -2815,10 +2822,10 @@
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="1">
         <v>3300</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>4200</v>
       </c>
       <c r="D32">
@@ -2838,10 +2845,10 @@
       <c r="A33" t="s">
         <v>40</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="1">
         <v>5470</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>7500</v>
       </c>
       <c r="D33">
@@ -2861,10 +2868,10 @@
       <c r="A34" t="s">
         <v>41</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="1">
         <v>8990</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>13000</v>
       </c>
       <c r="D34">
@@ -2884,10 +2891,10 @@
       <c r="A35" t="s">
         <v>42</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="1">
         <v>16650</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>22000</v>
       </c>
       <c r="D35">
@@ -2907,10 +2914,10 @@
       <c r="A36" t="s">
         <v>43</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="1">
         <v>1650</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="1">
         <v>2300</v>
       </c>
       <c r="D36">
@@ -2930,10 +2937,10 @@
       <c r="A37" t="s">
         <v>44</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="1">
         <v>1650</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>2300</v>
       </c>
       <c r="D37">
@@ -2953,10 +2960,10 @@
       <c r="A38" t="s">
         <v>45</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="1">
         <v>1650</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>2300</v>
       </c>
       <c r="D38">
@@ -2976,10 +2983,10 @@
       <c r="A39" t="s">
         <v>46</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="1">
         <v>1380</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>2000</v>
       </c>
       <c r="D39">
@@ -2999,10 +3006,10 @@
       <c r="A40" t="s">
         <v>47</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="1">
         <v>1380</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>2000</v>
       </c>
       <c r="D40">
@@ -3022,10 +3029,10 @@
       <c r="A41" t="s">
         <v>48</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="1">
         <v>1380</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="1">
         <v>2000</v>
       </c>
       <c r="D41">
@@ -3045,10 +3052,10 @@
       <c r="A42" t="s">
         <v>49</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="1">
         <v>1380</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="1">
         <v>2000</v>
       </c>
       <c r="D42">
@@ -3068,10 +3075,10 @@
       <c r="A43" t="s">
         <v>50</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="1">
         <v>1100</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>2000</v>
       </c>
       <c r="D43">
@@ -3091,10 +3098,10 @@
       <c r="A44" t="s">
         <v>51</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="1">
         <v>980</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="1">
         <v>1500</v>
       </c>
       <c r="D44">
@@ -3114,10 +3121,10 @@
       <c r="A45" t="s">
         <v>52</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="1">
         <v>1999</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="1">
         <v>2500</v>
       </c>
       <c r="D45">
@@ -3137,10 +3144,10 @@
       <c r="A46" t="s">
         <v>53</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="1">
         <v>1505</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="1">
         <v>2000</v>
       </c>
       <c r="D46">
@@ -3160,10 +3167,10 @@
       <c r="A47" t="s">
         <v>54</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="1">
         <v>1505</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="1">
         <v>2000</v>
       </c>
       <c r="D47">
@@ -3183,10 +3190,10 @@
       <c r="A48" t="s">
         <v>55</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="1">
         <v>1505</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="1">
         <v>2000</v>
       </c>
       <c r="D48">
@@ -3206,10 +3213,10 @@
       <c r="A49" t="s">
         <v>56</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="1">
         <v>1505</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="1">
         <v>2000</v>
       </c>
       <c r="D49">
@@ -3229,10 +3236,10 @@
       <c r="A50" t="s">
         <v>57</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="1">
         <v>3800</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="1">
         <v>5000</v>
       </c>
       <c r="D50">
@@ -3252,10 +3259,10 @@
       <c r="A51" t="s">
         <v>58</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="1">
         <v>2021</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="1">
         <v>2500</v>
       </c>
       <c r="D51">
@@ -3275,10 +3282,10 @@
       <c r="A52" t="s">
         <v>59</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="1">
         <v>3468</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="1">
         <v>4300</v>
       </c>
       <c r="D52">
@@ -3298,10 +3305,10 @@
       <c r="A53" t="s">
         <v>60</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="1">
         <v>2950</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="1">
         <v>3800</v>
       </c>
       <c r="D53">
@@ -3321,10 +3328,10 @@
       <c r="A54" t="s">
         <v>61</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="1">
         <v>1220</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="1">
         <v>1700</v>
       </c>
       <c r="D54">
@@ -3344,10 +3351,10 @@
       <c r="A55" t="s">
         <v>62</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="1">
         <v>790</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="1">
         <v>1300</v>
       </c>
       <c r="D55">
@@ -3367,10 +3374,10 @@
       <c r="A56" t="s">
         <v>63</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="1">
         <v>2120</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="1">
         <v>2700</v>
       </c>
       <c r="D56">
@@ -3390,10 +3397,10 @@
       <c r="A57" t="s">
         <v>64</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="1">
         <v>1430</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="1">
         <v>2000</v>
       </c>
       <c r="D57">
@@ -3413,10 +3420,10 @@
       <c r="A58" t="s">
         <v>65</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="1">
         <v>3200</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="1">
         <v>4000</v>
       </c>
       <c r="D58">
@@ -3436,10 +3443,10 @@
       <c r="A59" t="s">
         <v>66</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="1">
         <v>2875</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="1">
         <v>3500</v>
       </c>
       <c r="D59">
@@ -3459,10 +3466,10 @@
       <c r="A60" t="s">
         <v>67</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="1">
         <v>1350</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="1">
         <v>1800</v>
       </c>
       <c r="D60">
@@ -3482,10 +3489,10 @@
       <c r="A61" t="s">
         <v>68</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="1">
         <v>1550</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="1">
         <v>2000</v>
       </c>
       <c r="D61">
@@ -3505,10 +3512,10 @@
       <c r="A62" t="s">
         <v>69</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="1">
         <v>1925</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="1">
         <v>2500</v>
       </c>
       <c r="D62">
@@ -3528,10 +3535,10 @@
       <c r="A63" t="s">
         <v>70</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="1">
         <v>2980</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="1">
         <v>4000</v>
       </c>
       <c r="D63">
@@ -3551,10 +3558,10 @@
       <c r="A64" t="s">
         <v>71</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="1">
         <v>2040</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="1">
         <v>2500</v>
       </c>
       <c r="D64">
@@ -3574,10 +3581,10 @@
       <c r="A65" t="s">
         <v>72</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="1">
         <v>2720</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
         <v>3500</v>
       </c>
       <c r="D65">
@@ -3597,10 +3604,10 @@
       <c r="A66" t="s">
         <v>73</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="1">
         <v>8650</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="1">
         <v>10500</v>
       </c>
       <c r="D66">
@@ -3620,10 +3627,10 @@
       <c r="A67" t="s">
         <v>74</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="1">
         <v>3750</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="1">
         <v>5000</v>
       </c>
       <c r="D67">
@@ -3643,10 +3650,10 @@
       <c r="A68" t="s">
         <v>75</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="1">
         <v>1340</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="1">
         <v>2000</v>
       </c>
       <c r="D68">
@@ -3666,10 +3673,10 @@
       <c r="A69" t="s">
         <v>76</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="1">
         <v>375</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="1">
         <v>600</v>
       </c>
       <c r="D69">
@@ -3689,10 +3696,10 @@
       <c r="A70" t="s">
         <v>77</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="1">
         <v>250</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="1">
         <v>500</v>
       </c>
       <c r="D70">
@@ -3712,10 +3719,10 @@
       <c r="A71" t="s">
         <v>78</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="1">
         <v>650</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="1">
         <v>900</v>
       </c>
       <c r="D71">
@@ -3735,10 +3742,10 @@
       <c r="A72" t="s">
         <v>79</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="1">
         <v>3050</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="1">
         <v>3800</v>
       </c>
       <c r="D72">
@@ -3758,10 +3765,10 @@
       <c r="A73" t="s">
         <v>80</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="1">
         <v>7220</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="1">
         <v>8800</v>
       </c>
       <c r="D73">
@@ -3781,10 +3788,10 @@
       <c r="A74" t="s">
         <v>81</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="1">
         <v>875</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="1">
         <v>1200</v>
       </c>
       <c r="D74">
@@ -3804,10 +3811,10 @@
       <c r="A75" t="s">
         <v>82</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="1">
         <v>2535</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
         <v>3300</v>
       </c>
       <c r="D75">
@@ -3827,10 +3834,10 @@
       <c r="A76" t="s">
         <v>83</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="1">
         <v>3970</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
         <v>5000</v>
       </c>
       <c r="D76">
@@ -3850,10 +3857,10 @@
       <c r="A77" t="s">
         <v>84</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="1">
         <v>2300</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="1">
         <v>3000</v>
       </c>
       <c r="D77">
@@ -3873,10 +3880,10 @@
       <c r="A78" t="s">
         <v>85</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="1">
         <v>1300</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="1">
         <v>2000</v>
       </c>
       <c r="D78">
@@ -3896,10 +3903,10 @@
       <c r="A79" t="s">
         <v>86</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="1">
         <v>1625</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="1">
         <v>2500</v>
       </c>
       <c r="D79">
@@ -3919,10 +3926,10 @@
       <c r="A80" t="s">
         <v>87</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="1">
         <v>1022</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
         <v>1500</v>
       </c>
       <c r="D80">
@@ -3942,10 +3949,10 @@
       <c r="A81" t="s">
         <v>88</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="1">
         <v>1130</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="1">
         <v>1800</v>
       </c>
       <c r="D81">
@@ -3965,10 +3972,10 @@
       <c r="A82" t="s">
         <v>89</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="1">
         <v>1650</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="1">
         <v>2000</v>
       </c>
       <c r="D82">
@@ -3988,10 +3995,10 @@
       <c r="A83" t="s">
         <v>90</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="1">
         <v>1750</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="1">
         <v>2300</v>
       </c>
       <c r="D83">
@@ -4011,10 +4018,10 @@
       <c r="A84" t="s">
         <v>91</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="1">
         <v>1495</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="1">
         <v>2000</v>
       </c>
       <c r="D84">
@@ -4034,10 +4041,10 @@
       <c r="A85" t="s">
         <v>92</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="1">
         <v>1750</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="1">
         <v>2300</v>
       </c>
       <c r="D85">
@@ -4057,10 +4064,10 @@
       <c r="A86" t="s">
         <v>93</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="1">
         <v>2450</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="1">
         <v>3200</v>
       </c>
       <c r="D86">
@@ -4080,10 +4087,10 @@
       <c r="A87" t="s">
         <v>94</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="1">
         <v>2650</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="1">
         <v>3400</v>
       </c>
       <c r="D87">
@@ -4103,10 +4110,10 @@
       <c r="A88" t="s">
         <v>95</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="1">
         <v>122</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="1">
         <v>300</v>
       </c>
       <c r="D88">
@@ -4126,10 +4133,10 @@
       <c r="A89" t="s">
         <v>96</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="1">
         <v>890</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="1">
         <v>1200</v>
       </c>
       <c r="D89">
@@ -4149,10 +4156,10 @@
       <c r="A90" t="s">
         <v>97</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="1">
         <v>2750</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="1">
         <v>3500</v>
       </c>
       <c r="D90">
@@ -4172,10 +4179,10 @@
       <c r="A91" t="s">
         <v>98</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="1">
         <v>1360</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="1">
         <v>2000</v>
       </c>
       <c r="D91">
@@ -4195,10 +4202,10 @@
       <c r="A92" t="s">
         <v>99</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="1">
         <v>2500</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="1">
         <v>3500</v>
       </c>
       <c r="D92">
@@ -4218,10 +4225,10 @@
       <c r="A93" t="s">
         <v>100</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="1">
         <v>900</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="1">
         <v>1500</v>
       </c>
       <c r="D93">
@@ -4241,10 +4248,10 @@
       <c r="A94" t="s">
         <v>101</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="1">
         <v>3275</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="1">
         <v>4200</v>
       </c>
       <c r="D94">
@@ -4264,10 +4271,10 @@
       <c r="A95" t="s">
         <v>102</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="1">
         <v>1160</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="1">
         <v>1500</v>
       </c>
       <c r="D95">
@@ -4287,10 +4294,10 @@
       <c r="A96" t="s">
         <v>103</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="1">
         <v>155</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="1">
         <v>400</v>
       </c>
       <c r="D96">
@@ -4310,10 +4317,10 @@
       <c r="A97" t="s">
         <v>104</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="1">
         <v>195</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="1">
         <v>500</v>
       </c>
       <c r="D97">
@@ -4333,10 +4340,10 @@
       <c r="A98" t="s">
         <v>105</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="1">
         <v>81</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="1">
         <v>200</v>
       </c>
       <c r="D98">
@@ -4356,10 +4363,10 @@
       <c r="A99" t="s">
         <v>106</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="1">
         <v>2840</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="1">
         <v>3600</v>
       </c>
       <c r="D99">
@@ -4379,10 +4386,10 @@
       <c r="A100" t="s">
         <v>107</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="1">
         <v>2840</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="1">
         <v>3600</v>
       </c>
       <c r="D100">
@@ -4402,10 +4409,10 @@
       <c r="A101" t="s">
         <v>108</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="1">
         <v>2840</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="1">
         <v>3600</v>
       </c>
       <c r="D101">
@@ -4425,10 +4432,10 @@
       <c r="A102" t="s">
         <v>109</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="1">
         <v>3590</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="1">
         <v>4500</v>
       </c>
       <c r="D102">
@@ -4448,10 +4455,10 @@
       <c r="A103" t="s">
         <v>110</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="1">
         <v>3590</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="1">
         <v>4500</v>
       </c>
       <c r="D103">
@@ -4471,10 +4478,10 @@
       <c r="A104" t="s">
         <v>111</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="1">
         <v>3450</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="1">
         <v>4500</v>
       </c>
       <c r="D104">
@@ -4494,10 +4501,10 @@
       <c r="A105" t="s">
         <v>112</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="1">
         <v>2990</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="1">
         <v>3700</v>
       </c>
       <c r="D105">
@@ -4517,10 +4524,10 @@
       <c r="A106" t="s">
         <v>113</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="1">
         <v>4900</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="1">
         <v>6000</v>
       </c>
       <c r="D106">
@@ -4540,10 +4547,10 @@
       <c r="A107" t="s">
         <v>114</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="1">
         <v>6500</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="1">
         <v>8000</v>
       </c>
       <c r="D107">
@@ -4563,10 +4570,10 @@
       <c r="A108" t="s">
         <v>115</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="1">
         <v>1670</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="1">
         <v>2200</v>
       </c>
       <c r="D108">
@@ -4586,10 +4593,10 @@
       <c r="A109" t="s">
         <v>116</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="1">
         <v>450</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="1">
         <v>1000</v>
       </c>
       <c r="D109">
@@ -4609,10 +4616,10 @@
       <c r="A110" t="s">
         <v>117</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="1">
         <v>210</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="1">
         <v>800</v>
       </c>
       <c r="D110">
@@ -4632,10 +4639,10 @@
       <c r="A111" t="s">
         <v>118</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="1">
         <v>248</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="1">
         <v>800</v>
       </c>
       <c r="D111">
@@ -4655,10 +4662,10 @@
       <c r="A112" t="s">
         <v>119</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="1">
         <v>275</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="1">
         <v>800</v>
       </c>
       <c r="D112">
@@ -4678,10 +4685,10 @@
       <c r="A113" t="s">
         <v>120</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="1">
         <v>300</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="1">
         <v>800</v>
       </c>
       <c r="D113">
@@ -4701,10 +4708,10 @@
       <c r="A114" t="s">
         <v>121</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="1">
         <v>7440</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="1">
         <v>9000</v>
       </c>
       <c r="D114">
@@ -4724,10 +4731,10 @@
       <c r="A115" t="s">
         <v>122</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="1">
         <v>513</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="1">
         <v>1000</v>
       </c>
       <c r="D115">
@@ -4747,10 +4754,10 @@
       <c r="A116" t="s">
         <v>123</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="1">
         <v>5500</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="1">
         <v>7000</v>
       </c>
       <c r="D116">
@@ -4770,10 +4777,10 @@
       <c r="A117" t="s">
         <v>124</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="1">
         <v>2870</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="1">
         <v>3500</v>
       </c>
       <c r="D117">
@@ -4793,10 +4800,10 @@
       <c r="A118" t="s">
         <v>125</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="1">
         <v>2550</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="1">
         <v>3500</v>
       </c>
       <c r="D118">
@@ -4816,10 +4823,10 @@
       <c r="A119" t="s">
         <v>126</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="1">
         <v>2870</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="1">
         <v>3500</v>
       </c>
       <c r="D119">
@@ -4839,10 +4846,10 @@
       <c r="A120" t="s">
         <v>127</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="1">
         <v>2870</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="1">
         <v>3500</v>
       </c>
       <c r="D120">
@@ -4862,10 +4869,10 @@
       <c r="A121" t="s">
         <v>128</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="1">
         <v>2870</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="1">
         <v>3500</v>
       </c>
       <c r="D121">
@@ -4885,10 +4892,10 @@
       <c r="A122" t="s">
         <v>129</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="1">
         <v>2870</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="1">
         <v>3500</v>
       </c>
       <c r="D122">
@@ -4908,10 +4915,10 @@
       <c r="A123" t="s">
         <v>130</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="1">
         <v>14900</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="1">
         <v>20000</v>
       </c>
       <c r="D123">
@@ -4931,10 +4938,10 @@
       <c r="A124" t="s">
         <v>131</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="1">
         <v>20500</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="1">
         <v>25000</v>
       </c>
       <c r="D124">
@@ -4954,10 +4961,10 @@
       <c r="A125" t="s">
         <v>132</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="1">
         <v>1675</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="1">
         <v>2200</v>
       </c>
       <c r="D125">
@@ -4977,10 +4984,10 @@
       <c r="A126" t="s">
         <v>133</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="1">
         <v>1224</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="1">
         <v>1500</v>
       </c>
       <c r="D126">
@@ -5000,10 +5007,10 @@
       <c r="A127" t="s">
         <v>134</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="1">
         <v>1850</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="1">
         <v>2500</v>
       </c>
       <c r="D127">
@@ -5023,10 +5030,10 @@
       <c r="A128" t="s">
         <v>135</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="1">
         <v>1600</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="1">
         <v>2000</v>
       </c>
       <c r="D128">
@@ -5046,10 +5053,10 @@
       <c r="A129" t="s">
         <v>136</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="1">
         <v>950</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="1">
         <v>1200</v>
       </c>
       <c r="D129">
@@ -5069,10 +5076,10 @@
       <c r="A130" t="s">
         <v>137</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="1">
         <v>1499</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="1">
         <v>2000</v>
       </c>
       <c r="D130">
@@ -5092,10 +5099,10 @@
       <c r="A131" t="s">
         <v>138</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="1">
         <v>410</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="1">
         <v>500</v>
       </c>
       <c r="D131">
@@ -5115,10 +5122,10 @@
       <c r="A132" t="s">
         <v>139</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="1">
         <v>317</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="1">
         <v>500</v>
       </c>
       <c r="D132">
@@ -5138,10 +5145,10 @@
       <c r="A133" t="s">
         <v>140</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="1">
         <v>2533</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="1">
         <v>3500</v>
       </c>
       <c r="D133">
@@ -5161,10 +5168,10 @@
       <c r="A134" t="s">
         <v>141</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="1">
         <v>643</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="1">
         <v>1000</v>
       </c>
       <c r="D134">
@@ -5184,10 +5191,10 @@
       <c r="A135" t="s">
         <v>142</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="1">
         <v>355</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="1">
         <v>800</v>
       </c>
       <c r="D135">
@@ -5207,10 +5214,10 @@
       <c r="A136" t="s">
         <v>143</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="1">
         <v>1700</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="1">
         <v>2500</v>
       </c>
       <c r="D136">
@@ -5230,10 +5237,10 @@
       <c r="A137" t="s">
         <v>144</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="1">
         <v>798</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="1">
         <v>1200</v>
       </c>
       <c r="D137">
@@ -5253,10 +5260,10 @@
       <c r="A138" t="s">
         <v>145</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="1">
         <v>1380</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="1">
         <v>2000</v>
       </c>
       <c r="D138">
@@ -5276,10 +5283,10 @@
       <c r="A139" t="s">
         <v>146</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="1">
         <v>1100</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="1">
         <v>1500</v>
       </c>
       <c r="D139">
@@ -5299,10 +5306,10 @@
       <c r="A140" t="s">
         <v>147</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="1">
         <v>1820</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="1">
         <v>2200</v>
       </c>
       <c r="D140">
@@ -5322,10 +5329,10 @@
       <c r="A141" t="s">
         <v>148</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="1">
         <v>1570</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="1">
         <v>2000</v>
       </c>
       <c r="D141">
@@ -5345,10 +5352,10 @@
       <c r="A142" t="s">
         <v>149</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="1">
         <v>1350</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="1">
         <v>1800</v>
       </c>
       <c r="D142">
@@ -5368,10 +5375,10 @@
       <c r="A143" t="s">
         <v>150</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="1">
         <v>1350</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="1">
         <v>1800</v>
       </c>
       <c r="D143">
@@ -5391,10 +5398,10 @@
       <c r="A144" t="s">
         <v>151</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="1">
         <v>450</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="1">
         <v>700</v>
       </c>
       <c r="D144">
@@ -5414,10 +5421,10 @@
       <c r="A145" t="s">
         <v>152</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="1">
         <v>620</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="1">
         <v>1000</v>
       </c>
       <c r="D145">
@@ -5437,10 +5444,10 @@
       <c r="A146" t="s">
         <v>153</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="1">
         <v>850</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="1">
         <v>1300</v>
       </c>
       <c r="D146">
@@ -5460,10 +5467,10 @@
       <c r="A147" t="s">
         <v>154</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="1">
         <v>1150</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="1">
         <v>1500</v>
       </c>
       <c r="D147">
@@ -5483,10 +5490,10 @@
       <c r="A148" t="s">
         <v>155</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="1">
         <v>1350</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="1">
         <v>1800</v>
       </c>
       <c r="D148">
@@ -5506,10 +5513,10 @@
       <c r="A149" t="s">
         <v>156</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="1">
         <v>280</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="1">
         <v>400</v>
       </c>
       <c r="D149">
@@ -5529,10 +5536,10 @@
       <c r="A150" t="s">
         <v>157</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="1">
         <v>359</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="1">
         <v>500</v>
       </c>
       <c r="D150">
@@ -5552,10 +5559,10 @@
       <c r="A151" t="s">
         <v>158</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="1">
         <v>1450</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="1">
         <v>2000</v>
       </c>
       <c r="D151">
@@ -5575,10 +5582,10 @@
       <c r="A152" t="s">
         <v>159</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="1">
         <v>2200</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="1">
         <v>3000</v>
       </c>
       <c r="D152">
@@ -5598,10 +5605,10 @@
       <c r="A153" t="s">
         <v>160</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="1">
         <v>2100</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="1">
         <v>2600</v>
       </c>
       <c r="D153">
@@ -5621,10 +5628,10 @@
       <c r="A154" t="s">
         <v>161</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="1">
         <v>1370</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="1">
         <v>1700</v>
       </c>
       <c r="D154">
@@ -5644,10 +5651,10 @@
       <c r="A155" t="s">
         <v>162</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="1">
         <v>950</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="1">
         <v>1300</v>
       </c>
       <c r="D155">
@@ -5667,10 +5674,10 @@
       <c r="A156" t="s">
         <v>163</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="1">
         <v>140</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="1">
         <v>500</v>
       </c>
       <c r="D156">
@@ -5690,10 +5697,10 @@
       <c r="A157" t="s">
         <v>164</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="1">
         <v>400</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="1">
         <v>600</v>
       </c>
       <c r="D157">
@@ -5713,10 +5720,10 @@
       <c r="A158" t="s">
         <v>165</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="1">
         <v>620</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="1">
         <v>900</v>
       </c>
       <c r="D158">
@@ -5736,10 +5743,10 @@
       <c r="A159" t="s">
         <v>166</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="1">
         <v>3585</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="1">
         <v>4500</v>
       </c>
       <c r="D159">
@@ -5759,10 +5766,10 @@
       <c r="A160" t="s">
         <v>167</v>
       </c>
-      <c r="B160">
+      <c r="B160" s="1">
         <v>1790</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="1">
         <v>2300</v>
       </c>
       <c r="D160">
@@ -5782,10 +5789,10 @@
       <c r="A161" t="s">
         <v>168</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="1">
         <v>900</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="1">
         <v>1200</v>
       </c>
       <c r="D161">
@@ -5805,10 +5812,10 @@
       <c r="A162" t="s">
         <v>169</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="1">
         <v>450</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="1">
         <v>700</v>
       </c>
       <c r="D162">
@@ -5828,10 +5835,10 @@
       <c r="A163" t="s">
         <v>170</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="1">
         <v>650</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="1">
         <v>800</v>
       </c>
       <c r="D163">
@@ -5851,10 +5858,10 @@
       <c r="A164" t="s">
         <v>171</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="1">
         <v>799</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="1">
         <v>1000</v>
       </c>
       <c r="D164">
@@ -5874,10 +5881,10 @@
       <c r="A165" t="s">
         <v>172</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="1">
         <v>768</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="1">
         <v>1200</v>
       </c>
       <c r="D165">
@@ -5897,10 +5904,10 @@
       <c r="A166" t="s">
         <v>173</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="1">
         <v>870</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="1">
         <v>1300</v>
       </c>
       <c r="D166">
@@ -5920,10 +5927,10 @@
       <c r="A167" t="s">
         <v>174</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="1">
         <v>950</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="1">
         <v>1500</v>
       </c>
       <c r="D167">
@@ -5943,10 +5950,10 @@
       <c r="A168" t="s">
         <v>175</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="1">
         <v>799</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="1">
         <v>1200</v>
       </c>
       <c r="D168">
@@ -5966,10 +5973,10 @@
       <c r="A169" t="s">
         <v>176</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="1">
         <v>500</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="1">
         <v>800</v>
       </c>
       <c r="D169">
@@ -5989,10 +5996,10 @@
       <c r="A170" t="s">
         <v>177</v>
       </c>
-      <c r="B170">
+      <c r="B170" s="1">
         <v>500</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="1">
         <v>800</v>
       </c>
       <c r="D170">
@@ -6012,10 +6019,10 @@
       <c r="A171" t="s">
         <v>178</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="1">
         <v>4491</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="1">
         <v>5500</v>
       </c>
       <c r="D171">
@@ -6035,10 +6042,10 @@
       <c r="A172" t="s">
         <v>179</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="1">
         <v>2082</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="1">
         <v>3500</v>
       </c>
       <c r="D172">
@@ -6058,10 +6065,10 @@
       <c r="A173" t="s">
         <v>180</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="1">
         <v>3300</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="1">
         <v>4000</v>
       </c>
       <c r="D173">
@@ -6081,10 +6088,10 @@
       <c r="A174" t="s">
         <v>181</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="1">
         <v>7700</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="1">
         <v>9500</v>
       </c>
       <c r="D174">
@@ -6104,10 +6111,10 @@
       <c r="A175" t="s">
         <v>182</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="1">
         <v>2600</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="1">
         <v>3200</v>
       </c>
       <c r="D175">
@@ -6127,10 +6134,10 @@
       <c r="A176" t="s">
         <v>183</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="1">
         <v>375</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="1">
         <v>500</v>
       </c>
       <c r="D176">
@@ -6150,10 +6157,10 @@
       <c r="A177" t="s">
         <v>184</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="1">
         <v>599</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="1">
         <v>800</v>
       </c>
       <c r="D177">
@@ -6173,10 +6180,10 @@
       <c r="A178" t="s">
         <v>185</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="1">
         <v>8000</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="1">
         <v>9800</v>
       </c>
       <c r="D178">
@@ -6196,10 +6203,10 @@
       <c r="A179" t="s">
         <v>186</v>
       </c>
-      <c r="B179">
+      <c r="B179" s="1">
         <v>1480</v>
       </c>
-      <c r="C179">
+      <c r="C179" s="1">
         <v>2000</v>
       </c>
       <c r="D179">
@@ -6219,10 +6226,10 @@
       <c r="A180" t="s">
         <v>187</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="1">
         <v>1450</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="1">
         <v>2000</v>
       </c>
       <c r="D180">
@@ -6242,10 +6249,10 @@
       <c r="A181" t="s">
         <v>188</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="1">
         <v>3150</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="1">
         <v>4000</v>
       </c>
       <c r="D181">
@@ -6265,10 +6272,10 @@
       <c r="A182" t="s">
         <v>189</v>
       </c>
-      <c r="B182">
+      <c r="B182" s="1">
         <v>8450</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="1">
         <v>10500</v>
       </c>
       <c r="D182">
@@ -6288,10 +6295,10 @@
       <c r="A183" t="s">
         <v>190</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="1">
         <v>7950</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="1">
         <v>9800</v>
       </c>
       <c r="D183">
@@ -6311,10 +6318,10 @@
       <c r="A184" t="s">
         <v>191</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="1">
         <v>6200</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="1">
         <v>7500</v>
       </c>
       <c r="D184">
@@ -6334,10 +6341,10 @@
       <c r="A185" t="s">
         <v>192</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="1">
         <v>350</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="1">
         <v>500</v>
       </c>
       <c r="D185">
@@ -6357,10 +6364,10 @@
       <c r="A186" t="s">
         <v>193</v>
       </c>
-      <c r="B186">
+      <c r="B186" s="1">
         <v>9380</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="1">
         <v>12000</v>
       </c>
       <c r="D186">
@@ -6380,10 +6387,10 @@
       <c r="A187" t="s">
         <v>194</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="1">
         <v>670</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="1">
         <v>1000</v>
       </c>
       <c r="D187">
@@ -6403,10 +6410,10 @@
       <c r="A188" t="s">
         <v>195</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="1">
         <v>2250</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="1">
         <v>3000</v>
       </c>
       <c r="D188">
@@ -6426,10 +6433,10 @@
       <c r="A189" t="s">
         <v>196</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="1">
         <v>2250</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="1">
         <v>3000</v>
       </c>
       <c r="D189">
@@ -6449,10 +6456,10 @@
       <c r="A190" t="s">
         <v>197</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="1">
         <v>1725</v>
       </c>
-      <c r="C190">
+      <c r="C190" s="1">
         <v>2500</v>
       </c>
       <c r="D190">
@@ -6472,10 +6479,10 @@
       <c r="A191" t="s">
         <v>198</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="1">
         <v>1725</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="1">
         <v>2500</v>
       </c>
       <c r="D191">
@@ -6495,10 +6502,10 @@
       <c r="A192" t="s">
         <v>199</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="1">
         <v>2950</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="1">
         <v>3700</v>
       </c>
       <c r="D192">
@@ -6518,10 +6525,10 @@
       <c r="A193" t="s">
         <v>200</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="1">
         <v>2950</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="1">
         <v>3700</v>
       </c>
       <c r="D193">
@@ -6541,10 +6548,10 @@
       <c r="A194" t="s">
         <v>201</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="1">
         <v>4185</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="1">
         <v>5100</v>
       </c>
       <c r="D194">
@@ -6564,10 +6571,10 @@
       <c r="A195" t="s">
         <v>202</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="1">
         <v>4185</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="1">
         <v>5100</v>
       </c>
       <c r="D195">
@@ -6587,10 +6594,10 @@
       <c r="A196" t="s">
         <v>203</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="1">
         <v>2990</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="1">
         <v>3800</v>
       </c>
       <c r="D196">
@@ -6610,10 +6617,10 @@
       <c r="A197" t="s">
         <v>204</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="1">
         <v>2990</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="1">
         <v>3800</v>
       </c>
       <c r="D197">
@@ -6633,10 +6640,10 @@
       <c r="A198" t="s">
         <v>205</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="1">
         <v>2990</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="1">
         <v>3800</v>
       </c>
       <c r="D198">
@@ -6656,10 +6663,10 @@
       <c r="A199" t="s">
         <v>205</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="1">
         <v>2990</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="1">
         <v>3800</v>
       </c>
       <c r="D199">
@@ -6679,10 +6686,10 @@
       <c r="A200" t="s">
         <v>206</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="1">
         <v>2900</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="1">
         <v>3500</v>
       </c>
       <c r="D200">
@@ -6702,10 +6709,10 @@
       <c r="A201" t="s">
         <v>207</v>
       </c>
-      <c r="B201">
+      <c r="B201" s="1">
         <v>2100</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="1">
         <v>3000</v>
       </c>
       <c r="D201">
@@ -6725,10 +6732,10 @@
       <c r="A202" t="s">
         <v>208</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="1">
         <v>2220</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="1">
         <v>3000</v>
       </c>
       <c r="D202">
@@ -6748,10 +6755,10 @@
       <c r="A203" t="s">
         <v>209</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="1">
         <v>5900</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="1">
         <v>7500</v>
       </c>
       <c r="D203">
@@ -6771,10 +6778,10 @@
       <c r="A204" t="s">
         <v>210</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="1">
         <v>7250</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="1">
         <v>9000</v>
       </c>
       <c r="D204">
@@ -6794,10 +6801,10 @@
       <c r="A205" t="s">
         <v>211</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="1">
         <v>13975</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="1">
         <v>17000</v>
       </c>
       <c r="D205">
@@ -6817,10 +6824,10 @@
       <c r="A206" t="s">
         <v>212</v>
       </c>
-      <c r="B206">
+      <c r="B206" s="1">
         <v>2230</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="1">
         <v>3000</v>
       </c>
       <c r="D206">
@@ -6840,10 +6847,10 @@
       <c r="A207" t="s">
         <v>213</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="1">
         <v>2170</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="1">
         <v>3000</v>
       </c>
       <c r="D207">
@@ -6863,10 +6870,10 @@
       <c r="A208" t="s">
         <v>214</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="1">
         <v>2280</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="1">
         <v>3000</v>
       </c>
       <c r="D208">
@@ -6886,10 +6893,10 @@
       <c r="A209" t="s">
         <v>215</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="1">
         <v>960</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="1">
         <v>1300</v>
       </c>
       <c r="D209">
@@ -6909,10 +6916,10 @@
       <c r="A210" t="s">
         <v>216</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="1">
         <v>380</v>
       </c>
-      <c r="C210">
+      <c r="C210" s="1">
         <v>800</v>
       </c>
       <c r="D210">
@@ -6932,10 +6939,10 @@
       <c r="A211" t="s">
         <v>217</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="1">
         <v>490</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="1">
         <v>1000</v>
       </c>
       <c r="D211">
@@ -6955,10 +6962,10 @@
       <c r="A212" t="s">
         <v>218</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="1">
         <v>1850</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="1">
         <v>2500</v>
       </c>
       <c r="D212">
@@ -6978,10 +6985,10 @@
       <c r="A213" t="s">
         <v>219</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="1">
         <v>1440</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="1">
         <v>2000</v>
       </c>
       <c r="D213">
@@ -7001,10 +7008,10 @@
       <c r="A214" t="s">
         <v>220</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="1">
         <v>2600</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="1">
         <v>3500</v>
       </c>
       <c r="D214">
@@ -7024,10 +7031,10 @@
       <c r="A215" t="s">
         <v>221</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="1">
         <v>5650</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="1">
         <v>7000</v>
       </c>
       <c r="D215">
@@ -7047,10 +7054,10 @@
       <c r="A216" t="s">
         <v>222</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="1">
         <v>430</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="1">
         <v>600</v>
       </c>
       <c r="D216">
@@ -7070,10 +7077,10 @@
       <c r="A217" t="s">
         <v>223</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="1">
         <v>750</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="1">
         <v>1000</v>
       </c>
       <c r="D217">
@@ -7093,10 +7100,10 @@
       <c r="A218" t="s">
         <v>224</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="1">
         <v>12500</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="1">
         <v>20000</v>
       </c>
       <c r="D218">
@@ -7116,10 +7123,10 @@
       <c r="A219" t="s">
         <v>225</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="1">
         <v>4830</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="1">
         <v>6000</v>
       </c>
       <c r="D219">
@@ -7139,10 +7146,10 @@
       <c r="A220" t="s">
         <v>226</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="1">
         <v>4830</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="1">
         <v>6000</v>
       </c>
       <c r="D220">
@@ -7162,10 +7169,10 @@
       <c r="A221" t="s">
         <v>227</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="1">
         <v>8890</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="1">
         <v>11000</v>
       </c>
       <c r="D221">
@@ -7185,10 +7192,10 @@
       <c r="A222" t="s">
         <v>228</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="1">
         <v>2700</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="1">
         <v>3500</v>
       </c>
       <c r="D222">
@@ -7208,10 +7215,10 @@
       <c r="A223" t="s">
         <v>229</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="1">
         <v>5600</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="1">
         <v>7000</v>
       </c>
       <c r="D223">
@@ -7231,10 +7238,10 @@
       <c r="A224" t="s">
         <v>230</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="1">
         <v>5600</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="1">
         <v>7000</v>
       </c>
       <c r="D224">
@@ -7254,10 +7261,10 @@
       <c r="A225" t="s">
         <v>231</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="1">
         <v>5600</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="1">
         <v>7000</v>
       </c>
       <c r="D225">
@@ -7277,10 +7284,10 @@
       <c r="A226" t="s">
         <v>232</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="1">
         <v>5600</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="1">
         <v>7000</v>
       </c>
       <c r="D226">
@@ -7300,10 +7307,10 @@
       <c r="A227" t="s">
         <v>233</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="1">
         <v>1960</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="1">
         <v>2500</v>
       </c>
       <c r="D227">
@@ -7323,10 +7330,10 @@
       <c r="A228" t="s">
         <v>234</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="1">
         <v>1170</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="1">
         <v>1500</v>
       </c>
       <c r="D228">
@@ -7346,10 +7353,10 @@
       <c r="A229" t="s">
         <v>235</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="1">
         <v>1170</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="1">
         <v>1500</v>
       </c>
       <c r="D229">
@@ -7369,10 +7376,10 @@
       <c r="A230" t="s">
         <v>236</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="1">
         <v>1170</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="1">
         <v>1500</v>
       </c>
       <c r="D230">
@@ -7392,10 +7399,10 @@
       <c r="A231" t="s">
         <v>237</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="1">
         <v>1170</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="1">
         <v>1500</v>
       </c>
       <c r="D231">
@@ -7415,10 +7422,10 @@
       <c r="A232" t="s">
         <v>238</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="1">
         <v>1170</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="1">
         <v>1500</v>
       </c>
       <c r="D232">
@@ -7438,10 +7445,10 @@
       <c r="A233" t="s">
         <v>239</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="1">
         <v>772</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="1">
         <v>1200</v>
       </c>
       <c r="D233">
@@ -7461,10 +7468,10 @@
       <c r="A234" t="s">
         <v>240</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="1">
         <v>650</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="1">
         <v>1000</v>
       </c>
       <c r="D234">
@@ -7484,10 +7491,10 @@
       <c r="A235" t="s">
         <v>241</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="1">
         <v>390</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="1">
         <v>600</v>
       </c>
       <c r="D235">
@@ -7507,10 +7514,10 @@
       <c r="A236" t="s">
         <v>242</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="1">
         <v>405</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="1">
         <v>600</v>
       </c>
       <c r="D236">
@@ -7530,10 +7537,10 @@
       <c r="A237" t="s">
         <v>243</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="1">
         <v>438</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="1">
         <v>800</v>
       </c>
       <c r="D237">
@@ -7553,10 +7560,10 @@
       <c r="A238" t="s">
         <v>244</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="1">
         <v>700</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="1">
         <v>1000</v>
       </c>
       <c r="D238">
@@ -7576,10 +7583,10 @@
       <c r="A239" t="s">
         <v>245</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="1">
         <v>2530</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="1">
         <v>3500</v>
       </c>
       <c r="D239">
@@ -7599,10 +7606,10 @@
       <c r="A240" t="s">
         <v>246</v>
       </c>
-      <c r="B240">
+      <c r="B240" s="1">
         <v>4900</v>
       </c>
-      <c r="C240">
+      <c r="C240" s="1">
         <v>6000</v>
       </c>
       <c r="D240">
@@ -7622,10 +7629,10 @@
       <c r="A241" t="s">
         <v>247</v>
       </c>
-      <c r="B241">
+      <c r="B241" s="1">
         <v>2950</v>
       </c>
-      <c r="C241">
+      <c r="C241" s="1">
         <v>4000</v>
       </c>
       <c r="D241">
@@ -7645,10 +7652,10 @@
       <c r="A242" t="s">
         <v>248</v>
       </c>
-      <c r="B242">
+      <c r="B242" s="1">
         <v>1440</v>
       </c>
-      <c r="C242">
+      <c r="C242" s="1">
         <v>2000</v>
       </c>
       <c r="D242">
@@ -7668,10 +7675,10 @@
       <c r="A243" t="s">
         <v>249</v>
       </c>
-      <c r="B243">
+      <c r="B243" s="1">
         <v>3500</v>
       </c>
-      <c r="C243">
+      <c r="C243" s="1">
         <v>5000</v>
       </c>
       <c r="D243">
@@ -7691,10 +7698,10 @@
       <c r="A244" t="s">
         <v>250</v>
       </c>
-      <c r="B244">
+      <c r="B244" s="1">
         <v>762</v>
       </c>
-      <c r="C244">
+      <c r="C244" s="1">
         <v>1500</v>
       </c>
       <c r="D244">
@@ -7714,10 +7721,10 @@
       <c r="A245" t="s">
         <v>251</v>
       </c>
-      <c r="B245">
+      <c r="B245" s="1">
         <v>1650</v>
       </c>
-      <c r="C245">
+      <c r="C245" s="1">
         <v>2200</v>
       </c>
       <c r="D245">
@@ -7737,10 +7744,10 @@
       <c r="A246" t="s">
         <v>252</v>
       </c>
-      <c r="B246">
+      <c r="B246" s="1">
         <v>709</v>
       </c>
-      <c r="C246">
+      <c r="C246" s="1">
         <v>1500</v>
       </c>
       <c r="D246">
@@ -7760,10 +7767,10 @@
       <c r="A247" t="s">
         <v>253</v>
       </c>
-      <c r="B247">
+      <c r="B247" s="1">
         <v>50600</v>
       </c>
-      <c r="C247">
+      <c r="C247" s="1">
         <v>70000</v>
       </c>
       <c r="D247">
@@ -7783,10 +7790,10 @@
       <c r="A248" t="s">
         <v>254</v>
       </c>
-      <c r="B248">
+      <c r="B248" s="1">
         <v>430</v>
       </c>
-      <c r="C248">
+      <c r="C248" s="1">
         <v>1000</v>
       </c>
       <c r="D248">
@@ -7806,10 +7813,10 @@
       <c r="A249" t="s">
         <v>255</v>
       </c>
-      <c r="B249">
+      <c r="B249" s="1">
         <v>1700</v>
       </c>
-      <c r="C249">
+      <c r="C249" s="1">
         <v>2500</v>
       </c>
       <c r="D249">
@@ -7829,10 +7836,10 @@
       <c r="A250" t="s">
         <v>256</v>
       </c>
-      <c r="B250">
+      <c r="B250" s="1">
         <v>1700</v>
       </c>
-      <c r="C250">
+      <c r="C250" s="1">
         <v>2500</v>
       </c>
       <c r="D250">
@@ -7852,10 +7859,10 @@
       <c r="A251" t="s">
         <v>258</v>
       </c>
-      <c r="B251">
+      <c r="B251" s="1">
         <v>740</v>
       </c>
-      <c r="C251">
+      <c r="C251" s="1">
         <v>2500</v>
       </c>
       <c r="D251">
@@ -7875,10 +7882,10 @@
       <c r="A252" t="s">
         <v>259</v>
       </c>
-      <c r="B252">
+      <c r="B252" s="1">
         <v>740</v>
       </c>
-      <c r="C252">
+      <c r="C252" s="1">
         <v>2500</v>
       </c>
       <c r="D252">
@@ -7898,10 +7905,10 @@
       <c r="A253" t="s">
         <v>260</v>
       </c>
-      <c r="B253">
+      <c r="B253" s="1">
         <v>740</v>
       </c>
-      <c r="C253">
+      <c r="C253" s="1">
         <v>2500</v>
       </c>
       <c r="D253">
@@ -7921,10 +7928,10 @@
       <c r="A254" t="s">
         <v>261</v>
       </c>
-      <c r="B254">
+      <c r="B254" s="1">
         <v>7800</v>
       </c>
-      <c r="C254">
+      <c r="C254" s="1">
         <v>12000</v>
       </c>
       <c r="D254">
@@ -7944,10 +7951,10 @@
       <c r="A255" t="s">
         <v>262</v>
       </c>
-      <c r="B255">
+      <c r="B255" s="1">
         <v>5400</v>
       </c>
-      <c r="C255">
+      <c r="C255" s="1">
         <v>10000</v>
       </c>
       <c r="D255">
@@ -7967,10 +7974,10 @@
       <c r="A256" t="s">
         <v>263</v>
       </c>
-      <c r="B256">
+      <c r="B256" s="1">
         <v>1460</v>
       </c>
-      <c r="C256">
+      <c r="C256" s="1">
         <v>3500</v>
       </c>
       <c r="D256">
@@ -7990,10 +7997,10 @@
       <c r="A257" t="s">
         <v>264</v>
       </c>
-      <c r="B257">
+      <c r="B257" s="1">
         <v>7800</v>
       </c>
-      <c r="C257">
+      <c r="C257" s="1">
         <v>12000</v>
       </c>
       <c r="D257">
@@ -8013,10 +8020,10 @@
       <c r="A258" t="s">
         <v>265</v>
       </c>
-      <c r="B258">
+      <c r="B258" s="1">
         <v>5400</v>
       </c>
-      <c r="C258">
+      <c r="C258" s="1">
         <v>10000</v>
       </c>
       <c r="D258">
@@ -8036,10 +8043,10 @@
       <c r="A259" t="s">
         <v>266</v>
       </c>
-      <c r="B259">
+      <c r="B259" s="1">
         <v>1460</v>
       </c>
-      <c r="C259">
+      <c r="C259" s="1">
         <v>3500</v>
       </c>
       <c r="D259">
@@ -8059,10 +8066,10 @@
       <c r="A260" t="s">
         <v>267</v>
       </c>
-      <c r="B260">
+      <c r="B260" s="1">
         <v>1380</v>
       </c>
-      <c r="C260">
+      <c r="C260" s="1">
         <v>2000</v>
       </c>
       <c r="D260">
@@ -8082,10 +8089,10 @@
       <c r="A261" t="s">
         <v>268</v>
       </c>
-      <c r="B261">
+      <c r="B261" s="1">
         <v>1380</v>
       </c>
-      <c r="C261">
+      <c r="C261" s="1">
         <v>2000</v>
       </c>
       <c r="D261">
@@ -8105,10 +8112,10 @@
       <c r="A262" t="s">
         <v>269</v>
       </c>
-      <c r="B262">
+      <c r="B262" s="1">
         <v>1380</v>
       </c>
-      <c r="C262">
+      <c r="C262" s="1">
         <v>2000</v>
       </c>
       <c r="D262">
@@ -8128,10 +8135,10 @@
       <c r="A263" t="s">
         <v>270</v>
       </c>
-      <c r="B263">
+      <c r="B263" s="1">
         <v>3780</v>
       </c>
-      <c r="C263">
+      <c r="C263" s="1">
         <v>5000</v>
       </c>
       <c r="D263">
@@ -8151,10 +8158,10 @@
       <c r="A264" t="s">
         <v>271</v>
       </c>
-      <c r="B264">
+      <c r="B264" s="1">
         <v>9600</v>
       </c>
-      <c r="C264">
+      <c r="C264" s="1">
         <v>15000</v>
       </c>
       <c r="D264">
@@ -8174,10 +8181,10 @@
       <c r="A265" t="s">
         <v>272</v>
       </c>
-      <c r="B265">
+      <c r="B265" s="1">
         <v>1890</v>
       </c>
-      <c r="C265">
+      <c r="C265" s="1">
         <v>4000</v>
       </c>
       <c r="D265">
@@ -8197,10 +8204,10 @@
       <c r="A266" t="s">
         <v>273</v>
       </c>
-      <c r="B266">
+      <c r="B266" s="1">
         <v>1550</v>
       </c>
-      <c r="C266">
+      <c r="C266" s="1">
         <v>3500</v>
       </c>
       <c r="D266">
@@ -8220,10 +8227,10 @@
       <c r="A267" t="s">
         <v>274</v>
       </c>
-      <c r="B267">
+      <c r="B267" s="1">
         <v>1550</v>
       </c>
-      <c r="C267">
+      <c r="C267" s="1">
         <v>3500</v>
       </c>
       <c r="D267">
@@ -8243,10 +8250,10 @@
       <c r="A268" t="s">
         <v>275</v>
       </c>
-      <c r="B268">
+      <c r="B268" s="1">
         <v>1550</v>
       </c>
-      <c r="C268">
+      <c r="C268" s="1">
         <v>3500</v>
       </c>
       <c r="D268">
@@ -8266,10 +8273,10 @@
       <c r="A269" t="s">
         <v>276</v>
       </c>
-      <c r="B269">
+      <c r="B269" s="1">
         <v>1550</v>
       </c>
-      <c r="C269">
+      <c r="C269" s="1">
         <v>3500</v>
       </c>
       <c r="D269">
@@ -8289,10 +8296,10 @@
       <c r="A270" t="s">
         <v>277</v>
       </c>
-      <c r="B270">
+      <c r="B270" s="1">
         <v>5800</v>
       </c>
-      <c r="C270">
+      <c r="C270" s="1">
         <v>10000</v>
       </c>
       <c r="D270">
@@ -8312,10 +8319,10 @@
       <c r="A271" t="s">
         <v>278</v>
       </c>
-      <c r="B271">
+      <c r="B271" s="1">
         <v>5800</v>
       </c>
-      <c r="C271">
+      <c r="C271" s="1">
         <v>10000</v>
       </c>
       <c r="D271">
@@ -8335,10 +8342,10 @@
       <c r="A272" t="s">
         <v>279</v>
       </c>
-      <c r="B272">
+      <c r="B272" s="1">
         <v>5800</v>
       </c>
-      <c r="C272">
+      <c r="C272" s="1">
         <v>10000</v>
       </c>
       <c r="D272">
@@ -8358,10 +8365,10 @@
       <c r="A273" t="s">
         <v>280</v>
       </c>
-      <c r="B273">
+      <c r="B273" s="1">
         <v>5800</v>
       </c>
-      <c r="C273">
+      <c r="C273" s="1">
         <v>10000</v>
       </c>
       <c r="D273">
@@ -8381,10 +8388,10 @@
       <c r="A274" t="s">
         <v>281</v>
       </c>
-      <c r="B274">
+      <c r="B274" s="1">
         <v>5800</v>
       </c>
-      <c r="C274">
+      <c r="C274" s="1">
         <v>10000</v>
       </c>
       <c r="D274">
@@ -8404,10 +8411,10 @@
       <c r="A275" t="s">
         <v>282</v>
       </c>
-      <c r="B275">
+      <c r="B275" s="1">
         <v>5800</v>
       </c>
-      <c r="C275">
+      <c r="C275" s="1">
         <v>10000</v>
       </c>
       <c r="D275">
@@ -8427,10 +8434,10 @@
       <c r="A276" t="s">
         <v>283</v>
       </c>
-      <c r="B276">
+      <c r="B276" s="1">
         <v>5800</v>
       </c>
-      <c r="C276">
+      <c r="C276" s="1">
         <v>10000</v>
       </c>
       <c r="D276">
@@ -8450,10 +8457,10 @@
       <c r="A277" t="s">
         <v>284</v>
       </c>
-      <c r="B277">
+      <c r="B277" s="1">
         <v>5800</v>
       </c>
-      <c r="C277">
+      <c r="C277" s="1">
         <v>10000</v>
       </c>
       <c r="D277">
@@ -8473,10 +8480,10 @@
       <c r="A278" t="s">
         <v>285</v>
       </c>
-      <c r="B278">
+      <c r="B278" s="1">
         <v>5800</v>
       </c>
-      <c r="C278">
+      <c r="C278" s="1">
         <v>10000</v>
       </c>
       <c r="D278">
@@ -8496,10 +8503,10 @@
       <c r="A279" t="s">
         <v>286</v>
       </c>
-      <c r="B279">
+      <c r="B279" s="1">
         <v>5800</v>
       </c>
-      <c r="C279">
+      <c r="C279" s="1">
         <v>10000</v>
       </c>
       <c r="D279">
@@ -8519,10 +8526,10 @@
       <c r="A280" t="s">
         <v>287</v>
       </c>
-      <c r="B280">
+      <c r="B280" s="1">
         <v>4000</v>
       </c>
-      <c r="C280">
+      <c r="C280" s="1">
         <v>7000</v>
       </c>
       <c r="D280">
@@ -8542,10 +8549,10 @@
       <c r="A281" t="s">
         <v>288</v>
       </c>
-      <c r="B281">
+      <c r="B281" s="1">
         <v>4000</v>
       </c>
-      <c r="C281">
+      <c r="C281" s="1">
         <v>7000</v>
       </c>
       <c r="D281">
@@ -8565,10 +8572,10 @@
       <c r="A282" t="s">
         <v>289</v>
       </c>
-      <c r="B282">
+      <c r="B282" s="1">
         <v>1980</v>
       </c>
-      <c r="C282">
+      <c r="C282" s="1">
         <v>4000</v>
       </c>
       <c r="D282">
@@ -8588,10 +8595,10 @@
       <c r="A283" t="s">
         <v>290</v>
       </c>
-      <c r="B283">
+      <c r="B283" s="1">
         <v>380</v>
       </c>
-      <c r="C283">
+      <c r="C283" s="1">
         <v>2000</v>
       </c>
       <c r="D283">
@@ -8611,10 +8618,10 @@
       <c r="A284" t="s">
         <v>291</v>
       </c>
-      <c r="B284">
+      <c r="B284" s="1">
         <v>300</v>
       </c>
-      <c r="C284">
+      <c r="C284" s="1">
         <v>1500</v>
       </c>
       <c r="D284">
@@ -8634,10 +8641,10 @@
       <c r="A285" t="s">
         <v>292</v>
       </c>
-      <c r="B285">
+      <c r="B285" s="1">
         <v>4700</v>
       </c>
-      <c r="C285">
+      <c r="C285" s="1">
         <v>7000</v>
       </c>
       <c r="D285">
@@ -8657,10 +8664,10 @@
       <c r="A286" t="s">
         <v>293</v>
       </c>
-      <c r="B286">
+      <c r="B286" s="1">
         <v>960</v>
       </c>
-      <c r="C286">
+      <c r="C286" s="1">
         <v>2000</v>
       </c>
       <c r="D286">
@@ -8680,10 +8687,10 @@
       <c r="A287" t="s">
         <v>294</v>
       </c>
-      <c r="B287">
+      <c r="B287" s="1">
         <v>1800</v>
       </c>
-      <c r="C287">
+      <c r="C287" s="1">
         <v>4000</v>
       </c>
       <c r="D287">
@@ -8703,10 +8710,10 @@
       <c r="A288" t="s">
         <v>295</v>
       </c>
-      <c r="B288">
+      <c r="B288" s="1">
         <v>5800</v>
       </c>
-      <c r="C288">
+      <c r="C288" s="1">
         <v>10000</v>
       </c>
       <c r="D288">
@@ -8726,10 +8733,10 @@
       <c r="A289" t="s">
         <v>296</v>
       </c>
-      <c r="B289">
+      <c r="B289" s="1">
         <v>5800</v>
       </c>
-      <c r="C289">
+      <c r="C289" s="1">
         <v>10000</v>
       </c>
       <c r="D289">
@@ -8749,10 +8756,10 @@
       <c r="A290" t="s">
         <v>297</v>
       </c>
-      <c r="B290">
+      <c r="B290" s="1">
         <v>4500</v>
       </c>
-      <c r="C290">
+      <c r="C290" s="1">
         <v>6500</v>
       </c>
       <c r="D290">
@@ -8772,10 +8779,10 @@
       <c r="A291" t="s">
         <v>298</v>
       </c>
-      <c r="B291">
+      <c r="B291" s="1">
         <v>720</v>
       </c>
-      <c r="C291">
+      <c r="C291" s="1">
         <v>1500</v>
       </c>
       <c r="D291">
@@ -8795,10 +8802,10 @@
       <c r="A292" t="s">
         <v>299</v>
       </c>
-      <c r="B292">
+      <c r="B292" s="1">
         <v>980</v>
       </c>
-      <c r="C292">
+      <c r="C292" s="1">
         <v>2000</v>
       </c>
       <c r="D292">
@@ -8818,10 +8825,10 @@
       <c r="A293" t="s">
         <v>300</v>
       </c>
-      <c r="B293">
+      <c r="B293" s="1">
         <v>1100</v>
       </c>
-      <c r="C293">
+      <c r="C293" s="1">
         <v>2500</v>
       </c>
       <c r="D293">
@@ -8841,10 +8848,10 @@
       <c r="A294" t="s">
         <v>301</v>
       </c>
-      <c r="B294">
+      <c r="B294" s="1">
         <v>1600</v>
       </c>
-      <c r="C294">
+      <c r="C294" s="1">
         <v>2500</v>
       </c>
       <c r="D294">
@@ -8864,10 +8871,10 @@
       <c r="A295" t="s">
         <v>302</v>
       </c>
-      <c r="B295">
+      <c r="B295" s="1">
         <v>2400</v>
       </c>
-      <c r="C295">
+      <c r="C295" s="1">
         <v>3500</v>
       </c>
       <c r="D295">
@@ -8887,10 +8894,10 @@
       <c r="A296" t="s">
         <v>303</v>
       </c>
-      <c r="B296">
+      <c r="B296" s="1">
         <v>2400</v>
       </c>
-      <c r="C296">
+      <c r="C296" s="1">
         <v>3500</v>
       </c>
       <c r="D296">
@@ -8910,10 +8917,10 @@
       <c r="A297" t="s">
         <v>304</v>
       </c>
-      <c r="B297">
+      <c r="B297" s="1">
         <v>3900</v>
       </c>
-      <c r="C297">
+      <c r="C297" s="1">
         <v>8000</v>
       </c>
       <c r="D297">
@@ -8933,10 +8940,10 @@
       <c r="A298" t="s">
         <v>305</v>
       </c>
-      <c r="B298">
+      <c r="B298" s="1">
         <v>3900</v>
       </c>
-      <c r="C298">
+      <c r="C298" s="1">
         <v>8000</v>
       </c>
       <c r="D298">
@@ -8956,10 +8963,10 @@
       <c r="A299" t="s">
         <v>306</v>
       </c>
-      <c r="B299">
+      <c r="B299" s="1">
         <v>3900</v>
       </c>
-      <c r="C299">
+      <c r="C299" s="1">
         <v>8000</v>
       </c>
       <c r="D299">
@@ -8979,10 +8986,10 @@
       <c r="A300" t="s">
         <v>307</v>
       </c>
-      <c r="B300">
+      <c r="B300" s="1">
         <v>3900</v>
       </c>
-      <c r="C300">
+      <c r="C300" s="1">
         <v>8000</v>
       </c>
       <c r="D300">
@@ -9002,10 +9009,10 @@
       <c r="A301" t="s">
         <v>308</v>
       </c>
-      <c r="B301">
+      <c r="B301" s="1">
         <v>3900</v>
       </c>
-      <c r="C301">
+      <c r="C301" s="1">
         <v>8000</v>
       </c>
       <c r="D301">
@@ -9025,10 +9032,10 @@
       <c r="A302" t="s">
         <v>309</v>
       </c>
-      <c r="B302">
+      <c r="B302" s="1">
         <v>1100</v>
       </c>
-      <c r="C302">
+      <c r="C302" s="1">
         <v>3000</v>
       </c>
       <c r="D302">
@@ -9048,10 +9055,10 @@
       <c r="A303" t="s">
         <v>310</v>
       </c>
-      <c r="B303">
+      <c r="B303" s="1">
         <v>3900</v>
       </c>
-      <c r="C303">
+      <c r="C303" s="1">
         <v>8000</v>
       </c>
       <c r="D303">
@@ -9071,10 +9078,10 @@
       <c r="A304" t="s">
         <v>311</v>
       </c>
-      <c r="B304">
+      <c r="B304" s="1">
         <v>3900</v>
       </c>
-      <c r="C304">
+      <c r="C304" s="1">
         <v>8000</v>
       </c>
       <c r="D304">
@@ -9094,10 +9101,10 @@
       <c r="A305" t="s">
         <v>312</v>
       </c>
-      <c r="B305">
+      <c r="B305" s="1">
         <v>3900</v>
       </c>
-      <c r="C305">
+      <c r="C305" s="1">
         <v>8000</v>
       </c>
       <c r="D305">
@@ -9117,10 +9124,10 @@
       <c r="A306" t="s">
         <v>313</v>
       </c>
-      <c r="B306">
+      <c r="B306" s="1">
         <v>3900</v>
       </c>
-      <c r="C306">
+      <c r="C306" s="1">
         <v>8000</v>
       </c>
       <c r="D306">
@@ -9140,10 +9147,10 @@
       <c r="A307" t="s">
         <v>314</v>
       </c>
-      <c r="B307">
+      <c r="B307" s="1">
         <v>3900</v>
       </c>
-      <c r="C307">
+      <c r="C307" s="1">
         <v>8000</v>
       </c>
       <c r="D307">
@@ -9163,10 +9170,10 @@
       <c r="A308" t="s">
         <v>315</v>
       </c>
-      <c r="B308">
+      <c r="B308" s="1">
         <v>1100</v>
       </c>
-      <c r="C308">
+      <c r="C308" s="1">
         <v>3000</v>
       </c>
       <c r="D308">
@@ -9186,10 +9193,10 @@
       <c r="A309" t="s">
         <v>316</v>
       </c>
-      <c r="B309">
+      <c r="B309" s="1">
         <v>640</v>
       </c>
-      <c r="C309">
+      <c r="C309" s="1">
         <v>1000</v>
       </c>
       <c r="D309">
@@ -9209,10 +9216,10 @@
       <c r="A310" t="s">
         <v>317</v>
       </c>
-      <c r="B310">
+      <c r="B310" s="1">
         <v>1700</v>
       </c>
-      <c r="C310">
+      <c r="C310" s="1">
         <v>4000</v>
       </c>
       <c r="D310">
@@ -9232,10 +9239,10 @@
       <c r="A311" t="s">
         <v>318</v>
       </c>
-      <c r="B311">
+      <c r="B311" s="1">
         <v>1700</v>
       </c>
-      <c r="C311">
+      <c r="C311" s="1">
         <v>4000</v>
       </c>
       <c r="D311">
@@ -9255,10 +9262,10 @@
       <c r="A312" t="s">
         <v>319</v>
       </c>
-      <c r="B312">
+      <c r="B312" s="1">
         <v>1700</v>
       </c>
-      <c r="C312">
+      <c r="C312" s="1">
         <v>4000</v>
       </c>
       <c r="D312">
@@ -9278,10 +9285,10 @@
       <c r="A313" t="s">
         <v>320</v>
       </c>
-      <c r="B313">
+      <c r="B313" s="1">
         <v>1860</v>
       </c>
-      <c r="C313">
+      <c r="C313" s="1">
         <v>4500</v>
       </c>
       <c r="D313">
@@ -9301,10 +9308,10 @@
       <c r="A314" t="s">
         <v>321</v>
       </c>
-      <c r="B314">
+      <c r="B314" s="1">
         <v>1860</v>
       </c>
-      <c r="C314">
+      <c r="C314" s="1">
         <v>4500</v>
       </c>
       <c r="D314">
@@ -9324,10 +9331,10 @@
       <c r="A315" t="s">
         <v>322</v>
       </c>
-      <c r="B315">
+      <c r="B315" s="1">
         <v>1860</v>
       </c>
-      <c r="C315">
+      <c r="C315" s="1">
         <v>4500</v>
       </c>
       <c r="D315">
@@ -9347,10 +9354,10 @@
       <c r="A316" t="s">
         <v>323</v>
       </c>
-      <c r="B316">
+      <c r="B316" s="1">
         <v>1860</v>
       </c>
-      <c r="C316">
+      <c r="C316" s="1">
         <v>4500</v>
       </c>
       <c r="D316">
@@ -9370,10 +9377,10 @@
       <c r="A317" t="s">
         <v>324</v>
       </c>
-      <c r="B317">
+      <c r="B317" s="1">
         <v>1860</v>
       </c>
-      <c r="C317">
+      <c r="C317" s="1">
         <v>4500</v>
       </c>
       <c r="D317">
@@ -9393,10 +9400,10 @@
       <c r="A318" t="s">
         <v>325</v>
       </c>
-      <c r="B318">
+      <c r="B318" s="1">
         <v>1700</v>
       </c>
-      <c r="C318">
+      <c r="C318" s="1">
         <v>3000</v>
       </c>
       <c r="D318">
@@ -9416,10 +9423,10 @@
       <c r="A319" t="s">
         <v>326</v>
       </c>
-      <c r="B319">
+      <c r="B319" s="1">
         <v>64</v>
       </c>
-      <c r="C319">
+      <c r="C319" s="1">
         <v>200</v>
       </c>
       <c r="D319">
@@ -9439,10 +9446,10 @@
       <c r="A320" t="s">
         <v>327</v>
       </c>
-      <c r="B320">
+      <c r="B320" s="1">
         <v>1100</v>
       </c>
-      <c r="C320">
+      <c r="C320" s="1">
         <v>2000</v>
       </c>
       <c r="D320">
@@ -9462,10 +9469,10 @@
       <c r="A321" t="s">
         <v>328</v>
       </c>
-      <c r="B321">
+      <c r="B321" s="1">
         <v>1100</v>
       </c>
-      <c r="C321">
+      <c r="C321" s="1">
         <v>2000</v>
       </c>
       <c r="D321">
@@ -9485,10 +9492,10 @@
       <c r="A322" t="s">
         <v>329</v>
       </c>
-      <c r="B322">
+      <c r="B322" s="1">
         <v>18000</v>
       </c>
-      <c r="C322">
+      <c r="C322" s="1">
         <v>25000</v>
       </c>
       <c r="D322">
@@ -9508,10 +9515,10 @@
       <c r="A323" t="s">
         <v>330</v>
       </c>
-      <c r="B323">
+      <c r="B323" s="1">
         <v>1980</v>
       </c>
-      <c r="C323">
+      <c r="C323" s="1">
         <v>4000</v>
       </c>
       <c r="D323">
@@ -9531,10 +9538,10 @@
       <c r="A324" t="s">
         <v>331</v>
       </c>
-      <c r="B324">
+      <c r="B324" s="1">
         <v>400</v>
       </c>
-      <c r="C324">
+      <c r="C324" s="1">
         <v>1000</v>
       </c>
       <c r="D324">
@@ -9554,10 +9561,10 @@
       <c r="A325" t="s">
         <v>332</v>
       </c>
-      <c r="B325">
+      <c r="B325" s="1">
         <v>840</v>
       </c>
-      <c r="C325">
+      <c r="C325" s="1">
         <v>1500</v>
       </c>
       <c r="D325">
@@ -9577,10 +9584,10 @@
       <c r="A326" t="s">
         <v>333</v>
       </c>
-      <c r="B326">
+      <c r="B326" s="1">
         <v>1300</v>
       </c>
-      <c r="C326">
+      <c r="C326" s="1">
         <v>2500</v>
       </c>
       <c r="D326">
@@ -9600,10 +9607,10 @@
       <c r="A327" t="s">
         <v>334</v>
       </c>
-      <c r="B327">
+      <c r="B327" s="1">
         <v>3900</v>
       </c>
-      <c r="C327">
+      <c r="C327" s="1">
         <v>8000</v>
       </c>
       <c r="D327">
@@ -9623,10 +9630,10 @@
       <c r="A328" t="s">
         <v>335</v>
       </c>
-      <c r="B328">
+      <c r="B328" s="1">
         <v>3900</v>
       </c>
-      <c r="C328">
+      <c r="C328" s="1">
         <v>8000</v>
       </c>
       <c r="D328">
@@ -9646,10 +9653,10 @@
       <c r="A329" t="s">
         <v>336</v>
       </c>
-      <c r="B329">
+      <c r="B329" s="1">
         <v>1100</v>
       </c>
-      <c r="C329">
+      <c r="C329" s="1">
         <v>3000</v>
       </c>
       <c r="D329">
@@ -9669,10 +9676,10 @@
       <c r="A330" t="s">
         <v>337</v>
       </c>
-      <c r="B330">
+      <c r="B330" s="1">
         <v>1100</v>
       </c>
-      <c r="C330">
+      <c r="C330" s="1">
         <v>3000</v>
       </c>
       <c r="D330">
@@ -9692,10 +9699,10 @@
       <c r="A331" t="s">
         <v>338</v>
       </c>
-      <c r="B331">
+      <c r="B331" s="1">
         <v>1100</v>
       </c>
-      <c r="C331">
+      <c r="C331" s="1">
         <v>3000</v>
       </c>
       <c r="D331">
@@ -9715,10 +9722,10 @@
       <c r="A332" t="s">
         <v>339</v>
       </c>
-      <c r="B332">
+      <c r="B332" s="1">
         <v>1100</v>
       </c>
-      <c r="C332">
+      <c r="C332" s="1">
         <v>3000</v>
       </c>
       <c r="D332">
@@ -9738,10 +9745,10 @@
       <c r="A333" t="s">
         <v>340</v>
       </c>
-      <c r="B333">
+      <c r="B333" s="1">
         <v>1100</v>
       </c>
-      <c r="C333">
+      <c r="C333" s="1">
         <v>3000</v>
       </c>
       <c r="D333">
@@ -9761,10 +9768,10 @@
       <c r="A334" t="s">
         <v>341</v>
       </c>
-      <c r="B334">
+      <c r="B334" s="1">
         <v>1100</v>
       </c>
-      <c r="C334">
+      <c r="C334" s="1">
         <v>3000</v>
       </c>
       <c r="D334">
@@ -9784,10 +9791,10 @@
       <c r="A335" t="s">
         <v>342</v>
       </c>
-      <c r="B335">
+      <c r="B335" s="1">
         <v>1100</v>
       </c>
-      <c r="C335">
+      <c r="C335" s="1">
         <v>3000</v>
       </c>
       <c r="D335">
@@ -9807,10 +9814,10 @@
       <c r="A336" t="s">
         <v>343</v>
       </c>
-      <c r="B336">
+      <c r="B336" s="1">
         <v>1100</v>
       </c>
-      <c r="C336">
+      <c r="C336" s="1">
         <v>3000</v>
       </c>
       <c r="D336">
@@ -9830,10 +9837,10 @@
       <c r="A337" t="s">
         <v>344</v>
       </c>
-      <c r="B337">
+      <c r="B337" s="1">
         <v>1100</v>
       </c>
-      <c r="C337">
+      <c r="C337" s="1">
         <v>3000</v>
       </c>
       <c r="D337">
@@ -9853,10 +9860,10 @@
       <c r="A338" t="s">
         <v>345</v>
       </c>
-      <c r="B338">
+      <c r="B338" s="1">
         <v>1100</v>
       </c>
-      <c r="C338">
+      <c r="C338" s="1">
         <v>3000</v>
       </c>
       <c r="D338">
@@ -9876,10 +9883,10 @@
       <c r="A339" t="s">
         <v>346</v>
       </c>
-      <c r="B339">
+      <c r="B339" s="1">
         <v>1100</v>
       </c>
-      <c r="C339">
+      <c r="C339" s="1">
         <v>3000</v>
       </c>
       <c r="D339">
@@ -9899,10 +9906,10 @@
       <c r="A340" t="s">
         <v>347</v>
       </c>
-      <c r="B340">
+      <c r="B340" s="1">
         <v>1550</v>
       </c>
-      <c r="C340">
+      <c r="C340" s="1">
         <v>3500</v>
       </c>
       <c r="D340">
@@ -9922,10 +9929,10 @@
       <c r="A341" t="s">
         <v>348</v>
       </c>
-      <c r="B341">
+      <c r="B341" s="1">
         <v>15400</v>
       </c>
-      <c r="C341">
+      <c r="C341" s="1">
         <v>20000</v>
       </c>
       <c r="D341">
@@ -9945,10 +9952,10 @@
       <c r="A342" t="s">
         <v>349</v>
       </c>
-      <c r="B342">
+      <c r="B342" s="1">
         <v>15600</v>
       </c>
-      <c r="C342">
+      <c r="C342" s="1">
         <v>20000</v>
       </c>
       <c r="D342">
@@ -9968,10 +9975,10 @@
       <c r="A343" t="s">
         <v>350</v>
       </c>
-      <c r="B343">
+      <c r="B343" s="1">
         <v>700</v>
       </c>
-      <c r="C343">
+      <c r="C343" s="1">
         <v>3000</v>
       </c>
       <c r="D343">
@@ -9991,10 +9998,10 @@
       <c r="A344" t="s">
         <v>351</v>
       </c>
-      <c r="B344">
+      <c r="B344" s="1">
         <v>1260</v>
       </c>
-      <c r="C344">
+      <c r="C344" s="1">
         <v>2500</v>
       </c>
       <c r="D344">
@@ -10014,10 +10021,10 @@
       <c r="A345" t="s">
         <v>352</v>
       </c>
-      <c r="B345">
+      <c r="B345" s="1">
         <v>1260</v>
       </c>
-      <c r="C345">
+      <c r="C345" s="1">
         <v>2500</v>
       </c>
       <c r="D345">
@@ -10037,10 +10044,10 @@
       <c r="A346" t="s">
         <v>353</v>
       </c>
-      <c r="B346">
+      <c r="B346" s="1">
         <v>2480</v>
       </c>
-      <c r="C346">
+      <c r="C346" s="1">
         <v>4500</v>
       </c>
       <c r="D346">
@@ -10060,10 +10067,10 @@
       <c r="A347" t="s">
         <v>354</v>
       </c>
-      <c r="B347">
+      <c r="B347" s="1">
         <v>8800</v>
       </c>
-      <c r="C347">
+      <c r="C347" s="1">
         <v>21000</v>
       </c>
       <c r="D347">
@@ -10083,10 +10090,10 @@
       <c r="A348" t="s">
         <v>355</v>
       </c>
-      <c r="B348">
+      <c r="B348" s="1">
         <v>8800</v>
       </c>
-      <c r="C348">
+      <c r="C348" s="1">
         <v>21000</v>
       </c>
       <c r="D348">
@@ -10106,10 +10113,10 @@
       <c r="A349" t="s">
         <v>356</v>
       </c>
-      <c r="B349">
+      <c r="B349" s="1">
         <v>8800</v>
       </c>
-      <c r="C349">
+      <c r="C349" s="1">
         <v>21000</v>
       </c>
       <c r="D349">
@@ -10129,10 +10136,10 @@
       <c r="A350" t="s">
         <v>357</v>
       </c>
-      <c r="B350">
+      <c r="B350" s="1">
         <v>8800</v>
       </c>
-      <c r="C350">
+      <c r="C350" s="1">
         <v>21000</v>
       </c>
       <c r="D350">
@@ -10152,10 +10159,10 @@
       <c r="A351" t="s">
         <v>358</v>
       </c>
-      <c r="B351">
+      <c r="B351" s="1">
         <v>8800</v>
       </c>
-      <c r="C351">
+      <c r="C351" s="1">
         <v>21000</v>
       </c>
       <c r="D351">
@@ -10175,10 +10182,10 @@
       <c r="A352" t="s">
         <v>359</v>
       </c>
-      <c r="B352">
+      <c r="B352" s="1">
         <v>7600</v>
       </c>
-      <c r="C352">
+      <c r="C352" s="1">
         <v>22500</v>
       </c>
       <c r="D352">
@@ -10198,10 +10205,10 @@
       <c r="A353" t="s">
         <v>360</v>
       </c>
-      <c r="B353">
+      <c r="B353" s="1">
         <v>7600</v>
       </c>
-      <c r="C353">
+      <c r="C353" s="1">
         <v>22500</v>
       </c>
       <c r="D353">
@@ -10221,10 +10228,10 @@
       <c r="A354" t="s">
         <v>361</v>
       </c>
-      <c r="B354">
+      <c r="B354" s="1">
         <v>7600</v>
       </c>
-      <c r="C354">
+      <c r="C354" s="1">
         <v>22500</v>
       </c>
       <c r="D354">
@@ -10244,10 +10251,10 @@
       <c r="A355" t="s">
         <v>362</v>
       </c>
-      <c r="B355">
+      <c r="B355" s="1">
         <v>7600</v>
       </c>
-      <c r="C355">
+      <c r="C355" s="1">
         <v>22500</v>
       </c>
       <c r="D355">
@@ -10267,10 +10274,10 @@
       <c r="A356" t="s">
         <v>363</v>
       </c>
-      <c r="B356">
+      <c r="B356" s="1">
         <v>7600</v>
       </c>
-      <c r="C356">
+      <c r="C356" s="1">
         <v>22500</v>
       </c>
       <c r="D356">
@@ -10290,10 +10297,10 @@
       <c r="A357" t="s">
         <v>364</v>
       </c>
-      <c r="B357">
+      <c r="B357" s="1">
         <v>7600</v>
       </c>
-      <c r="C357">
+      <c r="C357" s="1">
         <v>22500</v>
       </c>
       <c r="D357">
@@ -10313,10 +10320,10 @@
       <c r="A358" t="s">
         <v>363</v>
       </c>
-      <c r="B358">
+      <c r="B358" s="1">
         <v>7600</v>
       </c>
-      <c r="C358">
+      <c r="C358" s="1">
         <v>22500</v>
       </c>
       <c r="D358">
@@ -10336,10 +10343,10 @@
       <c r="A359" t="s">
         <v>365</v>
       </c>
-      <c r="B359">
+      <c r="B359" s="1">
         <v>1200</v>
       </c>
-      <c r="C359">
+      <c r="C359" s="1">
         <v>2500</v>
       </c>
       <c r="D359">
@@ -10359,10 +10366,10 @@
       <c r="A360" t="s">
         <v>366</v>
       </c>
-      <c r="B360">
+      <c r="B360" s="1">
         <v>160</v>
       </c>
-      <c r="C360">
+      <c r="C360" s="1">
         <v>800</v>
       </c>
       <c r="D360">
@@ -10382,10 +10389,10 @@
       <c r="A361" t="s">
         <v>367</v>
       </c>
-      <c r="B361">
+      <c r="B361" s="1">
         <v>160</v>
       </c>
-      <c r="C361">
+      <c r="C361" s="1">
         <v>800</v>
       </c>
       <c r="D361">
@@ -10405,10 +10412,10 @@
       <c r="A362" t="s">
         <v>368</v>
       </c>
-      <c r="B362">
+      <c r="B362" s="1">
         <v>160</v>
       </c>
-      <c r="C362">
+      <c r="C362" s="1">
         <v>800</v>
       </c>
       <c r="D362">
@@ -10428,10 +10435,10 @@
       <c r="A363" t="s">
         <v>369</v>
       </c>
-      <c r="B363">
+      <c r="B363" s="1">
         <v>160</v>
       </c>
-      <c r="C363">
+      <c r="C363" s="1">
         <v>800</v>
       </c>
       <c r="D363">
@@ -10451,10 +10458,10 @@
       <c r="A364" t="s">
         <v>370</v>
       </c>
-      <c r="B364">
+      <c r="B364" s="1">
         <v>960</v>
       </c>
-      <c r="C364">
+      <c r="C364" s="1">
         <v>2000</v>
       </c>
       <c r="D364">
@@ -10474,10 +10481,10 @@
       <c r="A365" t="s">
         <v>371</v>
       </c>
-      <c r="B365">
+      <c r="B365" s="1">
         <v>2200</v>
       </c>
-      <c r="C365">
+      <c r="C365" s="1">
         <v>3000</v>
       </c>
       <c r="D365">
@@ -10497,10 +10504,10 @@
       <c r="A366" t="s">
         <v>372</v>
       </c>
-      <c r="B366">
+      <c r="B366" s="1">
         <v>2400</v>
       </c>
-      <c r="C366">
+      <c r="C366" s="1">
         <v>4000</v>
       </c>
       <c r="D366">
@@ -10520,10 +10527,10 @@
       <c r="A367" t="s">
         <v>373</v>
       </c>
-      <c r="B367">
+      <c r="B367" s="1">
         <v>1100</v>
       </c>
-      <c r="C367">
+      <c r="C367" s="1">
         <v>2500</v>
       </c>
       <c r="D367">
@@ -10543,10 +10550,10 @@
       <c r="A368" t="s">
         <v>374</v>
       </c>
-      <c r="B368">
+      <c r="B368" s="1">
         <v>1400</v>
       </c>
-      <c r="C368">
+      <c r="C368" s="1">
         <v>3000</v>
       </c>
       <c r="D368">
@@ -10566,10 +10573,10 @@
       <c r="A369" t="s">
         <v>375</v>
       </c>
-      <c r="B369">
+      <c r="B369" s="1">
         <v>2200</v>
       </c>
-      <c r="C369">
+      <c r="C369" s="1">
         <v>4000</v>
       </c>
       <c r="D369">
@@ -10589,10 +10596,10 @@
       <c r="A370" t="s">
         <v>376</v>
       </c>
-      <c r="B370">
+      <c r="B370" s="1">
         <v>880</v>
       </c>
-      <c r="C370">
+      <c r="C370" s="1">
         <v>2000</v>
       </c>
       <c r="D370">
@@ -10612,10 +10619,10 @@
       <c r="A371" t="s">
         <v>377</v>
       </c>
-      <c r="B371">
+      <c r="B371" s="1">
         <v>1300</v>
       </c>
-      <c r="C371">
+      <c r="C371" s="1">
         <v>3500</v>
       </c>
       <c r="D371">
@@ -10635,10 +10642,10 @@
       <c r="A372" t="s">
         <v>378</v>
       </c>
-      <c r="B372">
+      <c r="B372" s="1">
         <v>8300</v>
       </c>
-      <c r="C372">
+      <c r="C372" s="1">
         <v>12000</v>
       </c>
       <c r="D372">
@@ -10658,10 +10665,10 @@
       <c r="A373" t="s">
         <v>379</v>
       </c>
-      <c r="B373">
+      <c r="B373" s="1">
         <v>4560</v>
       </c>
-      <c r="C373">
+      <c r="C373" s="1">
         <v>8000</v>
       </c>
       <c r="D373">
@@ -10681,10 +10688,10 @@
       <c r="A374" t="s">
         <v>380</v>
       </c>
-      <c r="B374">
+      <c r="B374" s="1">
         <v>440</v>
       </c>
-      <c r="C374">
+      <c r="C374" s="1">
         <v>1500</v>
       </c>
       <c r="D374">
@@ -10704,10 +10711,10 @@
       <c r="A375" t="s">
         <v>381</v>
       </c>
-      <c r="B375">
+      <c r="B375" s="1">
         <v>440</v>
       </c>
-      <c r="C375">
+      <c r="C375" s="1">
         <v>1500</v>
       </c>
       <c r="D375">
@@ -10727,10 +10734,10 @@
       <c r="A376" t="s">
         <v>382</v>
       </c>
-      <c r="B376">
+      <c r="B376" s="1">
         <v>440</v>
       </c>
-      <c r="C376">
+      <c r="C376" s="1">
         <v>1500</v>
       </c>
       <c r="D376">
@@ -10750,10 +10757,10 @@
       <c r="A377" t="s">
         <v>383</v>
       </c>
-      <c r="B377">
+      <c r="B377" s="1">
         <v>440</v>
       </c>
-      <c r="C377">
+      <c r="C377" s="1">
         <v>1500</v>
       </c>
       <c r="D377">
@@ -10773,10 +10780,10 @@
       <c r="A378" t="s">
         <v>384</v>
       </c>
-      <c r="B378">
+      <c r="B378" s="1">
         <v>440</v>
       </c>
-      <c r="C378">
+      <c r="C378" s="1">
         <v>1500</v>
       </c>
       <c r="D378">
@@ -10796,10 +10803,10 @@
       <c r="A379" t="s">
         <v>385</v>
       </c>
-      <c r="B379">
+      <c r="B379" s="1">
         <v>440</v>
       </c>
-      <c r="C379">
+      <c r="C379" s="1">
         <v>1500</v>
       </c>
       <c r="D379">
@@ -10819,10 +10826,10 @@
       <c r="A380" t="s">
         <v>386</v>
       </c>
-      <c r="B380">
+      <c r="B380" s="1">
         <v>440</v>
       </c>
-      <c r="C380">
+      <c r="C380" s="1">
         <v>1500</v>
       </c>
       <c r="D380">
@@ -10842,10 +10849,10 @@
       <c r="A381" t="s">
         <v>387</v>
       </c>
-      <c r="B381">
+      <c r="B381" s="1">
         <v>440</v>
       </c>
-      <c r="C381">
+      <c r="C381" s="1">
         <v>1500</v>
       </c>
       <c r="D381">
@@ -10865,10 +10872,10 @@
       <c r="A382" t="s">
         <v>388</v>
       </c>
-      <c r="B382">
+      <c r="B382" s="1">
         <v>440</v>
       </c>
-      <c r="C382">
+      <c r="C382" s="1">
         <v>1500</v>
       </c>
       <c r="D382">
@@ -10888,10 +10895,10 @@
       <c r="A383" t="s">
         <v>389</v>
       </c>
-      <c r="B383">
+      <c r="B383" s="1">
         <v>440</v>
       </c>
-      <c r="C383">
+      <c r="C383" s="1">
         <v>1500</v>
       </c>
       <c r="D383">
@@ -10911,10 +10918,10 @@
       <c r="A384" t="s">
         <v>390</v>
       </c>
-      <c r="B384">
+      <c r="B384" s="1">
         <v>440</v>
       </c>
-      <c r="C384">
+      <c r="C384" s="1">
         <v>1500</v>
       </c>
       <c r="D384">
@@ -10934,10 +10941,10 @@
       <c r="A385" t="s">
         <v>391</v>
       </c>
-      <c r="B385">
+      <c r="B385" s="1">
         <v>440</v>
       </c>
-      <c r="C385">
+      <c r="C385" s="1">
         <v>1500</v>
       </c>
       <c r="D385">
@@ -10957,10 +10964,10 @@
       <c r="A386" t="s">
         <v>392</v>
       </c>
-      <c r="B386">
+      <c r="B386" s="1">
         <v>440</v>
       </c>
-      <c r="C386">
+      <c r="C386" s="1">
         <v>1500</v>
       </c>
       <c r="D386">
@@ -10980,10 +10987,10 @@
       <c r="A387" t="s">
         <v>393</v>
       </c>
-      <c r="B387">
+      <c r="B387" s="1">
         <v>440</v>
       </c>
-      <c r="C387">
+      <c r="C387" s="1">
         <v>1500</v>
       </c>
       <c r="D387">
@@ -11003,10 +11010,10 @@
       <c r="A388" t="s">
         <v>394</v>
       </c>
-      <c r="B388">
+      <c r="B388" s="1">
         <v>2760</v>
       </c>
-      <c r="C388">
+      <c r="C388" s="1">
         <v>6000</v>
       </c>
       <c r="D388">
@@ -11026,10 +11033,10 @@
       <c r="A389" t="s">
         <v>395</v>
       </c>
-      <c r="B389">
+      <c r="B389" s="1">
         <v>2760</v>
       </c>
-      <c r="C389">
+      <c r="C389" s="1">
         <v>6000</v>
       </c>
       <c r="D389">
@@ -11049,10 +11056,10 @@
       <c r="A390" t="s">
         <v>396</v>
       </c>
-      <c r="B390">
+      <c r="B390" s="1">
         <v>1380</v>
       </c>
-      <c r="C390">
+      <c r="C390" s="1">
         <v>4000</v>
       </c>
       <c r="D390">
@@ -11072,10 +11079,10 @@
       <c r="A391" t="s">
         <v>397</v>
       </c>
-      <c r="B391">
+      <c r="B391" s="1">
         <v>2540</v>
       </c>
-      <c r="C391">
+      <c r="C391" s="1">
         <v>4000</v>
       </c>
       <c r="D391">
@@ -11095,10 +11102,10 @@
       <c r="A392" t="s">
         <v>398</v>
       </c>
-      <c r="B392">
+      <c r="B392" s="1">
         <v>320</v>
       </c>
-      <c r="C392">
+      <c r="C392" s="1">
         <v>1000</v>
       </c>
       <c r="D392">
@@ -11118,10 +11125,10 @@
       <c r="A393" t="s">
         <v>399</v>
       </c>
-      <c r="B393">
+      <c r="B393" s="1">
         <v>6050</v>
       </c>
-      <c r="C393">
+      <c r="C393" s="1">
         <v>9000</v>
       </c>
       <c r="D393">
@@ -11141,10 +11148,10 @@
       <c r="A394" t="s">
         <v>400</v>
       </c>
-      <c r="B394">
+      <c r="B394" s="1">
         <v>10200</v>
       </c>
-      <c r="C394">
+      <c r="C394" s="1">
         <v>14000</v>
       </c>
       <c r="D394">
@@ -11164,10 +11171,10 @@
       <c r="A395" t="s">
         <v>401</v>
       </c>
-      <c r="B395">
+      <c r="B395" s="1">
         <v>1380</v>
       </c>
-      <c r="C395">
+      <c r="C395" s="1">
         <v>2500</v>
       </c>
       <c r="D395">
@@ -11187,10 +11194,10 @@
       <c r="A396" t="s">
         <v>402</v>
       </c>
-      <c r="B396">
+      <c r="B396" s="1">
         <v>1380</v>
       </c>
-      <c r="C396">
+      <c r="C396" s="1">
         <v>2500</v>
       </c>
       <c r="D396">
@@ -11210,10 +11217,10 @@
       <c r="A397" t="s">
         <v>403</v>
       </c>
-      <c r="B397">
+      <c r="B397" s="1">
         <v>3440</v>
       </c>
-      <c r="C397">
+      <c r="C397" s="1">
         <v>5000</v>
       </c>
       <c r="D397">

--- a/templates/importar_productos_template.xlsx
+++ b/templates/importar_productos_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duqueroso/Desktop/opencode-projects/control-plus/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABBA4327-82D1-F54B-BBFC-25D6B5CEB968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60346398-03B0-4140-998E-608417BAFB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{C1719250-87E2-DB49-8C6B-072748A47088}"/>
+    <workbookView xWindow="1600" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{C1719250-87E2-DB49-8C6B-072748A47088}"/>
   </bookViews>
   <sheets>
     <sheet name="importar_productos_template" sheetId="1" r:id="rId1"/>
@@ -46,141 +46,18 @@
     <t>stock_minimo</t>
   </si>
   <si>
-    <t>RESALTADOR OFFI-ESCO x 6 COLORES SURTIDO (OE-530)</t>
-  </si>
-  <si>
-    <t>papeleria</t>
-  </si>
-  <si>
-    <t>PLUMON GIPAO LAVABLE X12 PUNTA BALA (GP-267)</t>
-  </si>
-  <si>
-    <t>LAPIZ MIRADO No 2 AMARILLO (1790161)</t>
-  </si>
-  <si>
-    <t>LAPIZ NORMA TRIANGULAR 2HB (576174)(533131)</t>
-  </si>
-  <si>
-    <t>LAPIZ ROJO COLORCHEK (1705)(1790094)</t>
-  </si>
-  <si>
-    <t>LAPIZ OFFI-ESCO TRIANGULAR ROJO (OE-149) CAJA</t>
-  </si>
-  <si>
-    <t>COLOR NORMA 13+2 DRAGON NUEVA PRESENTACION (55580</t>
-  </si>
-  <si>
-    <t>COLOR PRISMACOLOR X 18 UNIPUNTA 4.0MM JUNIOR (215301</t>
-  </si>
-  <si>
-    <t>COLOR OFFI-ESCO X12 TRIANGULAR 4MM (OE-140)</t>
-  </si>
-  <si>
-    <t>COLOR NUEVO ARTISAN X 24 REDONDO 4 MM CAJA TRICOLO</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO BIC CRISTAL AZUL (1100003)</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO BIC CRISTAL ROJO (1100048)</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO BIC CRISTAL NEGRO (1100048)</t>
-  </si>
-  <si>
     <t>BOLIGRAFO OFFI-ESCO 0.7MM SEMI GEL NEGRO PUNTA FINA</t>
   </si>
   <si>
-    <t>BOLIGRAFO KILOMETRICO 100 NEGRO 1.0 mm SANFORD (3533</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO KILOMETRICO DISEÑOS 100 AZUL TAPA (1967172)</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO KILOMETRICO 100 ROJO 1.0 MM SANFORD (3532)</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO KILOMETRICO 100 FUCSIA 0.5 SANFORD (3565)</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO KILOMETRICO 100 MORADO SANFORD (3563)</t>
-  </si>
-  <si>
     <t>BOLIGRAFO KILOMETRICO 100 AZUL TURQUESA 0.5 SANFORD</t>
   </si>
   <si>
-    <t>BOLIGRAFO KILOMETRICO 100 RETRACTIL AZUL SANFORD (35</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO KILOMETRICO 100 RETRACTIL NEGRO SANFORD (</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO KILOMETRICO 100 RETRACTIL ROJO SANFORD (3</t>
-  </si>
-  <si>
-    <t>SACAPUNTA METAL IMPORT CAJA VERDE (A1002MR)</t>
-  </si>
-  <si>
-    <t>BORRADOR NATA 624 PEQUEÑO (LINEA AZUL)(ORION)(SCHO</t>
-  </si>
-  <si>
-    <t>BORRADOR NATA 612 GRANDE (LINEA AZUL)(ORION)(SCHOOL</t>
-  </si>
-  <si>
-    <t>BORRADOR GIPAO MIGA DE PAN 4B NEGRO-BEIS-COLORES-P</t>
-  </si>
-  <si>
-    <t>MICROPUNTA PELIKAN NEGRO 157 (30013017)</t>
-  </si>
-  <si>
-    <t>MICROPUNTA PELIKAN ROJO 157</t>
-  </si>
-  <si>
-    <t>MICROPUNTA PELIKAN AZUL 157</t>
-  </si>
-  <si>
-    <t>PLUMON PARCHESITO X 6 (761226)</t>
-  </si>
-  <si>
-    <t>PLUMON PARCHESITO X 12 (750008)</t>
-  </si>
-  <si>
-    <t>MICROPUNTAS DORICOLOR X 10 COLORES ESTUCHE</t>
-  </si>
-  <si>
-    <t>MARCADOR DORICOLOR GRAFICO X 10 ESTUCHE (570132)</t>
-  </si>
-  <si>
-    <t>LAPIZ FABER-CASTELL DIBUJO 8B GRADUADO (0625995)</t>
-  </si>
-  <si>
-    <t>LAPIZ FABER-CASTELL DIBUJO 6B GRADUADO (0501596)</t>
-  </si>
-  <si>
-    <t>LAPIZ FABER-CASTELL DIBUJO 2H GRADUADO (0501602)</t>
-  </si>
-  <si>
-    <t>MARCADOR DORICOLOR PERMANENTE AZUL (570026)</t>
-  </si>
-  <si>
-    <t>MARCADOR DORICOLOR PERMANENTE NEGRO (570033)</t>
-  </si>
-  <si>
-    <t>MARCADOR DORICOLOR PERMANENTE ROJO (570002)</t>
-  </si>
-  <si>
-    <t>MARCADOR DORICOLOR PERMANENTE VERDE (570019)</t>
-  </si>
-  <si>
     <t>CORRECTOR GIPAO LAPIZ BLACK</t>
   </si>
   <si>
     <t>CORRECTOR OFFI-ESCO LAPIZ 250</t>
   </si>
   <si>
-    <t>CORRECTOR CINTA OFFI-ESCO 6M CARTON (OE-260)</t>
-  </si>
-  <si>
     <t>MARCADOR DORICOLOR BORRABLE NEGRO</t>
   </si>
   <si>
@@ -202,18 +79,6 @@
     <t>VINILO POWER 125 COLORES FLUORESCENTES</t>
   </si>
   <si>
-    <t>PLASTILINA PARCHESITO X 13 LARGA (141332)</t>
-  </si>
-  <si>
-    <t>PLASTILINA PARCHESITO X 9 PEQUEÑA 55 GM (140038)(14134</t>
-  </si>
-  <si>
-    <t>PEGANTE SIPEGA X 40 GMS ESPECIAL DORICOLOR (151027)</t>
-  </si>
-  <si>
-    <t>PEGANTE SIPEGA X 125GMS DORICOLOR (151034)</t>
-  </si>
-  <si>
     <t>PEGANTE SIPEGA BARRA MEDIANO 15G</t>
   </si>
   <si>
@@ -223,27 +88,6 @@
     <t>PEGANTE SIPEGA BARRA GRANDE 40G</t>
   </si>
   <si>
-    <t>PALO PALETA NATURAL X 50 (101-92)</t>
-  </si>
-  <si>
-    <t>PALO PALETA DE COLORES X 50 (SU-279)(PTF-45)</t>
-  </si>
-  <si>
-    <t>SILICONA ETERNA 60 ML (59621)</t>
-  </si>
-  <si>
-    <t>SILICONA ETERNA 100 ML (59622)</t>
-  </si>
-  <si>
-    <t>CINTA CINTANDINA ENMASCARAR 18X20 SUPER MASK (CE-01</t>
-  </si>
-  <si>
-    <t>CINTA CINTANDINA ENMASCARAR 24X20 SUPER MASK (CE-01</t>
-  </si>
-  <si>
-    <t>CINTA CINTANDINA ENMASCARAR 48X40MTS (CE-007)</t>
-  </si>
-  <si>
     <t>CINTA ANCHA DE EMPAQUE 48MM X 100MTS</t>
   </si>
   <si>
@@ -259,261 +103,36 @@
     <t>SILICONA BARRA GRUESA</t>
   </si>
   <si>
-    <t>CRAYOLA PARCHESITOS PEQUEÑA DORICOLOR x 10 (140298)</t>
-  </si>
-  <si>
-    <t>CRAYOLA PARCHESITO GRUESA X10 COLORES SURTIDOS (14</t>
-  </si>
-  <si>
-    <t>TIJERA PUNTA ROMA ECONOMICA HOBART (3205/3025-2/3205-</t>
-  </si>
-  <si>
-    <t>TIJERA GIPAO 6.5" NEGRA CARTON MEDIANA (GP-165)</t>
-  </si>
-  <si>
-    <t>TIJERA GIPAO 8.5 MANGO NEGRO GRANDE CARTON (GP-215)</t>
-  </si>
-  <si>
-    <t>TIJERA ARTISAN PUNTA ROMA CARTON COLORES VIVOS Y P</t>
-  </si>
-  <si>
-    <t>PILA NALPILUX AA TIRA X 10 PARES</t>
-  </si>
-  <si>
-    <t>PILA NALPILUX AAA TIRA X 10 PARES</t>
-  </si>
-  <si>
-    <t>CARPETA BISEL CARTA COLORES IPP PAQUETE X 5</t>
-  </si>
-  <si>
-    <t>CARPETA BISEL OFICIO COLORES IPP PAQUETE X 5</t>
-  </si>
-  <si>
-    <t>CARPETA OFFI-ESCO HILO CARTA (OE-7218/OE-862)</t>
-  </si>
-  <si>
-    <t>CARPETA OFFI-ESCO HILO OFICIO HORI-VERT (OE-7249/OE-72</t>
-  </si>
-  <si>
-    <t>CARPETA OFFI-ESCO BROCHE CARTA (OE-872)(OE-7234)</t>
-  </si>
-  <si>
-    <t>CARPETA OFFI-ESCO BROCHE OFICIO (OE-874)(OE-7231)</t>
-  </si>
-  <si>
-    <t>CARPETA GIPAO LEGAJADORA CARTA CON GANCHO (GP-123)</t>
-  </si>
-  <si>
-    <t>CARPETA GIPAO LEGAJADORA OFICIO CON GANCHO (GP-124)</t>
-  </si>
-  <si>
-    <t>GANCHO LEGAJADOR TRITON PLASTICO BOLSA X 20 (5303NP</t>
-  </si>
-  <si>
-    <t>CLIP TRITON METALICO X 100  (5305IPL002)</t>
-  </si>
-  <si>
-    <t>CLIP TRITON MARIPOSA X 50  MEJIA (5305MPL004)</t>
-  </si>
-  <si>
-    <t>CHINCHE TRITON PLASTICO COLORES (TPLT01)</t>
-  </si>
-  <si>
-    <t>GANCHO TRITON COSEDORA 5000 GALVANIZADA (5301GPL00</t>
-  </si>
-  <si>
-    <t>GANCHO COSEDORA GIPAO X 1000 CAJA 26/6 (GP-01)</t>
-  </si>
-  <si>
-    <t>TIJERA PELUQUERA GIPAO GRANDE CARTON (GP-168)</t>
-  </si>
-  <si>
-    <t>SACAPUNTA MAPED CON DEPOSITO SHAKER (534753)</t>
-  </si>
-  <si>
-    <t>SOBRE MANILA NORMA CARTA 22.5 X 29 60 GM (57262)</t>
-  </si>
-  <si>
-    <t>SOBRE MANILA NORMA OFICIO 25X35 60 GMS (57264)</t>
-  </si>
-  <si>
-    <t>SOBRE  OFICIO BLANCO ANCHO 3-60 DISPAPELES (57101)(571</t>
-  </si>
-  <si>
     <t>BLOCK IMAGENES 70 HOJAS CARTA CUADRICULO</t>
   </si>
   <si>
-    <t>BLOCK IMAGENES/ 70 HOJAS CARTA RAYADO NOR</t>
-  </si>
-  <si>
-    <t>BLOCK IMAGENES 70 HOJAS CARTA SIN RAYADAS NORMA (54</t>
-  </si>
-  <si>
-    <t>BLOCK IMAGENES 70 HOJAS OFICIO CUADRICULADO (558254/</t>
-  </si>
-  <si>
-    <t>BLOCK IMAGENES 70 HOJAS OFICIO RAYAS (558253) (8000017)</t>
-  </si>
-  <si>
-    <t>BLOCK IMAGENES 70 HOJAS OFICIO SIN RAYAS (558255/80000</t>
-  </si>
-  <si>
-    <t>BLOCK IRIS CARTA ARTISAN X 35 HOJAS (112009)</t>
-  </si>
-  <si>
-    <t>BLOCK IRIS PRIMAVERA X 40 HOJAS FLUORESCENTE CARTA (</t>
-  </si>
-  <si>
-    <t>BLOCK IRIS PASTEL ARTISAN- FORMAS FUTURO CARTA (1120</t>
-  </si>
-  <si>
-    <t>FICHA BIBLIOGRAFICA COLORES SURTIDOS x 50 UNIDADES (1</t>
-  </si>
-  <si>
-    <t>PAPEL FOTOGRAFICO ETERNA X20</t>
-  </si>
-  <si>
-    <t>CARTULINA BRISTOL OCTAVOS X 10 COLORES SURTIDA PRIM</t>
-  </si>
-  <si>
-    <t>CARTULINA PLANA OCTAVOS X 10 SURTIDA PRIMAVERA (1178</t>
-  </si>
-  <si>
-    <t>CARTULINA PLANA OCTAVOS X 10 FLUORESCENTE PAPPYER/</t>
-  </si>
-  <si>
-    <t>CARTULINA NEGRA X 10 OCTAVOS GOMEZUL 180 GR (32195)</t>
-  </si>
-  <si>
     <t>BLOCK MILIMETRADO CALDERON</t>
   </si>
   <si>
-    <t>CARPETA KIMBERLY IMITACION BLANCO GRANITO PQTE X20 (</t>
-  </si>
-  <si>
-    <t>TABLA DE APOYO PLASTICA MANILLA METAL- FABRI/OYFORM</t>
-  </si>
-  <si>
-    <t>MARCADOR SHARPIE DELGADO negro SANFORD (4022)(30002</t>
-  </si>
-  <si>
-    <t>MARCADOR SHARPIE DELGADO AZUL SANFORD (30003B)(181</t>
-  </si>
-  <si>
-    <t>MARCADOR SHARPIE DELGADO FUCSIA (4059)(1789437)</t>
-  </si>
-  <si>
-    <t>MARCADOR SHARPIE DELGADO MORADO (4036)(30008)(18127</t>
-  </si>
-  <si>
-    <t>MARCADOR SHARPIE DELGADO ROJO SANFORD (4022)(30002</t>
-  </si>
-  <si>
-    <t>MARCADOR SHARPIE DELGADO VERDE LIMA (4058)(1789436)</t>
-  </si>
-  <si>
-    <t>RESMA FOTOCOPIA CARTA REPROGRAF PROPAL (10205)</t>
-  </si>
-  <si>
-    <t>RESMA FOTOCOPIA OFICIO REPROGRAF PROPAL (10206)</t>
-  </si>
-  <si>
-    <t>COMPAS GIPAO/DIVER CLASS CON LAPIZ (DC-16)(GP-25) CAJA</t>
-  </si>
-  <si>
-    <t>TRANSPORTADOR FABER-CASTELL 180° PLASTICO (30411-P)</t>
-  </si>
-  <si>
-    <t>TRANSPORTADOR FABER-CASTELL 360° PLASTICO (30421-P)</t>
-  </si>
-  <si>
-    <t>REGLA FABER-CASTELL 30 CMS ESCOLAR TRANSPARENTE (8</t>
-  </si>
-  <si>
     <t>REGLA GIPAO NEON RIGIDA 30CM</t>
   </si>
   <si>
-    <t>REGLA 30 CMS METALICA RULER (24819-4) ETERNA ET337/GIP</t>
-  </si>
-  <si>
     <t>PAPEL BOND PLIEGO 70X100 BLANCO</t>
   </si>
   <si>
     <t>PAPEL KRAF 70X100</t>
   </si>
   <si>
-    <t>CONTRATO ARRENDAMIENTO VIVIENDA URBANA 55-01 X 12 (8</t>
-  </si>
-  <si>
-    <t>HOJA DE VIDA AZUL MINERVA 10-03 (6000044)(8002)</t>
-  </si>
-  <si>
-    <t>HOJA DE VIDA GRIS X 20 MINERVA 10-00 (8000)</t>
-  </si>
-  <si>
-    <t>PORTAMINA FABER-CASTELL 0.7 LUMINUX ECONOMICO (3356</t>
-  </si>
-  <si>
-    <t>PORTAMINA OFFI-ESCO 0.5 COLORES (OE-154)</t>
-  </si>
-  <si>
-    <t>PORTAMINA OFFI-ESCO 2.0 COLORES PASTELES (OE-159)</t>
-  </si>
-  <si>
     <t>PORTAMINA OFFI-ESCO  0.7 AGARRE CAUCHO COLORES</t>
   </si>
   <si>
     <t>PORTAMINA GIPAO 0.7 COLORES</t>
   </si>
   <si>
-    <t>MINAS 2 MM GIPAO TARRO ROJO 2B (GP-620)</t>
-  </si>
-  <si>
-    <t>MINAS FABER-CASTELL 0.5 MM HB (70118-6)</t>
-  </si>
-  <si>
-    <t>MINAS FABER-CASTELL 0.7 MM HB (75718-3)</t>
-  </si>
-  <si>
-    <t>PINCEL ETERNA #1 IMPORT</t>
-  </si>
-  <si>
-    <t>PINCEL ETERNA #3 IMPORT</t>
-  </si>
-  <si>
-    <t>PINCEL ETERNA #5 IMPORT</t>
-  </si>
-  <si>
-    <t>PINCEL ETERNA #7 IMPORT</t>
-  </si>
-  <si>
-    <t>PINCEL ETERNA #9 IMPORT</t>
-  </si>
-  <si>
     <t>MIRELLA TUBO</t>
   </si>
   <si>
     <t>MURANO TUBO</t>
   </si>
   <si>
-    <t>BISTURI OFFI-ESCO PEQUEÑ0</t>
-  </si>
-  <si>
     <t>BISTURI OFFI-ESCO GRANDE</t>
   </si>
   <si>
-    <t>BISTURI ENCAUCHETADO JIAN ZHONG 18MM (286) PINGUINO (</t>
-  </si>
-  <si>
-    <t>CUCHILLA BISTURI GRANDE IMPORT</t>
-  </si>
-  <si>
-    <t>CUCHILLA BISTURI PEQUEÑA IMPORT</t>
-  </si>
-  <si>
-    <t>PAPEL SEDA CONTADO COLOR X 20 GOMEZUL (30201)(30101)</t>
-  </si>
-  <si>
     <t>PAPEL REGALO PRIMAVERA SENCILLO</t>
   </si>
   <si>
@@ -532,105 +151,27 @@
     <t>CARTON PAJA 1/8 CREMA Y BLANCO</t>
   </si>
   <si>
-    <t>PAPEL CELOFAN PLIEGO COLOR Y TRANSPARENTE (PRIMAVE</t>
-  </si>
-  <si>
-    <t>CARTULINA BRISTOL PLIEGO 70X100 BLANCA (111023)</t>
-  </si>
-  <si>
-    <t>CARTULINA PRIMAVERA PLANA PLIEGO COLOR GOMEZUL (31</t>
-  </si>
-  <si>
-    <t>CARTULINA PRIMAVERA PLANA PLIEGO DEGRADE GOMEZUL (31</t>
-  </si>
-  <si>
-    <t>CARTULINA PRIMAVERA PLANA PLIEGO FLUORESCENTE  GOMEZUL (31</t>
-  </si>
-  <si>
     <t>CARTULINA BRISTOL PLIEGO 70 X100 COLORES</t>
   </si>
   <si>
     <t>CARPETA FABRIFOLDER CARTON CARTA</t>
   </si>
   <si>
-    <t>CARPETA FABRIFOLDER CARTON OFICIO (201/202) (00203)</t>
-  </si>
-  <si>
-    <t>BLOCK MANTEQUILLA 1/8 X 35 HOJAS ARTISAN (31321)</t>
-  </si>
-  <si>
-    <t>RECIBO CAJA MANANTIAL CALDERON (61012)</t>
-  </si>
-  <si>
-    <t>DICCIONARIO ESPAÑOL BASICO ILUSTRADO FABRIFOLDER (9</t>
-  </si>
-  <si>
-    <t>DICCIONARIO INGLES CHICAGO AMARILLO ANCHO SUSAETA (</t>
-  </si>
-  <si>
-    <t>TABLA PLASTILINA SENCILLA (JULIO)</t>
-  </si>
-  <si>
     <t>FOMY CARTA COLORES SURTIDO</t>
   </si>
   <si>
     <t>FOMY CARTA MIRELLADO</t>
   </si>
   <si>
-    <t>CARTILLA NACHO INICIAL SUSAETA (714958)(425)</t>
-  </si>
-  <si>
     <t>TACO NOTAS BOND</t>
   </si>
   <si>
-    <t>TACO NOTAS X100 JIE JIAN/AH ROYAL (PA3064) (E3) (E304/E30</t>
-  </si>
-  <si>
-    <t>COSEDORA GIPAO (GP-134) MINI COLORES</t>
-  </si>
-  <si>
-    <t>PERFORADORA GIPAO (GP-05) 2 HUECOS MEDIANA</t>
-  </si>
-  <si>
-    <t>COSEDORA GIPAO (GP-200) METALICA</t>
-  </si>
-  <si>
-    <t>ROLLO CONTACT X 3 MTS TRANSPARENTE GIPAO (GP-60)</t>
-  </si>
-  <si>
-    <t>REGLA 30 CM PINGUINO COLORES Y TRANSPARENTE 8830 (M</t>
-  </si>
-  <si>
-    <t>BOLIGRAFO GIPAO MIRELLADO Y NEON  X 10 ESTUCHE (GP-1</t>
-  </si>
-  <si>
-    <t>PAPEL CREPE PLIEGO COLOR GOMEZUL (30801)</t>
-  </si>
-  <si>
-    <t>CUADERNO COSIDO 100-1 IMAGENES (576078FEM/576077SUR/</t>
-  </si>
-  <si>
-    <t>CUADERNO COSIDO 100-2 IMAGENES (576075/576076FEM/5513</t>
-  </si>
-  <si>
     <t>CUADERNO COSIDO 50-1 IMAGENES</t>
   </si>
   <si>
     <t>CUADERNO COSIDO 50-2 IMAGENES</t>
   </si>
   <si>
-    <t>CUADERNO DO 85-100-1 IMAGENES (557182SURT/80015MIX/80</t>
-  </si>
-  <si>
-    <t>CUADERNO DO 85-100-2 IMAGENES ECON (557183SURT)(8001</t>
-  </si>
-  <si>
-    <t>CUADERNO DO 105-80-1 IMAGENES (559187FEM/559188MAS/5</t>
-  </si>
-  <si>
-    <t>CUADERNO DO 105-80-2 IMAGENES (559185FEM/559186MAS/5</t>
-  </si>
-  <si>
     <t>CUADERNO COSIDO 100-1 LINK STICKER MASCULINO</t>
   </si>
   <si>
@@ -652,9 +193,6 @@
     <t>GANCHO LOTERO DINGLI COLORES</t>
   </si>
   <si>
-    <t>CALCULADORA KADIO 12 DIGITOS (KD-100B)</t>
-  </si>
-  <si>
     <t>CALCULADORA GIPAO COLORES PASTEL</t>
   </si>
   <si>
@@ -664,21 +202,12 @@
     <t>HUELLERO DIVERCLASS DC04</t>
   </si>
   <si>
-    <t>CUENTA FACIL SORTWICK PEQUEÑO (16-007)</t>
-  </si>
-  <si>
     <t>TALONARIO RIFA BOND CALDERON</t>
   </si>
   <si>
-    <t>PAPEL TORNASOL PLIEGO GOMEZUL (30528)</t>
-  </si>
-  <si>
     <t>PORTA DOCUMENTOS KEJEA  PLASTICA HORIZ-VERTIC</t>
   </si>
   <si>
-    <t>BORRADOR 5 PUNTAS BP-008 (24999-1)</t>
-  </si>
-  <si>
     <t>SACAPUNTAS KORES CON DEPOSITO CLICK</t>
   </si>
   <si>
@@ -691,9 +220,6 @@
     <t>TABLA PERIODICA PEQUEÑA</t>
   </si>
   <si>
-    <t>TABLA PERIODICA GRANDE (SU-295)</t>
-  </si>
-  <si>
     <t>LLUVIA DE SOBRE PRIMAVERA</t>
   </si>
   <si>
@@ -793,9 +319,6 @@
     <t>BOMBA ROSADO OSCURO MATE R12 X 12</t>
   </si>
   <si>
-    <t>piñateria</t>
-  </si>
-  <si>
     <t>VELAS CUMPLEAÑOS X10 DORADAS</t>
   </si>
   <si>
@@ -1232,6 +755,483 @@
   </si>
   <si>
     <t>VELA EROTICA CUMPLEAÑOS</t>
+  </si>
+  <si>
+    <t>Papelería</t>
+  </si>
+  <si>
+    <t>Pinatería</t>
+  </si>
+  <si>
+    <t>RESALTADOR OFFI-ESCO x 6 COLORES SURTIDO</t>
+  </si>
+  <si>
+    <t>PLUMON GIPAO LAVABLE X12 PUNTA BALA</t>
+  </si>
+  <si>
+    <t>LAPIZ MIRADO No 2 AMARILLO</t>
+  </si>
+  <si>
+    <t>LAPIZ NORMA TRIANGULAR 2HB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAPIZ ROJO COLORCHEK </t>
+  </si>
+  <si>
+    <t>LAPIZ OFFI-ESCO TRIANGULAR ROJO</t>
+  </si>
+  <si>
+    <t>COLOR NORMA 13+2 DRAGON NUEVA PRESENTACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR PRISMACOLOR X 18 UNIPUNTA 4.0MM JUNIOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR OFFI-ESCO X12 TRIANGULAR 4MM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLOR NUEVO ARTISAN X 24 REDONDO 4 MM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOLIGRAFO BIC CRISTAL AZUL </t>
+  </si>
+  <si>
+    <t>BOLIGRAFO BIC CRISTAL ROJO</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO BIC CRISTAL NEGRO</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 NEGRO 1.0 mm SANFORD</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO DISEÑOS 100 AZUL TAPA</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 ROJO 1.0 MM SANFORD</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 FUCSIA 0.5 SANFORD</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 MORADO SANFORD</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 RETRACTIL AZUL SANFORD</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 RETRACTIL NEGRO SANFORD</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO KILOMETRICO 100 RETRACTIL ROJO SANFORD</t>
+  </si>
+  <si>
+    <t>SACAPUNTA METAL IMPORT CAJA VERDE</t>
+  </si>
+  <si>
+    <t>BORRADOR NATA 624 PEQUEÑO</t>
+  </si>
+  <si>
+    <t>BORRADOR NATA 612 GRANDE</t>
+  </si>
+  <si>
+    <t>BORRADOR GIPAO MIGA DE PAN 4B</t>
+  </si>
+  <si>
+    <t>MICROPUNTA PELIKAN NEGRO</t>
+  </si>
+  <si>
+    <t>MICROPUNTA PELIKAN ROJO</t>
+  </si>
+  <si>
+    <t>MICROPUNTA PELIKAN AZUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLUMON PARCHESITO X 6 </t>
+  </si>
+  <si>
+    <t>PLUMON PARCHESITO X 12</t>
+  </si>
+  <si>
+    <t>MICROPUNTAS DORICOLOR X 10 COLORES</t>
+  </si>
+  <si>
+    <t>MARCADOR DORICOLOR GRAFICO X 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAPIZ FABER-CASTELL DIBUJO 8B GRADUADO </t>
+  </si>
+  <si>
+    <t>LAPIZ FABER-CASTELL DIBUJO 6B GRADUADO</t>
+  </si>
+  <si>
+    <t>LAPIZ FABER-CASTELL DIBUJO 2H GRADUADO</t>
+  </si>
+  <si>
+    <t>MARCADOR DORICOLOR PERMANENTE AZUL</t>
+  </si>
+  <si>
+    <t>MARCADOR DORICOLOR PERMANENTE NEGRO</t>
+  </si>
+  <si>
+    <t>MARCADOR DORICOLOR PERMANENTE ROJO</t>
+  </si>
+  <si>
+    <t>MARCADOR DORICOLOR PERMANENTE VERDE</t>
+  </si>
+  <si>
+    <t>CORRECTOR CINTA OFFI-ESCO 6M</t>
+  </si>
+  <si>
+    <t>PLASTILINA PARCHESITO X 13 LARGA</t>
+  </si>
+  <si>
+    <t>PLASTILINA PARCHESITO X 9 PEQUEÑA 55</t>
+  </si>
+  <si>
+    <t>PEGANTE SIPEGA X 40 GMS ESPECIAL DORICOLOR</t>
+  </si>
+  <si>
+    <t>PEGANTE SIPEGA X 125GMS DORICOLOR</t>
+  </si>
+  <si>
+    <t>PALO PALETA NATURAL X 50</t>
+  </si>
+  <si>
+    <t>PALO PALETA DE COLORES X 50</t>
+  </si>
+  <si>
+    <t>SILICONA ETERNA 60 ML</t>
+  </si>
+  <si>
+    <t>SILICONA ETERNA 100 ML</t>
+  </si>
+  <si>
+    <t>CINTA CINTANDINA ENMASCARAR 18X20 SUPER MASK</t>
+  </si>
+  <si>
+    <t>CINTA CINTANDINA ENMASCARAR 24X20 SUPER MASK</t>
+  </si>
+  <si>
+    <t>CINTA CINTANDINA ENMASCARAR 48X40MTS</t>
+  </si>
+  <si>
+    <t>CRAYOLA PARCHESITOS PEQUEÑA DORICOLOR x 10</t>
+  </si>
+  <si>
+    <t>CRAYOLA PARCHESITO GRUESA X10 COLORES SURTIDOS</t>
+  </si>
+  <si>
+    <t>TIJERA PUNTA ROMA ECONOMICA HOBART</t>
+  </si>
+  <si>
+    <t>TIJERA GIPAO 6.5" NEGRA CARTON MEDIANA</t>
+  </si>
+  <si>
+    <t>TIJERA GIPAO 8.5 MANGO NEGRO GRANDE CARTON</t>
+  </si>
+  <si>
+    <t>TIJERA ARTISAN PUNTA ROMA</t>
+  </si>
+  <si>
+    <t>PILA NALPILUX AA TIRA</t>
+  </si>
+  <si>
+    <t>PILA NALPILUX AAA TIRA</t>
+  </si>
+  <si>
+    <t>CARPETA BISEL CARTA</t>
+  </si>
+  <si>
+    <t>CARPETA BISEL OFICIO</t>
+  </si>
+  <si>
+    <t>CARPETA OFFI-ESCO HILO CARTA</t>
+  </si>
+  <si>
+    <t>CARPETA OFFI-ESCO HILO OFICIO</t>
+  </si>
+  <si>
+    <t>CARPETA OFFI-ESCO BROCHE CARTA</t>
+  </si>
+  <si>
+    <t>CARPETA OFFI-ESCO BROCHE OFICIO</t>
+  </si>
+  <si>
+    <t>CARPETA GIPAO LEGAJADORA CARTA CON GANCHO</t>
+  </si>
+  <si>
+    <t>CARPETA GIPAO LEGAJADORA OFICIO CON GANCHO</t>
+  </si>
+  <si>
+    <t>GANCHO LEGAJADOR TRITON PLASTICO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP TRITON METALICO X 100 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP TRITON MARIPOSA X 50 </t>
+  </si>
+  <si>
+    <t>CHINCHE TRITON PLASTICO COLORES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GANCHO TRITON COSEDORA 5000 GALVANIZADA </t>
+  </si>
+  <si>
+    <t>GANCHO COSEDORA GIPAO X 1000</t>
+  </si>
+  <si>
+    <t>TIJERA PELUQUERA GIPAO GRANDE CARTON</t>
+  </si>
+  <si>
+    <t>SACAPUNTA MAPED CON DEPOSITO SHAKER</t>
+  </si>
+  <si>
+    <t>SOBRE MANILA NORMA CARTA</t>
+  </si>
+  <si>
+    <t>SOBRE MANILA NORMA OFICIO</t>
+  </si>
+  <si>
+    <t>SOBRE  OFICIO BLANCO ANCHO</t>
+  </si>
+  <si>
+    <t>BLOCK IMAGENES/ 70 HOJAS CARTA RAYADO</t>
+  </si>
+  <si>
+    <t>BLOCK IMAGENES 70 HOJAS CARTA SIN RAYADAS</t>
+  </si>
+  <si>
+    <t>BLOCK IMAGENES 70 HOJAS OFICIO CUADRICULADO</t>
+  </si>
+  <si>
+    <t>BLOCK IMAGENES 70 HOJAS OFICIO RAYAS</t>
+  </si>
+  <si>
+    <t>BLOCK IMAGENES 70 HOJAS OFICIO SIN RAYAS</t>
+  </si>
+  <si>
+    <t>BLOCK IRIS CARTA ARTISAN X 35 HOJAS</t>
+  </si>
+  <si>
+    <t>BLOCK IRIS PRIMAVERA X 40 HOJAS FLUORESCENTE CARTA</t>
+  </si>
+  <si>
+    <t>BLOCK IRIS PASTEL ARTISAN- FORMAS FUTURO CARTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FICHA BIBLIOGRAFICA COLORES SURTIDOS x 50 UNIDADES </t>
+  </si>
+  <si>
+    <t>PAPEL FOTOGRAFICO</t>
+  </si>
+  <si>
+    <t>CARTULINA BRISTOL OCTAVOS</t>
+  </si>
+  <si>
+    <t>CARTULINA PLANA OCTAVOS SURTIDA</t>
+  </si>
+  <si>
+    <t>CARTULINA PLANA OCTAVOS FLUORESCENTE</t>
+  </si>
+  <si>
+    <t>CARTULINA NEGRA OCTAVOS</t>
+  </si>
+  <si>
+    <t>CARPETA KIMBERLY IMITACION BLANCO GRANITO</t>
+  </si>
+  <si>
+    <t>TABLA DE APOYO PLASTICA MANILLA METAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCADOR SHARPIE DELGADO negro SANFORD </t>
+  </si>
+  <si>
+    <t>MARCADOR SHARPIE DELGADO AZUL SANFORD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCADOR SHARPIE DELGADO FUCSIA </t>
+  </si>
+  <si>
+    <t>MARCADOR SHARPIE DELGADO MORADO</t>
+  </si>
+  <si>
+    <t>MARCADOR SHARPIE DELGADO ROJO SANFORD</t>
+  </si>
+  <si>
+    <t>MARCADOR SHARPIE DELGADO VERDE LIMA</t>
+  </si>
+  <si>
+    <t>RESMA FOTOCOPIA CARTA</t>
+  </si>
+  <si>
+    <t>RESMA FOTOCOPIA OFICIO</t>
+  </si>
+  <si>
+    <t>COMPAS GIPAO/DIVER CLASS CON LAPIZ</t>
+  </si>
+  <si>
+    <t>TRANSPORTADOR FABER-CASTELL 180° PLASTICO</t>
+  </si>
+  <si>
+    <t>TRANSPORTADOR FABER-CASTELL 360° PLASTICO</t>
+  </si>
+  <si>
+    <t>REGLA FABER-CASTELL 30 CMS TRANSPARENTE</t>
+  </si>
+  <si>
+    <t>REGLA 30 CMS METALICA</t>
+  </si>
+  <si>
+    <t>CONTRATO ARRENDAMIENTO VIVIENDA URBANA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOJA DE VIDA AZUL MINERVA </t>
+  </si>
+  <si>
+    <t>HOJA DE VIDA GRIS MINERVA</t>
+  </si>
+  <si>
+    <t>PORTAMINA FABER-CASTELL 0.7 LUMINUX ECONOMICO</t>
+  </si>
+  <si>
+    <t>PORTAMINA OFFI-ESCO 0.5 COLORES</t>
+  </si>
+  <si>
+    <t>PORTAMINA OFFI-ESCO 2.0 COLORES PASTELES</t>
+  </si>
+  <si>
+    <t>MINAS 2 MM GIPAO TARRO ROJO 2B</t>
+  </si>
+  <si>
+    <t>MINAS FABER-CASTELL 0.5 MM HB</t>
+  </si>
+  <si>
+    <t>MINAS FABER-CASTELL 0.7 MM HB</t>
+  </si>
+  <si>
+    <t>PINCEL ETERNA #1</t>
+  </si>
+  <si>
+    <t>PINCEL ETERNA #3</t>
+  </si>
+  <si>
+    <t>PINCEL ETERNA #5</t>
+  </si>
+  <si>
+    <t>PINCEL ETERNA #7</t>
+  </si>
+  <si>
+    <t>PINCEL ETERNA #9</t>
+  </si>
+  <si>
+    <t>BISTURI OFFI-ESCO PEQUEÑO</t>
+  </si>
+  <si>
+    <t>BISTURI ENCAUCHETADO JIAN ZHONG 18MM</t>
+  </si>
+  <si>
+    <t>CUCHILLA BISTURI GRANDE</t>
+  </si>
+  <si>
+    <t>CUCHILLA BISTURI PEQUEÑA</t>
+  </si>
+  <si>
+    <t>PAPEL SEDA CONTADO COLOR</t>
+  </si>
+  <si>
+    <t>PAPEL CELOFAN PLIEGO COLOR Y TRANSPARENTE</t>
+  </si>
+  <si>
+    <t>CARTULINA BRISTOL PLIEGO 70X100 BLANCA</t>
+  </si>
+  <si>
+    <t>CARTULINA PRIMAVERA PLANA PLIEGO COLOR</t>
+  </si>
+  <si>
+    <t>CARTULINA PRIMAVERA PLANA PLIEGO DEGRADE</t>
+  </si>
+  <si>
+    <t>CARTULINA PRIMAVERA PLANA PLIEGO FLUORESCENTE</t>
+  </si>
+  <si>
+    <t>CARPETA FABRIFOLDER CARTON OFICIO</t>
+  </si>
+  <si>
+    <t>BLOCK MANTEQUILLA 1/8 X 35 HOJAS</t>
+  </si>
+  <si>
+    <t>RECIBO CAJA MANANTIAL CALDERON</t>
+  </si>
+  <si>
+    <t>DICCIONARIO ESPAÑOL BASICO ILUSTRADO</t>
+  </si>
+  <si>
+    <t>DICCIONARIO INGLES CHICAGO AMARILLO ANCHO</t>
+  </si>
+  <si>
+    <t>TABLA PLASTILINA SENCILLA</t>
+  </si>
+  <si>
+    <t>CARTILLA NACHO INICIAL SUSAETA</t>
+  </si>
+  <si>
+    <t>TACO NOTAS X100 JIE JIAN/AH ROYAL</t>
+  </si>
+  <si>
+    <t>COSEDORA GIPAO MINI COLORES</t>
+  </si>
+  <si>
+    <t>PERFORADORA GIPAO 2 HUECOS MEDIANA</t>
+  </si>
+  <si>
+    <t>COSEDORA GIPAO  METALICA</t>
+  </si>
+  <si>
+    <t>ROLLO CONTACT X 3 MTS TRANSPARENTE GIPAO</t>
+  </si>
+  <si>
+    <t>REGLA 30 CM PINGUINO COLORES Y TRANSPARENTE</t>
+  </si>
+  <si>
+    <t>BOLIGRAFO GIPAO MIRELLADO Y NEON  X 10 ESTUCHE</t>
+  </si>
+  <si>
+    <t>PAPEL CREPE PLIEGO COLOR GOMEZUL</t>
+  </si>
+  <si>
+    <t>CUADERNO COSIDO 100-1 IMAGENES</t>
+  </si>
+  <si>
+    <t>CUADERNO COSIDO 100-2 IMAGENES</t>
+  </si>
+  <si>
+    <t>CUADERNO DO 85-100-1 IMAGENES</t>
+  </si>
+  <si>
+    <t>CUADERNO DO 85-100-2 IMAGENES ECON</t>
+  </si>
+  <si>
+    <t>CUADERNO DO 105-80-1 IMAGENES</t>
+  </si>
+  <si>
+    <t>CUADERNO DO 105-80-2 IMAGENES</t>
+  </si>
+  <si>
+    <t>CALCULADORA KADIO 12 DIGITOS</t>
+  </si>
+  <si>
+    <t>CUENTA FACIL SORTWICK PEQUEÑO</t>
+  </si>
+  <si>
+    <t>PAPEL TORNASOL PLIEGO GOMEZUL</t>
+  </si>
+  <si>
+    <t>BORRADOR 5 PUNTAS</t>
+  </si>
+  <si>
+    <t>TABLA PERIODICA GRANDE</t>
   </si>
 </sst>
 </file>
@@ -2099,6 +2099,7 @@
   <dimension ref="A1:H397"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="58.5" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -2130,7 +2131,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>247</v>
       </c>
       <c r="B2" s="1">
         <v>5370</v>
@@ -2142,7 +2143,7 @@
         <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2153,7 +2154,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>248</v>
       </c>
       <c r="B3" s="1">
         <v>6220</v>
@@ -2165,7 +2166,7 @@
         <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -2176,7 +2177,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>249</v>
       </c>
       <c r="B4" s="1">
         <v>610</v>
@@ -2188,7 +2189,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -2199,7 +2200,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>250</v>
       </c>
       <c r="B5" s="1">
         <v>440</v>
@@ -2211,7 +2212,7 @@
         <v>12</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -2222,7 +2223,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>251</v>
       </c>
       <c r="B6" s="1">
         <v>975</v>
@@ -2234,7 +2235,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -2245,7 +2246,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>252</v>
       </c>
       <c r="B7" s="1">
         <v>500</v>
@@ -2257,7 +2258,7 @@
         <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -2268,7 +2269,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>253</v>
       </c>
       <c r="B8" s="1">
         <v>11900</v>
@@ -2280,7 +2281,7 @@
         <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -2291,7 +2292,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>254</v>
       </c>
       <c r="B9" s="1">
         <v>12300</v>
@@ -2303,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -2314,7 +2315,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>255</v>
       </c>
       <c r="B10" s="1">
         <v>5550</v>
@@ -2326,7 +2327,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -2337,7 +2338,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>256</v>
       </c>
       <c r="B11" s="1">
         <v>12350</v>
@@ -2349,7 +2350,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -2360,7 +2361,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>257</v>
       </c>
       <c r="B12" s="1">
         <v>530</v>
@@ -2372,7 +2373,7 @@
         <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -2383,7 +2384,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>258</v>
       </c>
       <c r="B13" s="1">
         <v>530</v>
@@ -2395,7 +2396,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -2406,7 +2407,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="B14" s="1">
         <v>530</v>
@@ -2418,7 +2419,7 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -2429,7 +2430,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B15" s="1">
         <v>550</v>
@@ -2441,7 +2442,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -2452,7 +2453,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>260</v>
       </c>
       <c r="B16" s="1">
         <v>485</v>
@@ -2464,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -2475,7 +2476,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>261</v>
       </c>
       <c r="B17" s="1">
         <v>498</v>
@@ -2487,7 +2488,7 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -2498,7 +2499,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="B18" s="1">
         <v>485</v>
@@ -2510,7 +2511,7 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -2521,7 +2522,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>263</v>
       </c>
       <c r="B19" s="1">
         <v>485</v>
@@ -2533,7 +2534,7 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -2544,7 +2545,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>264</v>
       </c>
       <c r="B20" s="1">
         <v>590</v>
@@ -2556,7 +2557,7 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -2567,7 +2568,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B21" s="1">
         <v>485</v>
@@ -2579,7 +2580,7 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -2590,7 +2591,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>265</v>
       </c>
       <c r="B22" s="1">
         <v>750</v>
@@ -2602,7 +2603,7 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -2613,7 +2614,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>266</v>
       </c>
       <c r="B23" s="1">
         <v>750</v>
@@ -2625,7 +2626,7 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -2636,7 +2637,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>267</v>
       </c>
       <c r="B24" s="1">
         <v>750</v>
@@ -2648,7 +2649,7 @@
         <v>12</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -2659,7 +2660,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="B25" s="1">
         <v>260</v>
@@ -2671,7 +2672,7 @@
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F25">
         <v>24</v>
@@ -2682,7 +2683,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="B26" s="1">
         <v>150</v>
@@ -2694,7 +2695,7 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F26">
         <v>25</v>
@@ -2705,7 +2706,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="B27" s="1">
         <v>280</v>
@@ -2717,7 +2718,7 @@
         <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F27">
         <v>26</v>
@@ -2728,7 +2729,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>35</v>
+        <v>271</v>
       </c>
       <c r="B28" s="1">
         <v>710</v>
@@ -2740,7 +2741,7 @@
         <v>60</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F28">
         <v>27</v>
@@ -2751,7 +2752,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>272</v>
       </c>
       <c r="B29" s="1">
         <v>1300</v>
@@ -2763,7 +2764,7 @@
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F29">
         <v>28</v>
@@ -2774,7 +2775,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>273</v>
       </c>
       <c r="B30" s="1">
         <v>1300</v>
@@ -2786,7 +2787,7 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F30">
         <v>29</v>
@@ -2797,7 +2798,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>38</v>
+        <v>274</v>
       </c>
       <c r="B31" s="1">
         <v>1300</v>
@@ -2809,7 +2810,7 @@
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F31">
         <v>30</v>
@@ -2820,7 +2821,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>275</v>
       </c>
       <c r="B32" s="1">
         <v>3300</v>
@@ -2832,7 +2833,7 @@
         <v>6</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F32">
         <v>31</v>
@@ -2843,7 +2844,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="B33" s="1">
         <v>5470</v>
@@ -2855,7 +2856,7 @@
         <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F33">
         <v>32</v>
@@ -2866,7 +2867,7 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>277</v>
       </c>
       <c r="B34" s="1">
         <v>8990</v>
@@ -2878,7 +2879,7 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F34">
         <v>33</v>
@@ -2889,7 +2890,7 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>278</v>
       </c>
       <c r="B35" s="1">
         <v>16650</v>
@@ -2901,7 +2902,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F35">
         <v>34</v>
@@ -2912,7 +2913,7 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="B36" s="1">
         <v>1650</v>
@@ -2924,7 +2925,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F36">
         <v>35</v>
@@ -2935,7 +2936,7 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>280</v>
       </c>
       <c r="B37" s="1">
         <v>1650</v>
@@ -2947,7 +2948,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F37">
         <v>36</v>
@@ -2958,7 +2959,7 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>45</v>
+        <v>281</v>
       </c>
       <c r="B38" s="1">
         <v>1650</v>
@@ -2970,7 +2971,7 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F38">
         <v>37</v>
@@ -2981,7 +2982,7 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>282</v>
       </c>
       <c r="B39" s="1">
         <v>1380</v>
@@ -2993,7 +2994,7 @@
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F39">
         <v>38</v>
@@ -3004,7 +3005,7 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>283</v>
       </c>
       <c r="B40" s="1">
         <v>1380</v>
@@ -3016,7 +3017,7 @@
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F40">
         <v>39</v>
@@ -3027,7 +3028,7 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>284</v>
       </c>
       <c r="B41" s="1">
         <v>1380</v>
@@ -3039,7 +3040,7 @@
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F41">
         <v>40</v>
@@ -3050,7 +3051,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>285</v>
       </c>
       <c r="B42" s="1">
         <v>1380</v>
@@ -3062,7 +3063,7 @@
         <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F42">
         <v>41</v>
@@ -3073,7 +3074,7 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="B43" s="1">
         <v>1100</v>
@@ -3085,7 +3086,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F43">
         <v>42</v>
@@ -3096,7 +3097,7 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B44" s="1">
         <v>980</v>
@@ -3108,7 +3109,7 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F44">
         <v>43</v>
@@ -3119,7 +3120,7 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>52</v>
+        <v>286</v>
       </c>
       <c r="B45" s="1">
         <v>1999</v>
@@ -3131,7 +3132,7 @@
         <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F45">
         <v>44</v>
@@ -3142,7 +3143,7 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="B46" s="1">
         <v>1505</v>
@@ -3154,7 +3155,7 @@
         <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F46">
         <v>45</v>
@@ -3165,7 +3166,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1">
         <v>1505</v>
@@ -3177,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F47">
         <v>46</v>
@@ -3188,7 +3189,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B48" s="1">
         <v>1505</v>
@@ -3200,7 +3201,7 @@
         <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F48">
         <v>47</v>
@@ -3211,7 +3212,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B49" s="1">
         <v>1505</v>
@@ -3223,7 +3224,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F49">
         <v>48</v>
@@ -3234,7 +3235,7 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="B50" s="1">
         <v>3800</v>
@@ -3246,7 +3247,7 @@
         <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F50">
         <v>49</v>
@@ -3257,7 +3258,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
       <c r="B51" s="1">
         <v>2021</v>
@@ -3269,7 +3270,7 @@
         <v>24</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F51">
         <v>50</v>
@@ -3280,7 +3281,7 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="B52" s="1">
         <v>3468</v>
@@ -3292,7 +3293,7 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F52">
         <v>51</v>
@@ -3303,7 +3304,7 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>60</v>
+        <v>287</v>
       </c>
       <c r="B53" s="1">
         <v>2950</v>
@@ -3315,7 +3316,7 @@
         <v>6</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F53">
         <v>52</v>
@@ -3326,7 +3327,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>288</v>
       </c>
       <c r="B54" s="1">
         <v>1220</v>
@@ -3338,7 +3339,7 @@
         <v>6</v>
       </c>
       <c r="E54" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F54">
         <v>53</v>
@@ -3349,7 +3350,7 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>289</v>
       </c>
       <c r="B55" s="1">
         <v>790</v>
@@ -3361,7 +3362,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F55">
         <v>54</v>
@@ -3372,7 +3373,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>290</v>
       </c>
       <c r="B56" s="1">
         <v>2120</v>
@@ -3384,7 +3385,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F56">
         <v>55</v>
@@ -3395,7 +3396,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="B57" s="1">
         <v>1430</v>
@@ -3407,7 +3408,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F57">
         <v>56</v>
@@ -3418,7 +3419,7 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="B58" s="1">
         <v>3200</v>
@@ -3430,7 +3431,7 @@
         <v>6</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F58">
         <v>57</v>
@@ -3441,7 +3442,7 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="B59" s="1">
         <v>2875</v>
@@ -3453,7 +3454,7 @@
         <v>6</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F59">
         <v>58</v>
@@ -3464,7 +3465,7 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>291</v>
       </c>
       <c r="B60" s="1">
         <v>1350</v>
@@ -3476,7 +3477,7 @@
         <v>6</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F60">
         <v>59</v>
@@ -3487,7 +3488,7 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>292</v>
       </c>
       <c r="B61" s="1">
         <v>1550</v>
@@ -3499,7 +3500,7 @@
         <v>6</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F61">
         <v>60</v>
@@ -3510,7 +3511,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="B62" s="1">
         <v>1925</v>
@@ -3522,7 +3523,7 @@
         <v>6</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F62">
         <v>61</v>
@@ -3533,7 +3534,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>294</v>
       </c>
       <c r="B63" s="1">
         <v>2980</v>
@@ -3545,7 +3546,7 @@
         <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -3556,7 +3557,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>295</v>
       </c>
       <c r="B64" s="1">
         <v>2040</v>
@@ -3568,7 +3569,7 @@
         <v>6</v>
       </c>
       <c r="E64" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F64">
         <v>63</v>
@@ -3579,7 +3580,7 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>72</v>
+        <v>296</v>
       </c>
       <c r="B65" s="1">
         <v>2720</v>
@@ -3591,7 +3592,7 @@
         <v>6</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F65">
         <v>64</v>
@@ -3602,7 +3603,7 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>297</v>
       </c>
       <c r="B66" s="1">
         <v>8650</v>
@@ -3614,7 +3615,7 @@
         <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F66">
         <v>65</v>
@@ -3625,7 +3626,7 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B67" s="1">
         <v>3750</v>
@@ -3637,7 +3638,7 @@
         <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F67">
         <v>66</v>
@@ -3648,7 +3649,7 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="B68" s="1">
         <v>1340</v>
@@ -3660,7 +3661,7 @@
         <v>6</v>
       </c>
       <c r="E68" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F68">
         <v>67</v>
@@ -3671,7 +3672,7 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="B69" s="1">
         <v>375</v>
@@ -3683,7 +3684,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F69">
         <v>68</v>
@@ -3694,7 +3695,7 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="B70" s="1">
         <v>250</v>
@@ -3706,7 +3707,7 @@
         <v>50</v>
       </c>
       <c r="E70" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F70">
         <v>69</v>
@@ -3717,7 +3718,7 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="B71" s="1">
         <v>650</v>
@@ -3729,7 +3730,7 @@
         <v>25</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F71">
         <v>70</v>
@@ -3740,7 +3741,7 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>298</v>
       </c>
       <c r="B72" s="1">
         <v>3050</v>
@@ -3752,7 +3753,7 @@
         <v>6</v>
       </c>
       <c r="E72" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F72">
         <v>71</v>
@@ -3763,7 +3764,7 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>80</v>
+        <v>299</v>
       </c>
       <c r="B73" s="1">
         <v>7220</v>
@@ -3775,7 +3776,7 @@
         <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F73">
         <v>72</v>
@@ -3786,7 +3787,7 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="B74" s="1">
         <v>875</v>
@@ -3798,7 +3799,7 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F74">
         <v>73</v>
@@ -3809,7 +3810,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="B75" s="1">
         <v>2535</v>
@@ -3821,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="E75" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F75">
         <v>74</v>
@@ -3832,7 +3833,7 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>302</v>
       </c>
       <c r="B76" s="1">
         <v>3970</v>
@@ -3844,7 +3845,7 @@
         <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F76">
         <v>75</v>
@@ -3855,7 +3856,7 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>303</v>
       </c>
       <c r="B77" s="1">
         <v>2300</v>
@@ -3867,7 +3868,7 @@
         <v>6</v>
       </c>
       <c r="E77" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F77">
         <v>76</v>
@@ -3878,7 +3879,7 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>304</v>
       </c>
       <c r="B78" s="1">
         <v>1300</v>
@@ -3890,7 +3891,7 @@
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F78">
         <v>77</v>
@@ -3901,7 +3902,7 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>305</v>
       </c>
       <c r="B79" s="1">
         <v>1625</v>
@@ -3913,7 +3914,7 @@
         <v>10</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -3924,7 +3925,7 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>306</v>
       </c>
       <c r="B80" s="1">
         <v>1022</v>
@@ -3936,7 +3937,7 @@
         <v>10</v>
       </c>
       <c r="E80" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F80">
         <v>79</v>
@@ -3947,7 +3948,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>88</v>
+        <v>307</v>
       </c>
       <c r="B81" s="1">
         <v>1130</v>
@@ -3959,7 +3960,7 @@
         <v>10</v>
       </c>
       <c r="E81" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F81">
         <v>80</v>
@@ -3970,7 +3971,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>89</v>
+        <v>308</v>
       </c>
       <c r="B82" s="1">
         <v>1650</v>
@@ -3982,7 +3983,7 @@
         <v>6</v>
       </c>
       <c r="E82" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F82">
         <v>81</v>
@@ -3993,7 +3994,7 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="B83" s="1">
         <v>1750</v>
@@ -4005,7 +4006,7 @@
         <v>6</v>
       </c>
       <c r="E83" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F83">
         <v>82</v>
@@ -4016,7 +4017,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>310</v>
       </c>
       <c r="B84" s="1">
         <v>1495</v>
@@ -4028,7 +4029,7 @@
         <v>6</v>
       </c>
       <c r="E84" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F84">
         <v>83</v>
@@ -4039,7 +4040,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>92</v>
+        <v>311</v>
       </c>
       <c r="B85" s="1">
         <v>1750</v>
@@ -4051,7 +4052,7 @@
         <v>6</v>
       </c>
       <c r="E85" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F85">
         <v>84</v>
@@ -4062,7 +4063,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>93</v>
+        <v>312</v>
       </c>
       <c r="B86" s="1">
         <v>2450</v>
@@ -4074,7 +4075,7 @@
         <v>6</v>
       </c>
       <c r="E86" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F86">
         <v>85</v>
@@ -4085,7 +4086,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>94</v>
+        <v>313</v>
       </c>
       <c r="B87" s="1">
         <v>2650</v>
@@ -4097,7 +4098,7 @@
         <v>6</v>
       </c>
       <c r="E87" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F87">
         <v>86</v>
@@ -4108,7 +4109,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>95</v>
+        <v>314</v>
       </c>
       <c r="B88" s="1">
         <v>122</v>
@@ -4120,7 +4121,7 @@
         <v>60</v>
       </c>
       <c r="E88" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F88">
         <v>87</v>
@@ -4131,7 +4132,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>96</v>
+        <v>315</v>
       </c>
       <c r="B89" s="1">
         <v>890</v>
@@ -4143,7 +4144,7 @@
         <v>6</v>
       </c>
       <c r="E89" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F89">
         <v>88</v>
@@ -4154,7 +4155,7 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>97</v>
+        <v>316</v>
       </c>
       <c r="B90" s="1">
         <v>2750</v>
@@ -4166,7 +4167,7 @@
         <v>6</v>
       </c>
       <c r="E90" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F90">
         <v>89</v>
@@ -4177,7 +4178,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="B91" s="1">
         <v>1360</v>
@@ -4189,7 +4190,7 @@
         <v>6</v>
       </c>
       <c r="E91" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F91">
         <v>90</v>
@@ -4200,7 +4201,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>99</v>
+        <v>318</v>
       </c>
       <c r="B92" s="1">
         <v>2500</v>
@@ -4212,7 +4213,7 @@
         <v>6</v>
       </c>
       <c r="E92" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F92">
         <v>91</v>
@@ -4223,7 +4224,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>319</v>
       </c>
       <c r="B93" s="1">
         <v>900</v>
@@ -4235,7 +4236,7 @@
         <v>6</v>
       </c>
       <c r="E93" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F93">
         <v>92</v>
@@ -4246,7 +4247,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="B94" s="1">
         <v>3275</v>
@@ -4258,7 +4259,7 @@
         <v>3</v>
       </c>
       <c r="E94" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F94">
         <v>93</v>
@@ -4269,7 +4270,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>321</v>
       </c>
       <c r="B95" s="1">
         <v>1160</v>
@@ -4281,7 +4282,7 @@
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F95">
         <v>94</v>
@@ -4292,7 +4293,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>103</v>
+        <v>322</v>
       </c>
       <c r="B96" s="1">
         <v>155</v>
@@ -4304,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F96">
         <v>95</v>
@@ -4315,7 +4316,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>104</v>
+        <v>323</v>
       </c>
       <c r="B97" s="1">
         <v>195</v>
@@ -4327,7 +4328,7 @@
         <v>100</v>
       </c>
       <c r="E97" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F97">
         <v>96</v>
@@ -4338,7 +4339,7 @@
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>105</v>
+        <v>324</v>
       </c>
       <c r="B98" s="1">
         <v>81</v>
@@ -4350,7 +4351,7 @@
         <v>50</v>
       </c>
       <c r="E98" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F98">
         <v>97</v>
@@ -4361,7 +4362,7 @@
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="B99" s="1">
         <v>2840</v>
@@ -4373,7 +4374,7 @@
         <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F99">
         <v>98</v>
@@ -4384,7 +4385,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>107</v>
+        <v>325</v>
       </c>
       <c r="B100" s="1">
         <v>2840</v>
@@ -4396,7 +4397,7 @@
         <v>6</v>
       </c>
       <c r="E100" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F100">
         <v>99</v>
@@ -4407,7 +4408,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>326</v>
       </c>
       <c r="B101" s="1">
         <v>2840</v>
@@ -4419,7 +4420,7 @@
         <v>6</v>
       </c>
       <c r="E101" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F101">
         <v>100</v>
@@ -4430,7 +4431,7 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>109</v>
+        <v>327</v>
       </c>
       <c r="B102" s="1">
         <v>3590</v>
@@ -4442,7 +4443,7 @@
         <v>6</v>
       </c>
       <c r="E102" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F102">
         <v>101</v>
@@ -4453,7 +4454,7 @@
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>110</v>
+        <v>328</v>
       </c>
       <c r="B103" s="1">
         <v>3590</v>
@@ -4465,7 +4466,7 @@
         <v>6</v>
       </c>
       <c r="E103" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F103">
         <v>102</v>
@@ -4476,7 +4477,7 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>111</v>
+        <v>329</v>
       </c>
       <c r="B104" s="1">
         <v>3450</v>
@@ -4488,7 +4489,7 @@
         <v>6</v>
       </c>
       <c r="E104" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F104">
         <v>103</v>
@@ -4499,7 +4500,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>112</v>
+        <v>330</v>
       </c>
       <c r="B105" s="1">
         <v>2990</v>
@@ -4511,7 +4512,7 @@
         <v>6</v>
       </c>
       <c r="E105" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F105">
         <v>104</v>
@@ -4522,7 +4523,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>113</v>
+        <v>331</v>
       </c>
       <c r="B106" s="1">
         <v>4900</v>
@@ -4534,7 +4535,7 @@
         <v>3</v>
       </c>
       <c r="E106" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F106">
         <v>105</v>
@@ -4545,7 +4546,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>114</v>
+        <v>332</v>
       </c>
       <c r="B107" s="1">
         <v>6500</v>
@@ -4557,7 +4558,7 @@
         <v>2</v>
       </c>
       <c r="E107" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F107">
         <v>106</v>
@@ -4568,7 +4569,7 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>333</v>
       </c>
       <c r="B108" s="1">
         <v>1670</v>
@@ -4580,7 +4581,7 @@
         <v>8</v>
       </c>
       <c r="E108" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F108">
         <v>107</v>
@@ -4591,7 +4592,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>116</v>
+        <v>334</v>
       </c>
       <c r="B109" s="1">
         <v>450</v>
@@ -4603,7 +4604,7 @@
         <v>40</v>
       </c>
       <c r="E109" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F109">
         <v>108</v>
@@ -4614,7 +4615,7 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>117</v>
+        <v>335</v>
       </c>
       <c r="B110" s="1">
         <v>210</v>
@@ -4626,7 +4627,7 @@
         <v>60</v>
       </c>
       <c r="E110" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F110">
         <v>109</v>
@@ -4637,7 +4638,7 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>118</v>
+        <v>336</v>
       </c>
       <c r="B111" s="1">
         <v>248</v>
@@ -4649,7 +4650,7 @@
         <v>30</v>
       </c>
       <c r="E111" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F111">
         <v>110</v>
@@ -4660,7 +4661,7 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>119</v>
+        <v>337</v>
       </c>
       <c r="B112" s="1">
         <v>275</v>
@@ -4672,7 +4673,7 @@
         <v>30</v>
       </c>
       <c r="E112" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F112">
         <v>111</v>
@@ -4683,7 +4684,7 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>120</v>
+        <v>338</v>
       </c>
       <c r="B113" s="1">
         <v>300</v>
@@ -4695,7 +4696,7 @@
         <v>30</v>
       </c>
       <c r="E113" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F113">
         <v>112</v>
@@ -4706,7 +4707,7 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="B114" s="1">
         <v>7440</v>
@@ -4718,7 +4719,7 @@
         <v>3</v>
       </c>
       <c r="E114" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F114">
         <v>113</v>
@@ -4729,7 +4730,7 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>122</v>
+        <v>339</v>
       </c>
       <c r="B115" s="1">
         <v>513</v>
@@ -4741,7 +4742,7 @@
         <v>40</v>
       </c>
       <c r="E115" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F115">
         <v>114</v>
@@ -4752,7 +4753,7 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>340</v>
       </c>
       <c r="B116" s="1">
         <v>5500</v>
@@ -4764,7 +4765,7 @@
         <v>3</v>
       </c>
       <c r="E116" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F116">
         <v>115</v>
@@ -4775,7 +4776,7 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>124</v>
+        <v>341</v>
       </c>
       <c r="B117" s="1">
         <v>2870</v>
@@ -4787,7 +4788,7 @@
         <v>6</v>
       </c>
       <c r="E117" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F117">
         <v>116</v>
@@ -4798,7 +4799,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>125</v>
+        <v>342</v>
       </c>
       <c r="B118" s="1">
         <v>2550</v>
@@ -4810,7 +4811,7 @@
         <v>6</v>
       </c>
       <c r="E118" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F118">
         <v>117</v>
@@ -4821,7 +4822,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>126</v>
+        <v>343</v>
       </c>
       <c r="B119" s="1">
         <v>2870</v>
@@ -4833,7 +4834,7 @@
         <v>6</v>
       </c>
       <c r="E119" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F119">
         <v>118</v>
@@ -4844,7 +4845,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>127</v>
+        <v>344</v>
       </c>
       <c r="B120" s="1">
         <v>2870</v>
@@ -4856,7 +4857,7 @@
         <v>6</v>
       </c>
       <c r="E120" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F120">
         <v>119</v>
@@ -4867,7 +4868,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>128</v>
+        <v>345</v>
       </c>
       <c r="B121" s="1">
         <v>2870</v>
@@ -4879,7 +4880,7 @@
         <v>6</v>
       </c>
       <c r="E121" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F121">
         <v>120</v>
@@ -4890,7 +4891,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>129</v>
+        <v>346</v>
       </c>
       <c r="B122" s="1">
         <v>2870</v>
@@ -4902,7 +4903,7 @@
         <v>6</v>
       </c>
       <c r="E122" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F122">
         <v>121</v>
@@ -4913,7 +4914,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>130</v>
+        <v>347</v>
       </c>
       <c r="B123" s="1">
         <v>14900</v>
@@ -4925,7 +4926,7 @@
         <v>4</v>
       </c>
       <c r="E123" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F123">
         <v>122</v>
@@ -4936,7 +4937,7 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>131</v>
+        <v>348</v>
       </c>
       <c r="B124" s="1">
         <v>20500</v>
@@ -4948,7 +4949,7 @@
         <v>2</v>
       </c>
       <c r="E124" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F124">
         <v>123</v>
@@ -4959,7 +4960,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>132</v>
+        <v>349</v>
       </c>
       <c r="B125" s="1">
         <v>1675</v>
@@ -4971,7 +4972,7 @@
         <v>6</v>
       </c>
       <c r="E125" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F125">
         <v>124</v>
@@ -4982,7 +4983,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>133</v>
+        <v>350</v>
       </c>
       <c r="B126" s="1">
         <v>1224</v>
@@ -4994,7 +4995,7 @@
         <v>6</v>
       </c>
       <c r="E126" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F126">
         <v>125</v>
@@ -5005,7 +5006,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>134</v>
+        <v>351</v>
       </c>
       <c r="B127" s="1">
         <v>1850</v>
@@ -5017,7 +5018,7 @@
         <v>6</v>
       </c>
       <c r="E127" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F127">
         <v>126</v>
@@ -5028,7 +5029,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>135</v>
+        <v>352</v>
       </c>
       <c r="B128" s="1">
         <v>1600</v>
@@ -5040,7 +5041,7 @@
         <v>6</v>
       </c>
       <c r="E128" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F128">
         <v>127</v>
@@ -5051,7 +5052,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>136</v>
+        <v>29</v>
       </c>
       <c r="B129" s="1">
         <v>950</v>
@@ -5063,7 +5064,7 @@
         <v>6</v>
       </c>
       <c r="E129" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F129">
         <v>128</v>
@@ -5074,7 +5075,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>137</v>
+        <v>353</v>
       </c>
       <c r="B130" s="1">
         <v>1499</v>
@@ -5086,7 +5087,7 @@
         <v>6</v>
       </c>
       <c r="E130" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F130">
         <v>129</v>
@@ -5097,7 +5098,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>138</v>
+        <v>30</v>
       </c>
       <c r="B131" s="1">
         <v>410</v>
@@ -5109,7 +5110,7 @@
         <v>24</v>
       </c>
       <c r="E131" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F131">
         <v>130</v>
@@ -5120,7 +5121,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="B132" s="1">
         <v>317</v>
@@ -5132,7 +5133,7 @@
         <v>24</v>
       </c>
       <c r="E132" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F132">
         <v>131</v>
@@ -5143,7 +5144,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>140</v>
+        <v>354</v>
       </c>
       <c r="B133" s="1">
         <v>2533</v>
@@ -5155,7 +5156,7 @@
         <v>12</v>
       </c>
       <c r="E133" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F133">
         <v>132</v>
@@ -5166,7 +5167,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>141</v>
+        <v>355</v>
       </c>
       <c r="B134" s="1">
         <v>643</v>
@@ -5178,7 +5179,7 @@
         <v>20</v>
       </c>
       <c r="E134" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F134">
         <v>133</v>
@@ -5189,7 +5190,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>142</v>
+        <v>356</v>
       </c>
       <c r="B135" s="1">
         <v>355</v>
@@ -5201,7 +5202,7 @@
         <v>20</v>
       </c>
       <c r="E135" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F135">
         <v>134</v>
@@ -5212,7 +5213,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>143</v>
+        <v>357</v>
       </c>
       <c r="B136" s="1">
         <v>1700</v>
@@ -5224,7 +5225,7 @@
         <v>12</v>
       </c>
       <c r="E136" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F136">
         <v>135</v>
@@ -5235,7 +5236,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>144</v>
+        <v>358</v>
       </c>
       <c r="B137" s="1">
         <v>798</v>
@@ -5247,7 +5248,7 @@
         <v>12</v>
       </c>
       <c r="E137" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F137">
         <v>136</v>
@@ -5258,7 +5259,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>145</v>
+        <v>359</v>
       </c>
       <c r="B138" s="1">
         <v>1380</v>
@@ -5270,7 +5271,7 @@
         <v>12</v>
       </c>
       <c r="E138" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F138">
         <v>137</v>
@@ -5281,7 +5282,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="B139" s="1">
         <v>1100</v>
@@ -5293,7 +5294,7 @@
         <v>12</v>
       </c>
       <c r="E139" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F139">
         <v>138</v>
@@ -5304,7 +5305,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="B140" s="1">
         <v>1820</v>
@@ -5316,7 +5317,7 @@
         <v>12</v>
       </c>
       <c r="E140" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F140">
         <v>139</v>
@@ -5327,7 +5328,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="B141" s="1">
         <v>1570</v>
@@ -5339,7 +5340,7 @@
         <v>3</v>
       </c>
       <c r="E141" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F141">
         <v>140</v>
@@ -5350,7 +5351,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>149</v>
+        <v>361</v>
       </c>
       <c r="B142" s="1">
         <v>1350</v>
@@ -5362,7 +5363,7 @@
         <v>6</v>
       </c>
       <c r="E142" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F142">
         <v>141</v>
@@ -5373,7 +5374,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>150</v>
+        <v>362</v>
       </c>
       <c r="B143" s="1">
         <v>1350</v>
@@ -5385,7 +5386,7 @@
         <v>6</v>
       </c>
       <c r="E143" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F143">
         <v>142</v>
@@ -5396,7 +5397,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>151</v>
+        <v>363</v>
       </c>
       <c r="B144" s="1">
         <v>450</v>
@@ -5408,7 +5409,7 @@
         <v>12</v>
       </c>
       <c r="E144" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F144">
         <v>143</v>
@@ -5419,7 +5420,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>152</v>
+        <v>364</v>
       </c>
       <c r="B145" s="1">
         <v>620</v>
@@ -5431,7 +5432,7 @@
         <v>12</v>
       </c>
       <c r="E145" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F145">
         <v>144</v>
@@ -5442,7 +5443,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>153</v>
+        <v>365</v>
       </c>
       <c r="B146" s="1">
         <v>850</v>
@@ -5454,7 +5455,7 @@
         <v>12</v>
       </c>
       <c r="E146" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F146">
         <v>145</v>
@@ -5465,7 +5466,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>154</v>
+        <v>366</v>
       </c>
       <c r="B147" s="1">
         <v>1150</v>
@@ -5477,7 +5478,7 @@
         <v>12</v>
       </c>
       <c r="E147" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F147">
         <v>146</v>
@@ -5488,7 +5489,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>155</v>
+        <v>367</v>
       </c>
       <c r="B148" s="1">
         <v>1350</v>
@@ -5500,7 +5501,7 @@
         <v>12</v>
       </c>
       <c r="E148" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F148">
         <v>147</v>
@@ -5511,7 +5512,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="B149" s="1">
         <v>280</v>
@@ -5523,7 +5524,7 @@
         <v>24</v>
       </c>
       <c r="E149" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F149">
         <v>148</v>
@@ -5534,7 +5535,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>157</v>
+        <v>35</v>
       </c>
       <c r="B150" s="1">
         <v>359</v>
@@ -5546,7 +5547,7 @@
         <v>12</v>
       </c>
       <c r="E150" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F150">
         <v>149</v>
@@ -5557,7 +5558,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>158</v>
+        <v>368</v>
       </c>
       <c r="B151" s="1">
         <v>1450</v>
@@ -5569,7 +5570,7 @@
         <v>6</v>
       </c>
       <c r="E151" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F151">
         <v>150</v>
@@ -5580,7 +5581,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>159</v>
+        <v>36</v>
       </c>
       <c r="B152" s="1">
         <v>2200</v>
@@ -5592,7 +5593,7 @@
         <v>6</v>
       </c>
       <c r="E152" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F152">
         <v>151</v>
@@ -5603,7 +5604,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>160</v>
+        <v>369</v>
       </c>
       <c r="B153" s="1">
         <v>2100</v>
@@ -5615,7 +5616,7 @@
         <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F153">
         <v>152</v>
@@ -5626,7 +5627,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>161</v>
+        <v>370</v>
       </c>
       <c r="B154" s="1">
         <v>1370</v>
@@ -5638,7 +5639,7 @@
         <v>3</v>
       </c>
       <c r="E154" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F154">
         <v>153</v>
@@ -5649,7 +5650,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>162</v>
+        <v>371</v>
       </c>
       <c r="B155" s="1">
         <v>950</v>
@@ -5661,7 +5662,7 @@
         <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F155">
         <v>154</v>
@@ -5672,7 +5673,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>163</v>
+        <v>372</v>
       </c>
       <c r="B156" s="1">
         <v>140</v>
@@ -5684,7 +5685,7 @@
         <v>300</v>
       </c>
       <c r="E156" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F156">
         <v>155</v>
@@ -5695,7 +5696,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="B157" s="1">
         <v>400</v>
@@ -5707,7 +5708,7 @@
         <v>50</v>
       </c>
       <c r="E157" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F157">
         <v>156</v>
@@ -5718,19 +5719,19 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>165</v>
+        <v>38</v>
       </c>
       <c r="B158" s="1">
         <v>620</v>
       </c>
       <c r="C158" s="1">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="D158">
         <v>30</v>
       </c>
       <c r="E158" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F158">
         <v>157</v>
@@ -5741,7 +5742,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>166</v>
+        <v>39</v>
       </c>
       <c r="B159" s="1">
         <v>3585</v>
@@ -5753,7 +5754,7 @@
         <v>12</v>
       </c>
       <c r="E159" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F159">
         <v>158</v>
@@ -5764,7 +5765,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>167</v>
+        <v>40</v>
       </c>
       <c r="B160" s="1">
         <v>1790</v>
@@ -5776,7 +5777,7 @@
         <v>12</v>
       </c>
       <c r="E160" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F160">
         <v>159</v>
@@ -5787,7 +5788,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="B161" s="1">
         <v>900</v>
@@ -5799,7 +5800,7 @@
         <v>12</v>
       </c>
       <c r="E161" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F161">
         <v>160</v>
@@ -5810,7 +5811,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
       <c r="B162" s="1">
         <v>450</v>
@@ -5822,7 +5823,7 @@
         <v>12</v>
       </c>
       <c r="E162" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F162">
         <v>161</v>
@@ -5833,7 +5834,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>170</v>
+        <v>373</v>
       </c>
       <c r="B163" s="1">
         <v>650</v>
@@ -5845,7 +5846,7 @@
         <v>36</v>
       </c>
       <c r="E163" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F163">
         <v>162</v>
@@ -5856,7 +5857,7 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>171</v>
+        <v>374</v>
       </c>
       <c r="B164" s="1">
         <v>799</v>
@@ -5868,7 +5869,7 @@
         <v>24</v>
       </c>
       <c r="E164" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F164">
         <v>163</v>
@@ -5879,7 +5880,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>172</v>
+        <v>375</v>
       </c>
       <c r="B165" s="1">
         <v>768</v>
@@ -5891,7 +5892,7 @@
         <v>24</v>
       </c>
       <c r="E165" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F165">
         <v>164</v>
@@ -5902,7 +5903,7 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>173</v>
+        <v>376</v>
       </c>
       <c r="B166" s="1">
         <v>870</v>
@@ -5914,7 +5915,7 @@
         <v>12</v>
       </c>
       <c r="E166" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F166">
         <v>165</v>
@@ -5925,7 +5926,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>174</v>
+        <v>377</v>
       </c>
       <c r="B167" s="1">
         <v>950</v>
@@ -5937,7 +5938,7 @@
         <v>12</v>
       </c>
       <c r="E167" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F167">
         <v>166</v>
@@ -5948,7 +5949,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="B168" s="1">
         <v>799</v>
@@ -5960,7 +5961,7 @@
         <v>24</v>
       </c>
       <c r="E168" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F168">
         <v>167</v>
@@ -5971,7 +5972,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>176</v>
+        <v>44</v>
       </c>
       <c r="B169" s="1">
         <v>500</v>
@@ -5983,7 +5984,7 @@
         <v>24</v>
       </c>
       <c r="E169" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F169">
         <v>168</v>
@@ -5994,7 +5995,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>177</v>
+        <v>378</v>
       </c>
       <c r="B170" s="1">
         <v>500</v>
@@ -6006,7 +6007,7 @@
         <v>24</v>
       </c>
       <c r="E170" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F170">
         <v>169</v>
@@ -6017,7 +6018,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>178</v>
+        <v>379</v>
       </c>
       <c r="B171" s="1">
         <v>4491</v>
@@ -6029,7 +6030,7 @@
         <v>3</v>
       </c>
       <c r="E171" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F171">
         <v>170</v>
@@ -6040,7 +6041,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>179</v>
+        <v>380</v>
       </c>
       <c r="B172" s="1">
         <v>2082</v>
@@ -6052,7 +6053,7 @@
         <v>6</v>
       </c>
       <c r="E172" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F172">
         <v>171</v>
@@ -6063,7 +6064,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>180</v>
+        <v>381</v>
       </c>
       <c r="B173" s="1">
         <v>3300</v>
@@ -6075,7 +6076,7 @@
         <v>6</v>
       </c>
       <c r="E173" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F173">
         <v>172</v>
@@ -6086,7 +6087,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>181</v>
+        <v>382</v>
       </c>
       <c r="B174" s="1">
         <v>7700</v>
@@ -6098,7 +6099,7 @@
         <v>6</v>
       </c>
       <c r="E174" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F174">
         <v>173</v>
@@ -6109,7 +6110,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>182</v>
+        <v>383</v>
       </c>
       <c r="B175" s="1">
         <v>2600</v>
@@ -6121,7 +6122,7 @@
         <v>3</v>
       </c>
       <c r="E175" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F175">
         <v>174</v>
@@ -6132,7 +6133,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>183</v>
+        <v>45</v>
       </c>
       <c r="B176" s="1">
         <v>375</v>
@@ -6144,7 +6145,7 @@
         <v>30</v>
       </c>
       <c r="E176" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F176">
         <v>175</v>
@@ -6155,7 +6156,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>184</v>
+        <v>46</v>
       </c>
       <c r="B177" s="1">
         <v>599</v>
@@ -6167,7 +6168,7 @@
         <v>20</v>
       </c>
       <c r="E177" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F177">
         <v>176</v>
@@ -6178,7 +6179,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>185</v>
+        <v>384</v>
       </c>
       <c r="B178" s="1">
         <v>8000</v>
@@ -6190,7 +6191,7 @@
         <v>3</v>
       </c>
       <c r="E178" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F178">
         <v>177</v>
@@ -6201,7 +6202,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>186</v>
+        <v>47</v>
       </c>
       <c r="B179" s="1">
         <v>1480</v>
@@ -6213,7 +6214,7 @@
         <v>3</v>
       </c>
       <c r="E179" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F179">
         <v>178</v>
@@ -6224,7 +6225,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>187</v>
+        <v>385</v>
       </c>
       <c r="B180" s="1">
         <v>1450</v>
@@ -6236,7 +6237,7 @@
         <v>6</v>
       </c>
       <c r="E180" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F180">
         <v>179</v>
@@ -6247,7 +6248,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>188</v>
+        <v>386</v>
       </c>
       <c r="B181" s="1">
         <v>3150</v>
@@ -6259,7 +6260,7 @@
         <v>3</v>
       </c>
       <c r="E181" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F181">
         <v>180</v>
@@ -6270,7 +6271,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>189</v>
+        <v>387</v>
       </c>
       <c r="B182" s="1">
         <v>8450</v>
@@ -6282,7 +6283,7 @@
         <v>2</v>
       </c>
       <c r="E182" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F182">
         <v>181</v>
@@ -6293,7 +6294,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
       <c r="B183" s="1">
         <v>7950</v>
@@ -6305,7 +6306,7 @@
         <v>3</v>
       </c>
       <c r="E183" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F183">
         <v>182</v>
@@ -6316,7 +6317,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>191</v>
+        <v>389</v>
       </c>
       <c r="B184" s="1">
         <v>6200</v>
@@ -6328,7 +6329,7 @@
         <v>3</v>
       </c>
       <c r="E184" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F184">
         <v>183</v>
@@ -6339,7 +6340,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>192</v>
+        <v>390</v>
       </c>
       <c r="B185" s="1">
         <v>350</v>
@@ -6351,7 +6352,7 @@
         <v>15</v>
       </c>
       <c r="E185" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F185">
         <v>184</v>
@@ -6362,7 +6363,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="B186" s="1">
         <v>9380</v>
@@ -6374,7 +6375,7 @@
         <v>2</v>
       </c>
       <c r="E186" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F186">
         <v>185</v>
@@ -6385,7 +6386,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>194</v>
+        <v>392</v>
       </c>
       <c r="B187" s="1">
         <v>670</v>
@@ -6397,7 +6398,7 @@
         <v>20</v>
       </c>
       <c r="E187" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F187">
         <v>186</v>
@@ -6408,7 +6409,7 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>195</v>
+        <v>393</v>
       </c>
       <c r="B188" s="1">
         <v>2250</v>
@@ -6420,7 +6421,7 @@
         <v>12</v>
       </c>
       <c r="E188" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F188">
         <v>187</v>
@@ -6431,7 +6432,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>196</v>
+        <v>394</v>
       </c>
       <c r="B189" s="1">
         <v>2250</v>
@@ -6443,7 +6444,7 @@
         <v>12</v>
       </c>
       <c r="E189" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F189">
         <v>188</v>
@@ -6454,7 +6455,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>197</v>
+        <v>48</v>
       </c>
       <c r="B190" s="1">
         <v>1725</v>
@@ -6466,7 +6467,7 @@
         <v>12</v>
       </c>
       <c r="E190" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F190">
         <v>189</v>
@@ -6477,7 +6478,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>198</v>
+        <v>49</v>
       </c>
       <c r="B191" s="1">
         <v>1725</v>
@@ -6489,7 +6490,7 @@
         <v>12</v>
       </c>
       <c r="E191" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F191">
         <v>190</v>
@@ -6500,7 +6501,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>199</v>
+        <v>395</v>
       </c>
       <c r="B192" s="1">
         <v>2950</v>
@@ -6512,7 +6513,7 @@
         <v>6</v>
       </c>
       <c r="E192" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F192">
         <v>191</v>
@@ -6523,7 +6524,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>200</v>
+        <v>396</v>
       </c>
       <c r="B193" s="1">
         <v>2950</v>
@@ -6535,7 +6536,7 @@
         <v>6</v>
       </c>
       <c r="E193" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F193">
         <v>192</v>
@@ -6546,7 +6547,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>201</v>
+        <v>397</v>
       </c>
       <c r="B194" s="1">
         <v>4185</v>
@@ -6558,7 +6559,7 @@
         <v>6</v>
       </c>
       <c r="E194" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F194">
         <v>193</v>
@@ -6569,7 +6570,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>202</v>
+        <v>398</v>
       </c>
       <c r="B195" s="1">
         <v>4185</v>
@@ -6581,7 +6582,7 @@
         <v>6</v>
       </c>
       <c r="E195" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F195">
         <v>194</v>
@@ -6592,7 +6593,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>203</v>
+        <v>50</v>
       </c>
       <c r="B196" s="1">
         <v>2990</v>
@@ -6604,7 +6605,7 @@
         <v>6</v>
       </c>
       <c r="E196" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F196">
         <v>195</v>
@@ -6615,7 +6616,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>204</v>
+        <v>51</v>
       </c>
       <c r="B197" s="1">
         <v>2990</v>
@@ -6627,7 +6628,7 @@
         <v>6</v>
       </c>
       <c r="E197" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F197">
         <v>196</v>
@@ -6638,7 +6639,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>205</v>
+        <v>52</v>
       </c>
       <c r="B198" s="1">
         <v>2990</v>
@@ -6650,7 +6651,7 @@
         <v>6</v>
       </c>
       <c r="E198" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F198">
         <v>197</v>
@@ -6661,7 +6662,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>205</v>
+        <v>52</v>
       </c>
       <c r="B199" s="1">
         <v>2990</v>
@@ -6673,7 +6674,7 @@
         <v>6</v>
       </c>
       <c r="E199" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F199">
         <v>198</v>
@@ -6684,7 +6685,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>206</v>
+        <v>53</v>
       </c>
       <c r="B200" s="1">
         <v>2900</v>
@@ -6696,7 +6697,7 @@
         <v>3</v>
       </c>
       <c r="E200" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F200">
         <v>199</v>
@@ -6707,7 +6708,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>207</v>
+        <v>54</v>
       </c>
       <c r="B201" s="1">
         <v>2100</v>
@@ -6719,7 +6720,7 @@
         <v>3</v>
       </c>
       <c r="E201" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F201">
         <v>200</v>
@@ -6730,7 +6731,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>208</v>
+        <v>55</v>
       </c>
       <c r="B202" s="1">
         <v>2220</v>
@@ -6742,7 +6743,7 @@
         <v>3</v>
       </c>
       <c r="E202" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F202">
         <v>201</v>
@@ -6753,7 +6754,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>209</v>
+        <v>56</v>
       </c>
       <c r="B203" s="1">
         <v>5900</v>
@@ -6765,7 +6766,7 @@
         <v>2</v>
       </c>
       <c r="E203" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F203">
         <v>202</v>
@@ -6776,7 +6777,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>210</v>
+        <v>399</v>
       </c>
       <c r="B204" s="1">
         <v>7250</v>
@@ -6788,7 +6789,7 @@
         <v>3</v>
       </c>
       <c r="E204" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F204">
         <v>203</v>
@@ -6799,7 +6800,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>211</v>
+        <v>57</v>
       </c>
       <c r="B205" s="1">
         <v>13975</v>
@@ -6811,7 +6812,7 @@
         <v>3</v>
       </c>
       <c r="E205" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F205">
         <v>204</v>
@@ -6822,7 +6823,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>212</v>
+        <v>58</v>
       </c>
       <c r="B206" s="1">
         <v>2230</v>
@@ -6834,7 +6835,7 @@
         <v>3</v>
       </c>
       <c r="E206" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F206">
         <v>205</v>
@@ -6845,7 +6846,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>213</v>
+        <v>59</v>
       </c>
       <c r="B207" s="1">
         <v>2170</v>
@@ -6857,7 +6858,7 @@
         <v>6</v>
       </c>
       <c r="E207" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F207">
         <v>206</v>
@@ -6868,7 +6869,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>214</v>
+        <v>400</v>
       </c>
       <c r="B208" s="1">
         <v>2280</v>
@@ -6880,7 +6881,7 @@
         <v>3</v>
       </c>
       <c r="E208" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F208">
         <v>207</v>
@@ -6891,7 +6892,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>215</v>
+        <v>60</v>
       </c>
       <c r="B209" s="1">
         <v>960</v>
@@ -6903,7 +6904,7 @@
         <v>3</v>
       </c>
       <c r="E209" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F209">
         <v>208</v>
@@ -6914,7 +6915,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>216</v>
+        <v>401</v>
       </c>
       <c r="B210" s="1">
         <v>380</v>
@@ -6926,7 +6927,7 @@
         <v>15</v>
       </c>
       <c r="E210" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F210">
         <v>209</v>
@@ -6937,7 +6938,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>217</v>
+        <v>61</v>
       </c>
       <c r="B211" s="1">
         <v>490</v>
@@ -6949,7 +6950,7 @@
         <v>6</v>
       </c>
       <c r="E211" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F211">
         <v>210</v>
@@ -6960,7 +6961,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>218</v>
+        <v>402</v>
       </c>
       <c r="B212" s="1">
         <v>1850</v>
@@ -6972,7 +6973,7 @@
         <v>6</v>
       </c>
       <c r="E212" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F212">
         <v>211</v>
@@ -6983,7 +6984,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>219</v>
+        <v>62</v>
       </c>
       <c r="B213" s="1">
         <v>1440</v>
@@ -6995,7 +6996,7 @@
         <v>6</v>
       </c>
       <c r="E213" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F213">
         <v>212</v>
@@ -7006,7 +7007,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>220</v>
+        <v>63</v>
       </c>
       <c r="B214" s="1">
         <v>2600</v>
@@ -7018,7 +7019,7 @@
         <v>6</v>
       </c>
       <c r="E214" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F214">
         <v>213</v>
@@ -7029,7 +7030,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>221</v>
+        <v>64</v>
       </c>
       <c r="B215" s="1">
         <v>5650</v>
@@ -7041,7 +7042,7 @@
         <v>6</v>
       </c>
       <c r="E215" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F215">
         <v>214</v>
@@ -7052,7 +7053,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>222</v>
+        <v>65</v>
       </c>
       <c r="B216" s="1">
         <v>430</v>
@@ -7064,7 +7065,7 @@
         <v>6</v>
       </c>
       <c r="E216" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F216">
         <v>215</v>
@@ -7075,7 +7076,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>223</v>
+        <v>403</v>
       </c>
       <c r="B217" s="1">
         <v>750</v>
@@ -7087,7 +7088,7 @@
         <v>6</v>
       </c>
       <c r="E217" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F217">
         <v>216</v>
@@ -7098,7 +7099,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>224</v>
+        <v>66</v>
       </c>
       <c r="B218" s="1">
         <v>12500</v>
@@ -7110,7 +7111,7 @@
         <v>2</v>
       </c>
       <c r="E218" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F218">
         <v>217</v>
@@ -7121,7 +7122,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>225</v>
+        <v>67</v>
       </c>
       <c r="B219" s="1">
         <v>4830</v>
@@ -7133,7 +7134,7 @@
         <v>6</v>
       </c>
       <c r="E219" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F219">
         <v>218</v>
@@ -7144,7 +7145,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>226</v>
+        <v>68</v>
       </c>
       <c r="B220" s="1">
         <v>4830</v>
@@ -7156,7 +7157,7 @@
         <v>6</v>
       </c>
       <c r="E220" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F220">
         <v>219</v>
@@ -7167,7 +7168,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>227</v>
+        <v>69</v>
       </c>
       <c r="B221" s="1">
         <v>8890</v>
@@ -7179,7 +7180,7 @@
         <v>6</v>
       </c>
       <c r="E221" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F221">
         <v>220</v>
@@ -7190,7 +7191,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>228</v>
+        <v>70</v>
       </c>
       <c r="B222" s="1">
         <v>2700</v>
@@ -7202,7 +7203,7 @@
         <v>6</v>
       </c>
       <c r="E222" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F222">
         <v>221</v>
@@ -7213,7 +7214,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>229</v>
+        <v>71</v>
       </c>
       <c r="B223" s="1">
         <v>5600</v>
@@ -7225,7 +7226,7 @@
         <v>3</v>
       </c>
       <c r="E223" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F223">
         <v>222</v>
@@ -7236,7 +7237,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>230</v>
+        <v>72</v>
       </c>
       <c r="B224" s="1">
         <v>5600</v>
@@ -7248,7 +7249,7 @@
         <v>3</v>
       </c>
       <c r="E224" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F224">
         <v>223</v>
@@ -7259,7 +7260,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>231</v>
+        <v>73</v>
       </c>
       <c r="B225" s="1">
         <v>5600</v>
@@ -7271,7 +7272,7 @@
         <v>3</v>
       </c>
       <c r="E225" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F225">
         <v>224</v>
@@ -7282,7 +7283,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>232</v>
+        <v>74</v>
       </c>
       <c r="B226" s="1">
         <v>5600</v>
@@ -7294,7 +7295,7 @@
         <v>3</v>
       </c>
       <c r="E226" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F226">
         <v>225</v>
@@ -7305,7 +7306,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>233</v>
+        <v>75</v>
       </c>
       <c r="B227" s="1">
         <v>1960</v>
@@ -7317,7 +7318,7 @@
         <v>12</v>
       </c>
       <c r="E227" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F227">
         <v>226</v>
@@ -7328,7 +7329,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="B228" s="1">
         <v>1170</v>
@@ -7340,7 +7341,7 @@
         <v>10</v>
       </c>
       <c r="E228" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F228">
         <v>227</v>
@@ -7351,7 +7352,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="B229" s="1">
         <v>1170</v>
@@ -7363,7 +7364,7 @@
         <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F229">
         <v>228</v>
@@ -7374,7 +7375,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="B230" s="1">
         <v>1170</v>
@@ -7386,7 +7387,7 @@
         <v>10</v>
       </c>
       <c r="E230" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F230">
         <v>229</v>
@@ -7397,7 +7398,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>237</v>
+        <v>79</v>
       </c>
       <c r="B231" s="1">
         <v>1170</v>
@@ -7409,7 +7410,7 @@
         <v>10</v>
       </c>
       <c r="E231" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F231">
         <v>230</v>
@@ -7420,7 +7421,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>238</v>
+        <v>80</v>
       </c>
       <c r="B232" s="1">
         <v>1170</v>
@@ -7432,7 +7433,7 @@
         <v>10</v>
       </c>
       <c r="E232" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F232">
         <v>231</v>
@@ -7443,7 +7444,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="B233" s="1">
         <v>772</v>
@@ -7455,7 +7456,7 @@
         <v>24</v>
       </c>
       <c r="E233" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F233">
         <v>232</v>
@@ -7466,7 +7467,7 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="B234" s="1">
         <v>650</v>
@@ -7478,7 +7479,7 @@
         <v>12</v>
       </c>
       <c r="E234" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F234">
         <v>233</v>
@@ -7489,7 +7490,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>241</v>
+        <v>83</v>
       </c>
       <c r="B235" s="1">
         <v>390</v>
@@ -7501,7 +7502,7 @@
         <v>12</v>
       </c>
       <c r="E235" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F235">
         <v>234</v>
@@ -7512,7 +7513,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>242</v>
+        <v>84</v>
       </c>
       <c r="B236" s="1">
         <v>405</v>
@@ -7524,7 +7525,7 @@
         <v>12</v>
       </c>
       <c r="E236" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F236">
         <v>235</v>
@@ -7535,7 +7536,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
-        <v>243</v>
+        <v>85</v>
       </c>
       <c r="B237" s="1">
         <v>438</v>
@@ -7547,7 +7548,7 @@
         <v>12</v>
       </c>
       <c r="E237" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F237">
         <v>236</v>
@@ -7558,7 +7559,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>244</v>
+        <v>86</v>
       </c>
       <c r="B238" s="1">
         <v>700</v>
@@ -7570,7 +7571,7 @@
         <v>6</v>
       </c>
       <c r="E238" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F238">
         <v>237</v>
@@ -7581,7 +7582,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>245</v>
+        <v>87</v>
       </c>
       <c r="B239" s="1">
         <v>2530</v>
@@ -7593,7 +7594,7 @@
         <v>6</v>
       </c>
       <c r="E239" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F239">
         <v>238</v>
@@ -7604,7 +7605,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>246</v>
+        <v>88</v>
       </c>
       <c r="B240" s="1">
         <v>4900</v>
@@ -7616,7 +7617,7 @@
         <v>3</v>
       </c>
       <c r="E240" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F240">
         <v>239</v>
@@ -7627,7 +7628,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>247</v>
+        <v>89</v>
       </c>
       <c r="B241" s="1">
         <v>2950</v>
@@ -7639,7 +7640,7 @@
         <v>2</v>
       </c>
       <c r="E241" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F241">
         <v>240</v>
@@ -7650,7 +7651,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>248</v>
+        <v>90</v>
       </c>
       <c r="B242" s="1">
         <v>1440</v>
@@ -7662,7 +7663,7 @@
         <v>6</v>
       </c>
       <c r="E242" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F242">
         <v>241</v>
@@ -7673,7 +7674,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>249</v>
+        <v>91</v>
       </c>
       <c r="B243" s="1">
         <v>3500</v>
@@ -7685,7 +7686,7 @@
         <v>6</v>
       </c>
       <c r="E243" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F243">
         <v>242</v>
@@ -7696,7 +7697,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>250</v>
+        <v>92</v>
       </c>
       <c r="B244" s="1">
         <v>762</v>
@@ -7708,7 +7709,7 @@
         <v>12</v>
       </c>
       <c r="E244" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F244">
         <v>243</v>
@@ -7719,7 +7720,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>251</v>
+        <v>93</v>
       </c>
       <c r="B245" s="1">
         <v>1650</v>
@@ -7731,7 +7732,7 @@
         <v>8</v>
       </c>
       <c r="E245" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F245">
         <v>244</v>
@@ -7742,7 +7743,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>252</v>
+        <v>94</v>
       </c>
       <c r="B246" s="1">
         <v>709</v>
@@ -7754,7 +7755,7 @@
         <v>24</v>
       </c>
       <c r="E246" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F246">
         <v>245</v>
@@ -7765,7 +7766,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="B247" s="1">
         <v>50600</v>
@@ -7777,7 +7778,7 @@
         <v>2</v>
       </c>
       <c r="E247" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F247">
         <v>246</v>
@@ -7788,7 +7789,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="B248" s="1">
         <v>430</v>
@@ -7800,7 +7801,7 @@
         <v>6</v>
       </c>
       <c r="E248" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F248">
         <v>247</v>
@@ -7811,7 +7812,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>255</v>
+        <v>97</v>
       </c>
       <c r="B249" s="1">
         <v>1700</v>
@@ -7823,7 +7824,7 @@
         <v>6</v>
       </c>
       <c r="E249" t="s">
-        <v>9</v>
+        <v>245</v>
       </c>
       <c r="F249">
         <v>248</v>
@@ -7834,7 +7835,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>256</v>
+        <v>98</v>
       </c>
       <c r="B250" s="1">
         <v>1700</v>
@@ -7846,7 +7847,7 @@
         <v>6</v>
       </c>
       <c r="E250" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F250">
         <v>249</v>
@@ -7857,7 +7858,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>258</v>
+        <v>99</v>
       </c>
       <c r="B251" s="1">
         <v>740</v>
@@ -7869,7 +7870,7 @@
         <v>12</v>
       </c>
       <c r="E251" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F251">
         <v>250</v>
@@ -7880,7 +7881,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>259</v>
+        <v>100</v>
       </c>
       <c r="B252" s="1">
         <v>740</v>
@@ -7892,7 +7893,7 @@
         <v>12</v>
       </c>
       <c r="E252" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F252">
         <v>251</v>
@@ -7903,7 +7904,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>260</v>
+        <v>101</v>
       </c>
       <c r="B253" s="1">
         <v>740</v>
@@ -7915,7 +7916,7 @@
         <v>12</v>
       </c>
       <c r="E253" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F253">
         <v>252</v>
@@ -7926,7 +7927,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="B254" s="1">
         <v>7800</v>
@@ -7938,7 +7939,7 @@
         <v>6</v>
       </c>
       <c r="E254" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F254">
         <v>253</v>
@@ -7949,7 +7950,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>262</v>
+        <v>103</v>
       </c>
       <c r="B255" s="1">
         <v>5400</v>
@@ -7961,7 +7962,7 @@
         <v>6</v>
       </c>
       <c r="E255" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F255">
         <v>254</v>
@@ -7972,7 +7973,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>263</v>
+        <v>104</v>
       </c>
       <c r="B256" s="1">
         <v>1460</v>
@@ -7984,7 +7985,7 @@
         <v>12</v>
       </c>
       <c r="E256" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F256">
         <v>255</v>
@@ -7995,7 +7996,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>264</v>
+        <v>105</v>
       </c>
       <c r="B257" s="1">
         <v>7800</v>
@@ -8007,7 +8008,7 @@
         <v>6</v>
       </c>
       <c r="E257" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F257">
         <v>256</v>
@@ -8018,7 +8019,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>265</v>
+        <v>106</v>
       </c>
       <c r="B258" s="1">
         <v>5400</v>
@@ -8030,7 +8031,7 @@
         <v>6</v>
       </c>
       <c r="E258" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F258">
         <v>257</v>
@@ -8041,7 +8042,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>266</v>
+        <v>107</v>
       </c>
       <c r="B259" s="1">
         <v>1460</v>
@@ -8053,7 +8054,7 @@
         <v>12</v>
       </c>
       <c r="E259" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F259">
         <v>258</v>
@@ -8064,7 +8065,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
-        <v>267</v>
+        <v>108</v>
       </c>
       <c r="B260" s="1">
         <v>1380</v>
@@ -8076,7 +8077,7 @@
         <v>12</v>
       </c>
       <c r="E260" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F260">
         <v>259</v>
@@ -8087,7 +8088,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
-        <v>268</v>
+        <v>109</v>
       </c>
       <c r="B261" s="1">
         <v>1380</v>
@@ -8099,7 +8100,7 @@
         <v>12</v>
       </c>
       <c r="E261" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F261">
         <v>260</v>
@@ -8110,7 +8111,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>269</v>
+        <v>110</v>
       </c>
       <c r="B262" s="1">
         <v>1380</v>
@@ -8122,7 +8123,7 @@
         <v>12</v>
       </c>
       <c r="E262" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F262">
         <v>261</v>
@@ -8133,7 +8134,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>270</v>
+        <v>111</v>
       </c>
       <c r="B263" s="1">
         <v>3780</v>
@@ -8145,7 +8146,7 @@
         <v>12</v>
       </c>
       <c r="E263" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F263">
         <v>262</v>
@@ -8156,7 +8157,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>271</v>
+        <v>112</v>
       </c>
       <c r="B264" s="1">
         <v>9600</v>
@@ -8168,7 +8169,7 @@
         <v>6</v>
       </c>
       <c r="E264" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F264">
         <v>263</v>
@@ -8179,7 +8180,7 @@
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>272</v>
+        <v>113</v>
       </c>
       <c r="B265" s="1">
         <v>1890</v>
@@ -8191,7 +8192,7 @@
         <v>12</v>
       </c>
       <c r="E265" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F265">
         <v>264</v>
@@ -8202,7 +8203,7 @@
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>273</v>
+        <v>114</v>
       </c>
       <c r="B266" s="1">
         <v>1550</v>
@@ -8214,7 +8215,7 @@
         <v>12</v>
       </c>
       <c r="E266" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F266">
         <v>265</v>
@@ -8225,7 +8226,7 @@
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="B267" s="1">
         <v>1550</v>
@@ -8237,7 +8238,7 @@
         <v>12</v>
       </c>
       <c r="E267" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F267">
         <v>266</v>
@@ -8248,7 +8249,7 @@
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="B268" s="1">
         <v>1550</v>
@@ -8260,7 +8261,7 @@
         <v>12</v>
       </c>
       <c r="E268" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F268">
         <v>267</v>
@@ -8271,7 +8272,7 @@
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>276</v>
+        <v>117</v>
       </c>
       <c r="B269" s="1">
         <v>1550</v>
@@ -8283,7 +8284,7 @@
         <v>12</v>
       </c>
       <c r="E269" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F269">
         <v>268</v>
@@ -8294,7 +8295,7 @@
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>277</v>
+        <v>118</v>
       </c>
       <c r="B270" s="1">
         <v>5800</v>
@@ -8306,7 +8307,7 @@
         <v>6</v>
       </c>
       <c r="E270" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F270">
         <v>269</v>
@@ -8317,7 +8318,7 @@
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>278</v>
+        <v>119</v>
       </c>
       <c r="B271" s="1">
         <v>5800</v>
@@ -8329,7 +8330,7 @@
         <v>6</v>
       </c>
       <c r="E271" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F271">
         <v>270</v>
@@ -8340,7 +8341,7 @@
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>279</v>
+        <v>120</v>
       </c>
       <c r="B272" s="1">
         <v>5800</v>
@@ -8352,7 +8353,7 @@
         <v>6</v>
       </c>
       <c r="E272" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F272">
         <v>271</v>
@@ -8363,7 +8364,7 @@
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>280</v>
+        <v>121</v>
       </c>
       <c r="B273" s="1">
         <v>5800</v>
@@ -8375,7 +8376,7 @@
         <v>6</v>
       </c>
       <c r="E273" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F273">
         <v>272</v>
@@ -8386,7 +8387,7 @@
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>281</v>
+        <v>122</v>
       </c>
       <c r="B274" s="1">
         <v>5800</v>
@@ -8398,7 +8399,7 @@
         <v>6</v>
       </c>
       <c r="E274" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F274">
         <v>273</v>
@@ -8409,7 +8410,7 @@
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>282</v>
+        <v>123</v>
       </c>
       <c r="B275" s="1">
         <v>5800</v>
@@ -8421,7 +8422,7 @@
         <v>6</v>
       </c>
       <c r="E275" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F275">
         <v>274</v>
@@ -8432,7 +8433,7 @@
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>283</v>
+        <v>124</v>
       </c>
       <c r="B276" s="1">
         <v>5800</v>
@@ -8444,7 +8445,7 @@
         <v>6</v>
       </c>
       <c r="E276" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F276">
         <v>275</v>
@@ -8455,7 +8456,7 @@
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>284</v>
+        <v>125</v>
       </c>
       <c r="B277" s="1">
         <v>5800</v>
@@ -8467,7 +8468,7 @@
         <v>2</v>
       </c>
       <c r="E277" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F277">
         <v>276</v>
@@ -8478,7 +8479,7 @@
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>285</v>
+        <v>126</v>
       </c>
       <c r="B278" s="1">
         <v>5800</v>
@@ -8490,7 +8491,7 @@
         <v>6</v>
       </c>
       <c r="E278" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F278">
         <v>277</v>
@@ -8501,7 +8502,7 @@
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>286</v>
+        <v>127</v>
       </c>
       <c r="B279" s="1">
         <v>5800</v>
@@ -8513,7 +8514,7 @@
         <v>6</v>
       </c>
       <c r="E279" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F279">
         <v>278</v>
@@ -8524,7 +8525,7 @@
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>287</v>
+        <v>128</v>
       </c>
       <c r="B280" s="1">
         <v>4000</v>
@@ -8536,7 +8537,7 @@
         <v>6</v>
       </c>
       <c r="E280" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F280">
         <v>279</v>
@@ -8547,7 +8548,7 @@
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>288</v>
+        <v>129</v>
       </c>
       <c r="B281" s="1">
         <v>4000</v>
@@ -8559,7 +8560,7 @@
         <v>6</v>
       </c>
       <c r="E281" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F281">
         <v>280</v>
@@ -8570,7 +8571,7 @@
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>289</v>
+        <v>130</v>
       </c>
       <c r="B282" s="1">
         <v>1980</v>
@@ -8582,7 +8583,7 @@
         <v>12</v>
       </c>
       <c r="E282" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F282">
         <v>281</v>
@@ -8593,7 +8594,7 @@
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>290</v>
+        <v>131</v>
       </c>
       <c r="B283" s="1">
         <v>380</v>
@@ -8605,7 +8606,7 @@
         <v>24</v>
       </c>
       <c r="E283" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F283">
         <v>282</v>
@@ -8616,7 +8617,7 @@
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>291</v>
+        <v>132</v>
       </c>
       <c r="B284" s="1">
         <v>300</v>
@@ -8628,7 +8629,7 @@
         <v>24</v>
       </c>
       <c r="E284" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F284">
         <v>283</v>
@@ -8639,7 +8640,7 @@
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>292</v>
+        <v>133</v>
       </c>
       <c r="B285" s="1">
         <v>4700</v>
@@ -8651,7 +8652,7 @@
         <v>10</v>
       </c>
       <c r="E285" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F285">
         <v>284</v>
@@ -8662,7 +8663,7 @@
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>293</v>
+        <v>134</v>
       </c>
       <c r="B286" s="1">
         <v>960</v>
@@ -8674,7 +8675,7 @@
         <v>10</v>
       </c>
       <c r="E286" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F286">
         <v>285</v>
@@ -8685,7 +8686,7 @@
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>294</v>
+        <v>135</v>
       </c>
       <c r="B287" s="1">
         <v>1800</v>
@@ -8697,7 +8698,7 @@
         <v>12</v>
       </c>
       <c r="E287" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F287">
         <v>286</v>
@@ -8708,7 +8709,7 @@
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>295</v>
+        <v>136</v>
       </c>
       <c r="B288" s="1">
         <v>5800</v>
@@ -8720,7 +8721,7 @@
         <v>6</v>
       </c>
       <c r="E288" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F288">
         <v>287</v>
@@ -8731,7 +8732,7 @@
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="B289" s="1">
         <v>5800</v>
@@ -8743,7 +8744,7 @@
         <v>6</v>
       </c>
       <c r="E289" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F289">
         <v>288</v>
@@ -8754,7 +8755,7 @@
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>297</v>
+        <v>138</v>
       </c>
       <c r="B290" s="1">
         <v>4500</v>
@@ -8766,7 +8767,7 @@
         <v>10</v>
       </c>
       <c r="E290" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F290">
         <v>289</v>
@@ -8777,7 +8778,7 @@
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>298</v>
+        <v>139</v>
       </c>
       <c r="B291" s="1">
         <v>720</v>
@@ -8789,7 +8790,7 @@
         <v>12</v>
       </c>
       <c r="E291" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F291">
         <v>290</v>
@@ -8800,7 +8801,7 @@
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>299</v>
+        <v>140</v>
       </c>
       <c r="B292" s="1">
         <v>980</v>
@@ -8812,7 +8813,7 @@
         <v>12</v>
       </c>
       <c r="E292" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F292">
         <v>291</v>
@@ -8823,7 +8824,7 @@
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>300</v>
+        <v>141</v>
       </c>
       <c r="B293" s="1">
         <v>1100</v>
@@ -8835,7 +8836,7 @@
         <v>12</v>
       </c>
       <c r="E293" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F293">
         <v>292</v>
@@ -8846,7 +8847,7 @@
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>301</v>
+        <v>142</v>
       </c>
       <c r="B294" s="1">
         <v>1600</v>
@@ -8858,7 +8859,7 @@
         <v>12</v>
       </c>
       <c r="E294" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F294">
         <v>293</v>
@@ -8869,7 +8870,7 @@
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>302</v>
+        <v>143</v>
       </c>
       <c r="B295" s="1">
         <v>2400</v>
@@ -8881,7 +8882,7 @@
         <v>12</v>
       </c>
       <c r="E295" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F295">
         <v>294</v>
@@ -8892,7 +8893,7 @@
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>303</v>
+        <v>144</v>
       </c>
       <c r="B296" s="1">
         <v>2400</v>
@@ -8904,7 +8905,7 @@
         <v>12</v>
       </c>
       <c r="E296" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F296">
         <v>295</v>
@@ -8915,7 +8916,7 @@
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>304</v>
+        <v>145</v>
       </c>
       <c r="B297" s="1">
         <v>3900</v>
@@ -8927,7 +8928,7 @@
         <v>6</v>
       </c>
       <c r="E297" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F297">
         <v>296</v>
@@ -8938,7 +8939,7 @@
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>305</v>
+        <v>146</v>
       </c>
       <c r="B298" s="1">
         <v>3900</v>
@@ -8950,7 +8951,7 @@
         <v>6</v>
       </c>
       <c r="E298" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F298">
         <v>297</v>
@@ -8961,7 +8962,7 @@
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>306</v>
+        <v>147</v>
       </c>
       <c r="B299" s="1">
         <v>3900</v>
@@ -8973,7 +8974,7 @@
         <v>6</v>
       </c>
       <c r="E299" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F299">
         <v>298</v>
@@ -8984,7 +8985,7 @@
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>307</v>
+        <v>148</v>
       </c>
       <c r="B300" s="1">
         <v>3900</v>
@@ -8996,7 +8997,7 @@
         <v>6</v>
       </c>
       <c r="E300" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F300">
         <v>299</v>
@@ -9007,7 +9008,7 @@
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
       <c r="B301" s="1">
         <v>3900</v>
@@ -9019,7 +9020,7 @@
         <v>6</v>
       </c>
       <c r="E301" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F301">
         <v>300</v>
@@ -9030,7 +9031,7 @@
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>309</v>
+        <v>150</v>
       </c>
       <c r="B302" s="1">
         <v>1100</v>
@@ -9042,7 +9043,7 @@
         <v>12</v>
       </c>
       <c r="E302" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F302">
         <v>301</v>
@@ -9053,7 +9054,7 @@
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
-        <v>310</v>
+        <v>151</v>
       </c>
       <c r="B303" s="1">
         <v>3900</v>
@@ -9065,7 +9066,7 @@
         <v>6</v>
       </c>
       <c r="E303" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F303">
         <v>302</v>
@@ -9076,7 +9077,7 @@
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
-        <v>311</v>
+        <v>152</v>
       </c>
       <c r="B304" s="1">
         <v>3900</v>
@@ -9088,7 +9089,7 @@
         <v>6</v>
       </c>
       <c r="E304" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F304">
         <v>303</v>
@@ -9099,7 +9100,7 @@
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>312</v>
+        <v>153</v>
       </c>
       <c r="B305" s="1">
         <v>3900</v>
@@ -9111,7 +9112,7 @@
         <v>6</v>
       </c>
       <c r="E305" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F305">
         <v>304</v>
@@ -9122,7 +9123,7 @@
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>313</v>
+        <v>154</v>
       </c>
       <c r="B306" s="1">
         <v>3900</v>
@@ -9134,7 +9135,7 @@
         <v>6</v>
       </c>
       <c r="E306" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F306">
         <v>305</v>
@@ -9145,7 +9146,7 @@
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
       <c r="B307" s="1">
         <v>3900</v>
@@ -9157,7 +9158,7 @@
         <v>6</v>
       </c>
       <c r="E307" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F307">
         <v>306</v>
@@ -9168,7 +9169,7 @@
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>315</v>
+        <v>156</v>
       </c>
       <c r="B308" s="1">
         <v>1100</v>
@@ -9180,7 +9181,7 @@
         <v>12</v>
       </c>
       <c r="E308" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F308">
         <v>307</v>
@@ -9191,7 +9192,7 @@
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>316</v>
+        <v>157</v>
       </c>
       <c r="B309" s="1">
         <v>640</v>
@@ -9203,7 +9204,7 @@
         <v>50</v>
       </c>
       <c r="E309" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F309">
         <v>308</v>
@@ -9214,7 +9215,7 @@
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
       <c r="B310" s="1">
         <v>1700</v>
@@ -9226,7 +9227,7 @@
         <v>12</v>
       </c>
       <c r="E310" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F310">
         <v>309</v>
@@ -9237,7 +9238,7 @@
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>318</v>
+        <v>159</v>
       </c>
       <c r="B311" s="1">
         <v>1700</v>
@@ -9249,7 +9250,7 @@
         <v>12</v>
       </c>
       <c r="E311" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F311">
         <v>310</v>
@@ -9260,7 +9261,7 @@
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>319</v>
+        <v>160</v>
       </c>
       <c r="B312" s="1">
         <v>1700</v>
@@ -9272,7 +9273,7 @@
         <v>12</v>
       </c>
       <c r="E312" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F312">
         <v>311</v>
@@ -9283,7 +9284,7 @@
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>320</v>
+        <v>161</v>
       </c>
       <c r="B313" s="1">
         <v>1860</v>
@@ -9295,7 +9296,7 @@
         <v>10</v>
       </c>
       <c r="E313" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F313">
         <v>312</v>
@@ -9306,7 +9307,7 @@
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>321</v>
+        <v>162</v>
       </c>
       <c r="B314" s="1">
         <v>1860</v>
@@ -9318,7 +9319,7 @@
         <v>10</v>
       </c>
       <c r="E314" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F314">
         <v>313</v>
@@ -9329,7 +9330,7 @@
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>322</v>
+        <v>163</v>
       </c>
       <c r="B315" s="1">
         <v>1860</v>
@@ -9341,7 +9342,7 @@
         <v>10</v>
       </c>
       <c r="E315" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F315">
         <v>314</v>
@@ -9352,7 +9353,7 @@
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>323</v>
+        <v>164</v>
       </c>
       <c r="B316" s="1">
         <v>1860</v>
@@ -9364,7 +9365,7 @@
         <v>10</v>
       </c>
       <c r="E316" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F316">
         <v>315</v>
@@ -9375,7 +9376,7 @@
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="B317" s="1">
         <v>1860</v>
@@ -9387,7 +9388,7 @@
         <v>10</v>
       </c>
       <c r="E317" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F317">
         <v>316</v>
@@ -9398,7 +9399,7 @@
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>325</v>
+        <v>166</v>
       </c>
       <c r="B318" s="1">
         <v>1700</v>
@@ -9410,7 +9411,7 @@
         <v>12</v>
       </c>
       <c r="E318" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F318">
         <v>317</v>
@@ -9421,7 +9422,7 @@
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>326</v>
+        <v>167</v>
       </c>
       <c r="B319" s="1">
         <v>64</v>
@@ -9433,7 +9434,7 @@
         <v>200</v>
       </c>
       <c r="E319" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F319">
         <v>318</v>
@@ -9444,7 +9445,7 @@
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>327</v>
+        <v>168</v>
       </c>
       <c r="B320" s="1">
         <v>1100</v>
@@ -9456,7 +9457,7 @@
         <v>10</v>
       </c>
       <c r="E320" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F320">
         <v>319</v>
@@ -9467,7 +9468,7 @@
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>328</v>
+        <v>169</v>
       </c>
       <c r="B321" s="1">
         <v>1100</v>
@@ -9479,7 +9480,7 @@
         <v>10</v>
       </c>
       <c r="E321" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F321">
         <v>320</v>
@@ -9490,7 +9491,7 @@
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>329</v>
+        <v>170</v>
       </c>
       <c r="B322" s="1">
         <v>18000</v>
@@ -9502,7 +9503,7 @@
         <v>2</v>
       </c>
       <c r="E322" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F322">
         <v>321</v>
@@ -9513,7 +9514,7 @@
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>330</v>
+        <v>171</v>
       </c>
       <c r="B323" s="1">
         <v>1980</v>
@@ -9525,7 +9526,7 @@
         <v>10</v>
       </c>
       <c r="E323" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F323">
         <v>322</v>
@@ -9536,7 +9537,7 @@
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>331</v>
+        <v>172</v>
       </c>
       <c r="B324" s="1">
         <v>400</v>
@@ -9548,7 +9549,7 @@
         <v>50</v>
       </c>
       <c r="E324" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F324">
         <v>323</v>
@@ -9559,7 +9560,7 @@
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>332</v>
+        <v>173</v>
       </c>
       <c r="B325" s="1">
         <v>840</v>
@@ -9571,7 +9572,7 @@
         <v>12</v>
       </c>
       <c r="E325" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F325">
         <v>324</v>
@@ -9582,7 +9583,7 @@
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>333</v>
+        <v>174</v>
       </c>
       <c r="B326" s="1">
         <v>1300</v>
@@ -9594,7 +9595,7 @@
         <v>12</v>
       </c>
       <c r="E326" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F326">
         <v>325</v>
@@ -9605,7 +9606,7 @@
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>334</v>
+        <v>175</v>
       </c>
       <c r="B327" s="1">
         <v>3900</v>
@@ -9617,7 +9618,7 @@
         <v>6</v>
       </c>
       <c r="E327" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F327">
         <v>326</v>
@@ -9628,7 +9629,7 @@
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>335</v>
+        <v>176</v>
       </c>
       <c r="B328" s="1">
         <v>3900</v>
@@ -9640,7 +9641,7 @@
         <v>6</v>
       </c>
       <c r="E328" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F328">
         <v>327</v>
@@ -9651,7 +9652,7 @@
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>336</v>
+        <v>177</v>
       </c>
       <c r="B329" s="1">
         <v>1100</v>
@@ -9663,7 +9664,7 @@
         <v>12</v>
       </c>
       <c r="E329" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F329">
         <v>328</v>
@@ -9674,7 +9675,7 @@
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>337</v>
+        <v>178</v>
       </c>
       <c r="B330" s="1">
         <v>1100</v>
@@ -9686,7 +9687,7 @@
         <v>12</v>
       </c>
       <c r="E330" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F330">
         <v>329</v>
@@ -9697,7 +9698,7 @@
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>338</v>
+        <v>179</v>
       </c>
       <c r="B331" s="1">
         <v>1100</v>
@@ -9709,7 +9710,7 @@
         <v>12</v>
       </c>
       <c r="E331" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F331">
         <v>330</v>
@@ -9720,7 +9721,7 @@
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>339</v>
+        <v>180</v>
       </c>
       <c r="B332" s="1">
         <v>1100</v>
@@ -9732,7 +9733,7 @@
         <v>12</v>
       </c>
       <c r="E332" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F332">
         <v>331</v>
@@ -9743,7 +9744,7 @@
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>340</v>
+        <v>181</v>
       </c>
       <c r="B333" s="1">
         <v>1100</v>
@@ -9755,7 +9756,7 @@
         <v>12</v>
       </c>
       <c r="E333" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F333">
         <v>332</v>
@@ -9766,7 +9767,7 @@
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>341</v>
+        <v>182</v>
       </c>
       <c r="B334" s="1">
         <v>1100</v>
@@ -9778,7 +9779,7 @@
         <v>12</v>
       </c>
       <c r="E334" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F334">
         <v>333</v>
@@ -9789,7 +9790,7 @@
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>342</v>
+        <v>183</v>
       </c>
       <c r="B335" s="1">
         <v>1100</v>
@@ -9801,7 +9802,7 @@
         <v>12</v>
       </c>
       <c r="E335" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F335">
         <v>334</v>
@@ -9812,7 +9813,7 @@
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>343</v>
+        <v>184</v>
       </c>
       <c r="B336" s="1">
         <v>1100</v>
@@ -9824,7 +9825,7 @@
         <v>12</v>
       </c>
       <c r="E336" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F336">
         <v>335</v>
@@ -9835,7 +9836,7 @@
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>344</v>
+        <v>185</v>
       </c>
       <c r="B337" s="1">
         <v>1100</v>
@@ -9847,7 +9848,7 @@
         <v>12</v>
       </c>
       <c r="E337" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F337">
         <v>336</v>
@@ -9858,7 +9859,7 @@
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>345</v>
+        <v>186</v>
       </c>
       <c r="B338" s="1">
         <v>1100</v>
@@ -9870,7 +9871,7 @@
         <v>12</v>
       </c>
       <c r="E338" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F338">
         <v>337</v>
@@ -9881,7 +9882,7 @@
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>346</v>
+        <v>187</v>
       </c>
       <c r="B339" s="1">
         <v>1100</v>
@@ -9893,7 +9894,7 @@
         <v>12</v>
       </c>
       <c r="E339" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F339">
         <v>338</v>
@@ -9904,7 +9905,7 @@
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>347</v>
+        <v>188</v>
       </c>
       <c r="B340" s="1">
         <v>1550</v>
@@ -9916,7 +9917,7 @@
         <v>12</v>
       </c>
       <c r="E340" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F340">
         <v>339</v>
@@ -9927,7 +9928,7 @@
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>348</v>
+        <v>189</v>
       </c>
       <c r="B341" s="1">
         <v>15400</v>
@@ -9939,7 +9940,7 @@
         <v>2</v>
       </c>
       <c r="E341" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F341">
         <v>340</v>
@@ -9950,7 +9951,7 @@
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>349</v>
+        <v>190</v>
       </c>
       <c r="B342" s="1">
         <v>15600</v>
@@ -9962,7 +9963,7 @@
         <v>6</v>
       </c>
       <c r="E342" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F342">
         <v>341</v>
@@ -9973,7 +9974,7 @@
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>350</v>
+        <v>191</v>
       </c>
       <c r="B343" s="1">
         <v>700</v>
@@ -9985,7 +9986,7 @@
         <v>12</v>
       </c>
       <c r="E343" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F343">
         <v>342</v>
@@ -9996,7 +9997,7 @@
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="B344" s="1">
         <v>1260</v>
@@ -10008,7 +10009,7 @@
         <v>20</v>
       </c>
       <c r="E344" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F344">
         <v>343</v>
@@ -10019,7 +10020,7 @@
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>352</v>
+        <v>193</v>
       </c>
       <c r="B345" s="1">
         <v>1260</v>
@@ -10031,7 +10032,7 @@
         <v>20</v>
       </c>
       <c r="E345" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F345">
         <v>344</v>
@@ -10042,7 +10043,7 @@
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>353</v>
+        <v>194</v>
       </c>
       <c r="B346" s="1">
         <v>2480</v>
@@ -10054,7 +10055,7 @@
         <v>12</v>
       </c>
       <c r="E346" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F346">
         <v>345</v>
@@ -10065,7 +10066,7 @@
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>354</v>
+        <v>195</v>
       </c>
       <c r="B347" s="1">
         <v>8800</v>
@@ -10077,7 +10078,7 @@
         <v>5</v>
       </c>
       <c r="E347" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F347">
         <v>346</v>
@@ -10088,7 +10089,7 @@
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>355</v>
+        <v>196</v>
       </c>
       <c r="B348" s="1">
         <v>8800</v>
@@ -10100,7 +10101,7 @@
         <v>5</v>
       </c>
       <c r="E348" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F348">
         <v>347</v>
@@ -10111,7 +10112,7 @@
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>356</v>
+        <v>197</v>
       </c>
       <c r="B349" s="1">
         <v>8800</v>
@@ -10123,7 +10124,7 @@
         <v>5</v>
       </c>
       <c r="E349" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F349">
         <v>348</v>
@@ -10134,7 +10135,7 @@
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>357</v>
+        <v>198</v>
       </c>
       <c r="B350" s="1">
         <v>8800</v>
@@ -10146,7 +10147,7 @@
         <v>5</v>
       </c>
       <c r="E350" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F350">
         <v>349</v>
@@ -10157,7 +10158,7 @@
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>358</v>
+        <v>199</v>
       </c>
       <c r="B351" s="1">
         <v>8800</v>
@@ -10169,7 +10170,7 @@
         <v>5</v>
       </c>
       <c r="E351" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F351">
         <v>350</v>
@@ -10180,7 +10181,7 @@
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>359</v>
+        <v>200</v>
       </c>
       <c r="B352" s="1">
         <v>7600</v>
@@ -10192,7 +10193,7 @@
         <v>5</v>
       </c>
       <c r="E352" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F352">
         <v>351</v>
@@ -10203,7 +10204,7 @@
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="B353" s="1">
         <v>7600</v>
@@ -10215,7 +10216,7 @@
         <v>5</v>
       </c>
       <c r="E353" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F353">
         <v>352</v>
@@ -10226,7 +10227,7 @@
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>361</v>
+        <v>202</v>
       </c>
       <c r="B354" s="1">
         <v>7600</v>
@@ -10238,7 +10239,7 @@
         <v>5</v>
       </c>
       <c r="E354" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F354">
         <v>353</v>
@@ -10249,7 +10250,7 @@
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>362</v>
+        <v>203</v>
       </c>
       <c r="B355" s="1">
         <v>7600</v>
@@ -10261,7 +10262,7 @@
         <v>5</v>
       </c>
       <c r="E355" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F355">
         <v>354</v>
@@ -10272,7 +10273,7 @@
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>363</v>
+        <v>204</v>
       </c>
       <c r="B356" s="1">
         <v>7600</v>
@@ -10284,7 +10285,7 @@
         <v>5</v>
       </c>
       <c r="E356" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F356">
         <v>355</v>
@@ -10295,7 +10296,7 @@
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>364</v>
+        <v>205</v>
       </c>
       <c r="B357" s="1">
         <v>7600</v>
@@ -10307,7 +10308,7 @@
         <v>5</v>
       </c>
       <c r="E357" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F357">
         <v>356</v>
@@ -10318,7 +10319,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>363</v>
+        <v>204</v>
       </c>
       <c r="B358" s="1">
         <v>7600</v>
@@ -10330,7 +10331,7 @@
         <v>5</v>
       </c>
       <c r="E358" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F358">
         <v>357</v>
@@ -10341,7 +10342,7 @@
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>365</v>
+        <v>206</v>
       </c>
       <c r="B359" s="1">
         <v>1200</v>
@@ -10353,7 +10354,7 @@
         <v>20</v>
       </c>
       <c r="E359" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F359">
         <v>358</v>
@@ -10364,7 +10365,7 @@
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>366</v>
+        <v>207</v>
       </c>
       <c r="B360" s="1">
         <v>160</v>
@@ -10376,7 +10377,7 @@
         <v>100</v>
       </c>
       <c r="E360" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F360">
         <v>359</v>
@@ -10387,7 +10388,7 @@
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>367</v>
+        <v>208</v>
       </c>
       <c r="B361" s="1">
         <v>160</v>
@@ -10399,7 +10400,7 @@
         <v>100</v>
       </c>
       <c r="E361" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F361">
         <v>360</v>
@@ -10410,7 +10411,7 @@
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>368</v>
+        <v>209</v>
       </c>
       <c r="B362" s="1">
         <v>160</v>
@@ -10422,7 +10423,7 @@
         <v>100</v>
       </c>
       <c r="E362" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F362">
         <v>361</v>
@@ -10433,7 +10434,7 @@
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>369</v>
+        <v>210</v>
       </c>
       <c r="B363" s="1">
         <v>160</v>
@@ -10445,7 +10446,7 @@
         <v>100</v>
       </c>
       <c r="E363" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F363">
         <v>362</v>
@@ -10456,7 +10457,7 @@
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>370</v>
+        <v>211</v>
       </c>
       <c r="B364" s="1">
         <v>960</v>
@@ -10468,7 +10469,7 @@
         <v>12</v>
       </c>
       <c r="E364" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F364">
         <v>363</v>
@@ -10479,7 +10480,7 @@
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>371</v>
+        <v>212</v>
       </c>
       <c r="B365" s="1">
         <v>2200</v>
@@ -10491,7 +10492,7 @@
         <v>12</v>
       </c>
       <c r="E365" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F365">
         <v>364</v>
@@ -10502,7 +10503,7 @@
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>372</v>
+        <v>213</v>
       </c>
       <c r="B366" s="1">
         <v>2400</v>
@@ -10514,7 +10515,7 @@
         <v>12</v>
       </c>
       <c r="E366" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F366">
         <v>365</v>
@@ -10525,7 +10526,7 @@
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>373</v>
+        <v>214</v>
       </c>
       <c r="B367" s="1">
         <v>1100</v>
@@ -10537,7 +10538,7 @@
         <v>12</v>
       </c>
       <c r="E367" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F367">
         <v>366</v>
@@ -10548,7 +10549,7 @@
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>374</v>
+        <v>215</v>
       </c>
       <c r="B368" s="1">
         <v>1400</v>
@@ -10560,7 +10561,7 @@
         <v>12</v>
       </c>
       <c r="E368" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F368">
         <v>367</v>
@@ -10571,7 +10572,7 @@
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>375</v>
+        <v>216</v>
       </c>
       <c r="B369" s="1">
         <v>2200</v>
@@ -10583,7 +10584,7 @@
         <v>12</v>
       </c>
       <c r="E369" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F369">
         <v>368</v>
@@ -10594,7 +10595,7 @@
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>376</v>
+        <v>217</v>
       </c>
       <c r="B370" s="1">
         <v>880</v>
@@ -10606,7 +10607,7 @@
         <v>12</v>
       </c>
       <c r="E370" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F370">
         <v>369</v>
@@ -10617,7 +10618,7 @@
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>377</v>
+        <v>218</v>
       </c>
       <c r="B371" s="1">
         <v>1300</v>
@@ -10629,7 +10630,7 @@
         <v>12</v>
       </c>
       <c r="E371" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F371">
         <v>370</v>
@@ -10640,7 +10641,7 @@
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>378</v>
+        <v>219</v>
       </c>
       <c r="B372" s="1">
         <v>8300</v>
@@ -10652,7 +10653,7 @@
         <v>2</v>
       </c>
       <c r="E372" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F372">
         <v>371</v>
@@ -10663,7 +10664,7 @@
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>379</v>
+        <v>220</v>
       </c>
       <c r="B373" s="1">
         <v>4560</v>
@@ -10675,7 +10676,7 @@
         <v>10</v>
       </c>
       <c r="E373" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F373">
         <v>372</v>
@@ -10686,7 +10687,7 @@
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>380</v>
+        <v>221</v>
       </c>
       <c r="B374" s="1">
         <v>440</v>
@@ -10698,7 +10699,7 @@
         <v>12</v>
       </c>
       <c r="E374" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F374">
         <v>373</v>
@@ -10709,7 +10710,7 @@
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>381</v>
+        <v>222</v>
       </c>
       <c r="B375" s="1">
         <v>440</v>
@@ -10721,7 +10722,7 @@
         <v>12</v>
       </c>
       <c r="E375" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F375">
         <v>374</v>
@@ -10732,7 +10733,7 @@
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>382</v>
+        <v>223</v>
       </c>
       <c r="B376" s="1">
         <v>440</v>
@@ -10744,7 +10745,7 @@
         <v>12</v>
       </c>
       <c r="E376" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F376">
         <v>375</v>
@@ -10755,7 +10756,7 @@
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>383</v>
+        <v>224</v>
       </c>
       <c r="B377" s="1">
         <v>440</v>
@@ -10767,7 +10768,7 @@
         <v>12</v>
       </c>
       <c r="E377" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F377">
         <v>376</v>
@@ -10778,7 +10779,7 @@
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>384</v>
+        <v>225</v>
       </c>
       <c r="B378" s="1">
         <v>440</v>
@@ -10790,7 +10791,7 @@
         <v>12</v>
       </c>
       <c r="E378" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F378">
         <v>377</v>
@@ -10801,7 +10802,7 @@
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>385</v>
+        <v>226</v>
       </c>
       <c r="B379" s="1">
         <v>440</v>
@@ -10813,7 +10814,7 @@
         <v>12</v>
       </c>
       <c r="E379" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F379">
         <v>378</v>
@@ -10824,7 +10825,7 @@
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>386</v>
+        <v>227</v>
       </c>
       <c r="B380" s="1">
         <v>440</v>
@@ -10836,7 +10837,7 @@
         <v>12</v>
       </c>
       <c r="E380" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F380">
         <v>379</v>
@@ -10847,7 +10848,7 @@
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>387</v>
+        <v>228</v>
       </c>
       <c r="B381" s="1">
         <v>440</v>
@@ -10859,7 +10860,7 @@
         <v>12</v>
       </c>
       <c r="E381" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F381">
         <v>380</v>
@@ -10870,7 +10871,7 @@
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>388</v>
+        <v>229</v>
       </c>
       <c r="B382" s="1">
         <v>440</v>
@@ -10882,7 +10883,7 @@
         <v>12</v>
       </c>
       <c r="E382" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F382">
         <v>381</v>
@@ -10893,7 +10894,7 @@
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>389</v>
+        <v>230</v>
       </c>
       <c r="B383" s="1">
         <v>440</v>
@@ -10905,7 +10906,7 @@
         <v>12</v>
       </c>
       <c r="E383" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F383">
         <v>382</v>
@@ -10916,7 +10917,7 @@
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>390</v>
+        <v>231</v>
       </c>
       <c r="B384" s="1">
         <v>440</v>
@@ -10928,7 +10929,7 @@
         <v>12</v>
       </c>
       <c r="E384" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F384">
         <v>383</v>
@@ -10939,7 +10940,7 @@
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>391</v>
+        <v>232</v>
       </c>
       <c r="B385" s="1">
         <v>440</v>
@@ -10951,7 +10952,7 @@
         <v>12</v>
       </c>
       <c r="E385" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F385">
         <v>384</v>
@@ -10962,7 +10963,7 @@
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>392</v>
+        <v>233</v>
       </c>
       <c r="B386" s="1">
         <v>440</v>
@@ -10974,7 +10975,7 @@
         <v>12</v>
       </c>
       <c r="E386" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F386">
         <v>385</v>
@@ -10985,7 +10986,7 @@
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>393</v>
+        <v>234</v>
       </c>
       <c r="B387" s="1">
         <v>440</v>
@@ -10997,7 +10998,7 @@
         <v>12</v>
       </c>
       <c r="E387" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F387">
         <v>386</v>
@@ -11008,7 +11009,7 @@
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>394</v>
+        <v>235</v>
       </c>
       <c r="B388" s="1">
         <v>2760</v>
@@ -11020,7 +11021,7 @@
         <v>10</v>
       </c>
       <c r="E388" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F388">
         <v>387</v>
@@ -11031,7 +11032,7 @@
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>395</v>
+        <v>236</v>
       </c>
       <c r="B389" s="1">
         <v>2760</v>
@@ -11043,7 +11044,7 @@
         <v>10</v>
       </c>
       <c r="E389" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F389">
         <v>388</v>
@@ -11054,7 +11055,7 @@
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>396</v>
+        <v>237</v>
       </c>
       <c r="B390" s="1">
         <v>1380</v>
@@ -11066,7 +11067,7 @@
         <v>10</v>
       </c>
       <c r="E390" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F390">
         <v>389</v>
@@ -11077,7 +11078,7 @@
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>397</v>
+        <v>238</v>
       </c>
       <c r="B391" s="1">
         <v>2540</v>
@@ -11089,7 +11090,7 @@
         <v>10</v>
       </c>
       <c r="E391" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F391">
         <v>390</v>
@@ -11100,7 +11101,7 @@
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>398</v>
+        <v>239</v>
       </c>
       <c r="B392" s="1">
         <v>320</v>
@@ -11112,7 +11113,7 @@
         <v>50</v>
       </c>
       <c r="E392" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F392">
         <v>391</v>
@@ -11123,7 +11124,7 @@
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>399</v>
+        <v>240</v>
       </c>
       <c r="B393" s="1">
         <v>6050</v>
@@ -11135,7 +11136,7 @@
         <v>6</v>
       </c>
       <c r="E393" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F393">
         <v>392</v>
@@ -11146,7 +11147,7 @@
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>400</v>
+        <v>241</v>
       </c>
       <c r="B394" s="1">
         <v>10200</v>
@@ -11158,7 +11159,7 @@
         <v>6</v>
       </c>
       <c r="E394" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F394">
         <v>393</v>
@@ -11169,7 +11170,7 @@
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>401</v>
+        <v>242</v>
       </c>
       <c r="B395" s="1">
         <v>1380</v>
@@ -11181,7 +11182,7 @@
         <v>120</v>
       </c>
       <c r="E395" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F395">
         <v>394</v>
@@ -11192,7 +11193,7 @@
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>402</v>
+        <v>243</v>
       </c>
       <c r="B396" s="1">
         <v>1380</v>
@@ -11204,7 +11205,7 @@
         <v>120</v>
       </c>
       <c r="E396" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F396">
         <v>395</v>
@@ -11215,7 +11216,7 @@
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>403</v>
+        <v>244</v>
       </c>
       <c r="B397" s="1">
         <v>3440</v>
@@ -11227,7 +11228,7 @@
         <v>12</v>
       </c>
       <c r="E397" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F397">
         <v>396</v>

--- a/templates/importar_productos_template.xlsx
+++ b/templates/importar_productos_template.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duqueroso/Desktop/opencode-projects/control-plus/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60346398-03B0-4140-998E-608417BAFB1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F30022F-8776-0548-8A3A-69839935550E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1600" yWindow="1400" windowWidth="27640" windowHeight="16680" xr2:uid="{C1719250-87E2-DB49-8C6B-072748A47088}"/>
   </bookViews>
   <sheets>
     <sheet name="importar_productos_template" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">importar_productos_template!$A$1:$A$397</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="406">
   <si>
     <t>nombre</t>
   </si>
@@ -1232,6 +1235,12 @@
   </si>
   <si>
     <t>TABLA PERIODICA GRANDE</t>
+  </si>
+  <si>
+    <t>CUADERNO COSIDO 100-2 LINK STICKER FEMENINO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CINTA SATIN DORADO  2.5CM X 45MTS </t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1775,18 @@
     <cellStyle name="Título 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -6662,7 +6682,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>52</v>
+        <v>404</v>
       </c>
       <c r="B199" s="1">
         <v>2990</v>
@@ -10319,7 +10339,7 @@
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>204</v>
+        <v>405</v>
       </c>
       <c r="B358" s="1">
         <v>7600</v>
@@ -11238,6 +11258,10 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:A397" xr:uid="{2CC4BADA-14F4-D54D-A860-0AAF5E159701}"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>